--- a/고양이_오메가3_제품_채점표.xlsx
+++ b/고양이_오메가3_제품_채점표.xlsx
@@ -1196,20 +1196,18 @@
           <t>명시</t>
         </is>
       </c>
-      <c r="O2" s="7" t="inlineStr">
+      <c r="O2" s="7">
+        <f>IF(H2="식물성","Y","N")</f>
+        <v/>
+      </c>
+      <c r="P2" s="7" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P2" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q2" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+      <c r="Q2" s="7">
+        <f>IF(AND(J2="취약",I2&lt;&gt;"있음",OR(M2="없음",M2="미상")),"Y","N")</f>
+        <v/>
       </c>
       <c r="R2" s="8">
         <f>IF(NOT(ISNUMBER(D2)),0,IF(D2&gt;=300,20,IF(D2&gt;=200,15,IF(D2&gt;=100,10,5))))+IF(NOT(ISNUMBER(E2)),0,IF(E2&gt;=60,10,IF(E2&gt;=40,6,3)))+IFERROR(VLOOKUP(F2,기준!$B$4:$C$7,2,FALSE),0)</f>
@@ -1328,20 +1326,18 @@
           <t>명시</t>
         </is>
       </c>
-      <c r="O3" s="7" t="inlineStr">
+      <c r="O3" s="7">
+        <f>IF(H3="식물성","Y","N")</f>
+        <v/>
+      </c>
+      <c r="P3" s="7" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P3" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q3" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+      <c r="Q3" s="7">
+        <f>IF(AND(J3="취약",I3&lt;&gt;"있음",OR(M3="없음",M3="미상")),"Y","N")</f>
+        <v/>
       </c>
       <c r="R3" s="8">
         <f>IF(NOT(ISNUMBER(D3)),0,IF(D3&gt;=300,20,IF(D3&gt;=200,15,IF(D3&gt;=100,10,5))))+IF(NOT(ISNUMBER(E3)),0,IF(E3&gt;=60,10,IF(E3&gt;=40,6,3)))+IFERROR(VLOOKUP(F3,기준!$B$4:$C$7,2,FALSE),0)</f>
@@ -1462,20 +1458,18 @@
           <t>명시</t>
         </is>
       </c>
-      <c r="O4" s="7" t="inlineStr">
+      <c r="O4" s="7">
+        <f>IF(H4="식물성","Y","N")</f>
+        <v/>
+      </c>
+      <c r="P4" s="7" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P4" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q4" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+      <c r="Q4" s="7">
+        <f>IF(AND(J4="취약",I4&lt;&gt;"있음",OR(M4="없음",M4="미상")),"Y","N")</f>
+        <v/>
       </c>
       <c r="R4" s="8">
         <f>IF(NOT(ISNUMBER(D4)),0,IF(D4&gt;=300,20,IF(D4&gt;=200,15,IF(D4&gt;=100,10,5))))+IF(NOT(ISNUMBER(E4)),0,IF(E4&gt;=60,10,IF(E4&gt;=40,6,3)))+IFERROR(VLOOKUP(F4,기준!$B$4:$C$7,2,FALSE),0)</f>
@@ -1596,20 +1590,18 @@
           <t>명시</t>
         </is>
       </c>
-      <c r="O5" s="7" t="inlineStr">
+      <c r="O5" s="7">
+        <f>IF(H5="식물성","Y","N")</f>
+        <v/>
+      </c>
+      <c r="P5" s="7" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P5" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q5" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+      <c r="Q5" s="7">
+        <f>IF(AND(J5="취약",I5&lt;&gt;"있음",OR(M5="없음",M5="미상")),"Y","N")</f>
+        <v/>
       </c>
       <c r="R5" s="8">
         <f>IF(NOT(ISNUMBER(D5)),0,IF(D5&gt;=300,20,IF(D5&gt;=200,15,IF(D5&gt;=100,10,5))))+IF(NOT(ISNUMBER(E5)),0,IF(E5&gt;=60,10,IF(E5&gt;=40,6,3)))+IFERROR(VLOOKUP(F5,기준!$B$4:$C$7,2,FALSE),0)</f>
@@ -1730,20 +1722,18 @@
           <t>명시</t>
         </is>
       </c>
-      <c r="O6" s="7" t="inlineStr">
+      <c r="O6" s="7">
+        <f>IF(H6="식물성","Y","N")</f>
+        <v/>
+      </c>
+      <c r="P6" s="7" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P6" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q6" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+      <c r="Q6" s="7">
+        <f>IF(AND(J6="취약",I6&lt;&gt;"있음",OR(M6="없음",M6="미상")),"Y","N")</f>
+        <v/>
       </c>
       <c r="R6" s="8">
         <f>IF(NOT(ISNUMBER(D6)),0,IF(D6&gt;=300,20,IF(D6&gt;=200,15,IF(D6&gt;=100,10,5))))+IF(NOT(ISNUMBER(E6)),0,IF(E6&gt;=60,10,IF(E6&gt;=40,6,3)))+IFERROR(VLOOKUP(F6,기준!$B$4:$C$7,2,FALSE),0)</f>
@@ -1864,20 +1854,18 @@
           <t>명시</t>
         </is>
       </c>
-      <c r="O7" s="7" t="inlineStr">
+      <c r="O7" s="7">
+        <f>IF(H7="식물성","Y","N")</f>
+        <v/>
+      </c>
+      <c r="P7" s="7" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P7" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q7" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+      <c r="Q7" s="7">
+        <f>IF(AND(J7="취약",I7&lt;&gt;"있음",OR(M7="없음",M7="미상")),"Y","N")</f>
+        <v/>
       </c>
       <c r="R7" s="8">
         <f>IF(NOT(ISNUMBER(D7)),0,IF(D7&gt;=300,20,IF(D7&gt;=200,15,IF(D7&gt;=100,10,5))))+IF(NOT(ISNUMBER(E7)),0,IF(E7&gt;=60,10,IF(E7&gt;=40,6,3)))+IFERROR(VLOOKUP(F7,기준!$B$4:$C$7,2,FALSE),0)</f>
@@ -1994,20 +1982,18 @@
           <t>미상</t>
         </is>
       </c>
-      <c r="O8" s="7" t="inlineStr">
+      <c r="O8" s="7">
+        <f>IF(H8="식물성","Y","N")</f>
+        <v/>
+      </c>
+      <c r="P8" s="7" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P8" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q8" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+      <c r="Q8" s="7">
+        <f>IF(AND(J8="취약",I8&lt;&gt;"있음",OR(M8="없음",M8="미상")),"Y","N")</f>
+        <v/>
       </c>
       <c r="R8" s="8">
         <f>IF(NOT(ISNUMBER(D8)),0,IF(D8&gt;=300,20,IF(D8&gt;=200,15,IF(D8&gt;=100,10,5))))+IF(NOT(ISNUMBER(E8)),0,IF(E8&gt;=60,10,IF(E8&gt;=40,6,3)))+IFERROR(VLOOKUP(F8,기준!$B$4:$C$7,2,FALSE),0)</f>
@@ -2124,20 +2110,18 @@
           <t>미상</t>
         </is>
       </c>
-      <c r="O9" s="7" t="inlineStr">
+      <c r="O9" s="7">
+        <f>IF(H9="식물성","Y","N")</f>
+        <v/>
+      </c>
+      <c r="P9" s="7" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P9" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q9" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+      <c r="Q9" s="7">
+        <f>IF(AND(J9="취약",I9&lt;&gt;"있음",OR(M9="없음",M9="미상")),"Y","N")</f>
+        <v/>
       </c>
       <c r="R9" s="8">
         <f>IF(NOT(ISNUMBER(D9)),0,IF(D9&gt;=300,20,IF(D9&gt;=200,15,IF(D9&gt;=100,10,5))))+IF(NOT(ISNUMBER(E9)),0,IF(E9&gt;=60,10,IF(E9&gt;=40,6,3)))+IFERROR(VLOOKUP(F9,기준!$B$4:$C$7,2,FALSE),0)</f>
@@ -2254,20 +2238,18 @@
           <t>미상</t>
         </is>
       </c>
-      <c r="O10" s="7" t="inlineStr">
+      <c r="O10" s="7">
+        <f>IF(H10="식물성","Y","N")</f>
+        <v/>
+      </c>
+      <c r="P10" s="7" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P10" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q10" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+      <c r="Q10" s="7">
+        <f>IF(AND(J10="취약",I10&lt;&gt;"있음",OR(M10="없음",M10="미상")),"Y","N")</f>
+        <v/>
       </c>
       <c r="R10" s="8">
         <f>IF(NOT(ISNUMBER(D10)),0,IF(D10&gt;=300,20,IF(D10&gt;=200,15,IF(D10&gt;=100,10,5))))+IF(NOT(ISNUMBER(E10)),0,IF(E10&gt;=60,10,IF(E10&gt;=40,6,3)))+IFERROR(VLOOKUP(F10,기준!$B$4:$C$7,2,FALSE),0)</f>
@@ -2384,20 +2366,18 @@
           <t>미상</t>
         </is>
       </c>
-      <c r="O11" s="7" t="inlineStr">
+      <c r="O11" s="7">
+        <f>IF(H11="식물성","Y","N")</f>
+        <v/>
+      </c>
+      <c r="P11" s="7" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P11" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q11" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+      <c r="Q11" s="7">
+        <f>IF(AND(J11="취약",I11&lt;&gt;"있음",OR(M11="없음",M11="미상")),"Y","N")</f>
+        <v/>
       </c>
       <c r="R11" s="8">
         <f>IF(NOT(ISNUMBER(D11)),0,IF(D11&gt;=300,20,IF(D11&gt;=200,15,IF(D11&gt;=100,10,5))))+IF(NOT(ISNUMBER(E11)),0,IF(E11&gt;=60,10,IF(E11&gt;=40,6,3)))+IFERROR(VLOOKUP(F11,기준!$B$4:$C$7,2,FALSE),0)</f>
@@ -2514,20 +2494,18 @@
           <t>미상</t>
         </is>
       </c>
-      <c r="O12" s="7" t="inlineStr">
+      <c r="O12" s="7">
+        <f>IF(H12="식물성","Y","N")</f>
+        <v/>
+      </c>
+      <c r="P12" s="7" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P12" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q12" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+      <c r="Q12" s="7">
+        <f>IF(AND(J12="취약",I12&lt;&gt;"있음",OR(M12="없음",M12="미상")),"Y","N")</f>
+        <v/>
       </c>
       <c r="R12" s="8">
         <f>IF(NOT(ISNUMBER(D12)),0,IF(D12&gt;=300,20,IF(D12&gt;=200,15,IF(D12&gt;=100,10,5))))+IF(NOT(ISNUMBER(E12)),0,IF(E12&gt;=60,10,IF(E12&gt;=40,6,3)))+IFERROR(VLOOKUP(F12,기준!$B$4:$C$7,2,FALSE),0)</f>
@@ -2644,20 +2622,18 @@
           <t>미상</t>
         </is>
       </c>
-      <c r="O13" s="7" t="inlineStr">
+      <c r="O13" s="7">
+        <f>IF(H13="식물성","Y","N")</f>
+        <v/>
+      </c>
+      <c r="P13" s="7" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P13" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q13" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+      <c r="Q13" s="7">
+        <f>IF(AND(J13="취약",I13&lt;&gt;"있음",OR(M13="없음",M13="미상")),"Y","N")</f>
+        <v/>
       </c>
       <c r="R13" s="8">
         <f>IF(NOT(ISNUMBER(D13)),0,IF(D13&gt;=300,20,IF(D13&gt;=200,15,IF(D13&gt;=100,10,5))))+IF(NOT(ISNUMBER(E13)),0,IF(E13&gt;=60,10,IF(E13&gt;=40,6,3)))+IFERROR(VLOOKUP(F13,기준!$B$4:$C$7,2,FALSE),0)</f>
@@ -2774,20 +2750,18 @@
           <t>미상</t>
         </is>
       </c>
-      <c r="O14" s="7" t="inlineStr">
+      <c r="O14" s="7">
+        <f>IF(H14="식물성","Y","N")</f>
+        <v/>
+      </c>
+      <c r="P14" s="7" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P14" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q14" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+      <c r="Q14" s="7">
+        <f>IF(AND(J14="취약",I14&lt;&gt;"있음",OR(M14="없음",M14="미상")),"Y","N")</f>
+        <v/>
       </c>
       <c r="R14" s="8">
         <f>IF(NOT(ISNUMBER(D14)),0,IF(D14&gt;=300,20,IF(D14&gt;=200,15,IF(D14&gt;=100,10,5))))+IF(NOT(ISNUMBER(E14)),0,IF(E14&gt;=60,10,IF(E14&gt;=40,6,3)))+IFERROR(VLOOKUP(F14,기준!$B$4:$C$7,2,FALSE),0)</f>
@@ -2904,20 +2878,18 @@
           <t>미상</t>
         </is>
       </c>
-      <c r="O15" s="7" t="inlineStr">
+      <c r="O15" s="7">
+        <f>IF(H15="식물성","Y","N")</f>
+        <v/>
+      </c>
+      <c r="P15" s="7" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P15" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q15" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+      <c r="Q15" s="7">
+        <f>IF(AND(J15="취약",I15&lt;&gt;"있음",OR(M15="없음",M15="미상")),"Y","N")</f>
+        <v/>
       </c>
       <c r="R15" s="8">
         <f>IF(NOT(ISNUMBER(D15)),0,IF(D15&gt;=300,20,IF(D15&gt;=200,15,IF(D15&gt;=100,10,5))))+IF(NOT(ISNUMBER(E15)),0,IF(E15&gt;=60,10,IF(E15&gt;=40,6,3)))+IFERROR(VLOOKUP(F15,기준!$B$4:$C$7,2,FALSE),0)</f>
@@ -3034,20 +3006,18 @@
           <t>미상</t>
         </is>
       </c>
-      <c r="O16" s="7" t="inlineStr">
+      <c r="O16" s="7">
+        <f>IF(H16="식물성","Y","N")</f>
+        <v/>
+      </c>
+      <c r="P16" s="7" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P16" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q16" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+      <c r="Q16" s="7">
+        <f>IF(AND(J16="취약",I16&lt;&gt;"있음",OR(M16="없음",M16="미상")),"Y","N")</f>
+        <v/>
       </c>
       <c r="R16" s="8">
         <f>IF(NOT(ISNUMBER(D16)),0,IF(D16&gt;=300,20,IF(D16&gt;=200,15,IF(D16&gt;=100,10,5))))+IF(NOT(ISNUMBER(E16)),0,IF(E16&gt;=60,10,IF(E16&gt;=40,6,3)))+IFERROR(VLOOKUP(F16,기준!$B$4:$C$7,2,FALSE),0)</f>
@@ -3164,20 +3134,18 @@
           <t>미상</t>
         </is>
       </c>
-      <c r="O17" s="7" t="inlineStr">
+      <c r="O17" s="7">
+        <f>IF(H17="식물성","Y","N")</f>
+        <v/>
+      </c>
+      <c r="P17" s="7" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P17" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q17" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+      <c r="Q17" s="7">
+        <f>IF(AND(J17="취약",I17&lt;&gt;"있음",OR(M17="없음",M17="미상")),"Y","N")</f>
+        <v/>
       </c>
       <c r="R17" s="8">
         <f>IF(NOT(ISNUMBER(D17)),0,IF(D17&gt;=300,20,IF(D17&gt;=200,15,IF(D17&gt;=100,10,5))))+IF(NOT(ISNUMBER(E17)),0,IF(E17&gt;=60,10,IF(E17&gt;=40,6,3)))+IFERROR(VLOOKUP(F17,기준!$B$4:$C$7,2,FALSE),0)</f>
@@ -3294,20 +3262,18 @@
           <t>미상</t>
         </is>
       </c>
-      <c r="O18" s="7" t="inlineStr">
+      <c r="O18" s="7">
+        <f>IF(H18="식물성","Y","N")</f>
+        <v/>
+      </c>
+      <c r="P18" s="7" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P18" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q18" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+      <c r="Q18" s="7">
+        <f>IF(AND(J18="취약",I18&lt;&gt;"있음",OR(M18="없음",M18="미상")),"Y","N")</f>
+        <v/>
       </c>
       <c r="R18" s="8">
         <f>IF(NOT(ISNUMBER(D18)),0,IF(D18&gt;=300,20,IF(D18&gt;=200,15,IF(D18&gt;=100,10,5))))+IF(NOT(ISNUMBER(E18)),0,IF(E18&gt;=60,10,IF(E18&gt;=40,6,3)))+IFERROR(VLOOKUP(F18,기준!$B$4:$C$7,2,FALSE),0)</f>
@@ -3424,20 +3390,18 @@
           <t>미상</t>
         </is>
       </c>
-      <c r="O19" s="7" t="inlineStr">
+      <c r="O19" s="7">
+        <f>IF(H19="식물성","Y","N")</f>
+        <v/>
+      </c>
+      <c r="P19" s="7" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P19" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q19" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+      <c r="Q19" s="7">
+        <f>IF(AND(J19="취약",I19&lt;&gt;"있음",OR(M19="없음",M19="미상")),"Y","N")</f>
+        <v/>
       </c>
       <c r="R19" s="8">
         <f>IF(NOT(ISNUMBER(D19)),0,IF(D19&gt;=300,20,IF(D19&gt;=200,15,IF(D19&gt;=100,10,5))))+IF(NOT(ISNUMBER(E19)),0,IF(E19&gt;=60,10,IF(E19&gt;=40,6,3)))+IFERROR(VLOOKUP(F19,기준!$B$4:$C$7,2,FALSE),0)</f>
@@ -3554,20 +3518,18 @@
           <t>미상</t>
         </is>
       </c>
-      <c r="O20" s="7" t="inlineStr">
+      <c r="O20" s="7">
+        <f>IF(H20="식물성","Y","N")</f>
+        <v/>
+      </c>
+      <c r="P20" s="7" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P20" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q20" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+      <c r="Q20" s="7">
+        <f>IF(AND(J20="취약",I20&lt;&gt;"있음",OR(M20="없음",M20="미상")),"Y","N")</f>
+        <v/>
       </c>
       <c r="R20" s="8">
         <f>IF(NOT(ISNUMBER(D20)),0,IF(D20&gt;=300,20,IF(D20&gt;=200,15,IF(D20&gt;=100,10,5))))+IF(NOT(ISNUMBER(E20)),0,IF(E20&gt;=60,10,IF(E20&gt;=40,6,3)))+IFERROR(VLOOKUP(F20,기준!$B$4:$C$7,2,FALSE),0)</f>
@@ -3684,20 +3646,18 @@
           <t>미상</t>
         </is>
       </c>
-      <c r="O21" s="7" t="inlineStr">
+      <c r="O21" s="7">
+        <f>IF(H21="식물성","Y","N")</f>
+        <v/>
+      </c>
+      <c r="P21" s="7" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P21" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q21" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+      <c r="Q21" s="7">
+        <f>IF(AND(J21="취약",I21&lt;&gt;"있음",OR(M21="없음",M21="미상")),"Y","N")</f>
+        <v/>
       </c>
       <c r="R21" s="8">
         <f>IF(NOT(ISNUMBER(D21)),0,IF(D21&gt;=300,20,IF(D21&gt;=200,15,IF(D21&gt;=100,10,5))))+IF(NOT(ISNUMBER(E21)),0,IF(E21&gt;=60,10,IF(E21&gt;=40,6,3)))+IFERROR(VLOOKUP(F21,기준!$B$4:$C$7,2,FALSE),0)</f>
@@ -3814,20 +3774,18 @@
           <t>미상</t>
         </is>
       </c>
-      <c r="O22" s="7" t="inlineStr">
+      <c r="O22" s="7">
+        <f>IF(H22="식물성","Y","N")</f>
+        <v/>
+      </c>
+      <c r="P22" s="7" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P22" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q22" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+      <c r="Q22" s="7">
+        <f>IF(AND(J22="취약",I22&lt;&gt;"있음",OR(M22="없음",M22="미상")),"Y","N")</f>
+        <v/>
       </c>
       <c r="R22" s="8">
         <f>IF(NOT(ISNUMBER(D22)),0,IF(D22&gt;=300,20,IF(D22&gt;=200,15,IF(D22&gt;=100,10,5))))+IF(NOT(ISNUMBER(E22)),0,IF(E22&gt;=60,10,IF(E22&gt;=40,6,3)))+IFERROR(VLOOKUP(F22,기준!$B$4:$C$7,2,FALSE),0)</f>
@@ -3946,20 +3904,18 @@
           <t>미상</t>
         </is>
       </c>
-      <c r="O23" s="7" t="inlineStr">
+      <c r="O23" s="7">
+        <f>IF(H23="식물성","Y","N")</f>
+        <v/>
+      </c>
+      <c r="P23" s="7" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P23" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q23" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+      <c r="Q23" s="7">
+        <f>IF(AND(J23="취약",I23&lt;&gt;"있음",OR(M23="없음",M23="미상")),"Y","N")</f>
+        <v/>
       </c>
       <c r="R23" s="8">
         <f>IF(NOT(ISNUMBER(D23)),0,IF(D23&gt;=300,20,IF(D23&gt;=200,15,IF(D23&gt;=100,10,5))))+IF(NOT(ISNUMBER(E23)),0,IF(E23&gt;=60,10,IF(E23&gt;=40,6,3)))+IFERROR(VLOOKUP(F23,기준!$B$4:$C$7,2,FALSE),0)</f>
@@ -4076,20 +4032,18 @@
           <t>미상</t>
         </is>
       </c>
-      <c r="O24" s="7" t="inlineStr">
+      <c r="O24" s="7">
+        <f>IF(H24="식물성","Y","N")</f>
+        <v/>
+      </c>
+      <c r="P24" s="7" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P24" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q24" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+      <c r="Q24" s="7">
+        <f>IF(AND(J24="취약",I24&lt;&gt;"있음",OR(M24="없음",M24="미상")),"Y","N")</f>
+        <v/>
       </c>
       <c r="R24" s="8">
         <f>IF(NOT(ISNUMBER(D24)),0,IF(D24&gt;=300,20,IF(D24&gt;=200,15,IF(D24&gt;=100,10,5))))+IF(NOT(ISNUMBER(E24)),0,IF(E24&gt;=60,10,IF(E24&gt;=40,6,3)))+IFERROR(VLOOKUP(F24,기준!$B$4:$C$7,2,FALSE),0)</f>
@@ -4206,20 +4160,18 @@
           <t>미상</t>
         </is>
       </c>
-      <c r="O25" s="7" t="inlineStr">
+      <c r="O25" s="7">
+        <f>IF(H25="식물성","Y","N")</f>
+        <v/>
+      </c>
+      <c r="P25" s="7" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P25" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q25" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+      <c r="Q25" s="7">
+        <f>IF(AND(J25="취약",I25&lt;&gt;"있음",OR(M25="없음",M25="미상")),"Y","N")</f>
+        <v/>
       </c>
       <c r="R25" s="8">
         <f>IF(NOT(ISNUMBER(D25)),0,IF(D25&gt;=300,20,IF(D25&gt;=200,15,IF(D25&gt;=100,10,5))))+IF(NOT(ISNUMBER(E25)),0,IF(E25&gt;=60,10,IF(E25&gt;=40,6,3)))+IFERROR(VLOOKUP(F25,기준!$B$4:$C$7,2,FALSE),0)</f>
@@ -4336,20 +4288,18 @@
           <t>미상</t>
         </is>
       </c>
-      <c r="O26" s="7" t="inlineStr">
+      <c r="O26" s="7">
+        <f>IF(H26="식물성","Y","N")</f>
+        <v/>
+      </c>
+      <c r="P26" s="7" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P26" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q26" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+      <c r="Q26" s="7">
+        <f>IF(AND(J26="취약",I26&lt;&gt;"있음",OR(M26="없음",M26="미상")),"Y","N")</f>
+        <v/>
       </c>
       <c r="R26" s="8">
         <f>IF(NOT(ISNUMBER(D26)),0,IF(D26&gt;=300,20,IF(D26&gt;=200,15,IF(D26&gt;=100,10,5))))+IF(NOT(ISNUMBER(E26)),0,IF(E26&gt;=60,10,IF(E26&gt;=40,6,3)))+IFERROR(VLOOKUP(F26,기준!$B$4:$C$7,2,FALSE),0)</f>
@@ -4470,20 +4420,18 @@
           <t>명시</t>
         </is>
       </c>
-      <c r="O27" s="7" t="inlineStr">
+      <c r="O27" s="7">
+        <f>IF(H27="식물성","Y","N")</f>
+        <v/>
+      </c>
+      <c r="P27" s="7" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P27" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q27" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+      <c r="Q27" s="7">
+        <f>IF(AND(J27="취약",I27&lt;&gt;"있음",OR(M27="없음",M27="미상")),"Y","N")</f>
+        <v/>
       </c>
       <c r="R27" s="8">
         <f>IF(NOT(ISNUMBER(D27)),0,IF(D27&gt;=300,20,IF(D27&gt;=200,15,IF(D27&gt;=100,10,5))))+IF(NOT(ISNUMBER(E27)),0,IF(E27&gt;=60,10,IF(E27&gt;=40,6,3)))+IFERROR(VLOOKUP(F27,기준!$B$4:$C$7,2,FALSE),0)</f>
@@ -4602,20 +4550,18 @@
           <t>명시</t>
         </is>
       </c>
-      <c r="O28" s="7" t="inlineStr">
+      <c r="O28" s="7">
+        <f>IF(H28="식물성","Y","N")</f>
+        <v/>
+      </c>
+      <c r="P28" s="7" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P28" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q28" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+      <c r="Q28" s="7">
+        <f>IF(AND(J28="취약",I28&lt;&gt;"있음",OR(M28="없음",M28="미상")),"Y","N")</f>
+        <v/>
       </c>
       <c r="R28" s="8">
         <f>IF(NOT(ISNUMBER(D28)),0,IF(D28&gt;=300,20,IF(D28&gt;=200,15,IF(D28&gt;=100,10,5))))+IF(NOT(ISNUMBER(E28)),0,IF(E28&gt;=60,10,IF(E28&gt;=40,6,3)))+IFERROR(VLOOKUP(F28,기준!$B$4:$C$7,2,FALSE),0)</f>
@@ -4732,20 +4678,18 @@
           <t>미상</t>
         </is>
       </c>
-      <c r="O29" s="7" t="inlineStr">
+      <c r="O29" s="7">
+        <f>IF(H29="식물성","Y","N")</f>
+        <v/>
+      </c>
+      <c r="P29" s="7" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P29" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q29" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+      <c r="Q29" s="7">
+        <f>IF(AND(J29="취약",I29&lt;&gt;"있음",OR(M29="없음",M29="미상")),"Y","N")</f>
+        <v/>
       </c>
       <c r="R29" s="8">
         <f>IF(NOT(ISNUMBER(D29)),0,IF(D29&gt;=300,20,IF(D29&gt;=200,15,IF(D29&gt;=100,10,5))))+IF(NOT(ISNUMBER(E29)),0,IF(E29&gt;=60,10,IF(E29&gt;=40,6,3)))+IFERROR(VLOOKUP(F29,기준!$B$4:$C$7,2,FALSE),0)</f>
@@ -4864,20 +4808,18 @@
           <t>미상</t>
         </is>
       </c>
-      <c r="O30" s="7" t="inlineStr">
+      <c r="O30" s="7">
+        <f>IF(H30="식물성","Y","N")</f>
+        <v/>
+      </c>
+      <c r="P30" s="7" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P30" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q30" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+      <c r="Q30" s="7">
+        <f>IF(AND(J30="취약",I30&lt;&gt;"있음",OR(M30="없음",M30="미상")),"Y","N")</f>
+        <v/>
       </c>
       <c r="R30" s="8">
         <f>IF(NOT(ISNUMBER(D30)),0,IF(D30&gt;=300,20,IF(D30&gt;=200,15,IF(D30&gt;=100,10,5))))+IF(NOT(ISNUMBER(E30)),0,IF(E30&gt;=60,10,IF(E30&gt;=40,6,3)))+IFERROR(VLOOKUP(F30,기준!$B$4:$C$7,2,FALSE),0)</f>
@@ -4996,20 +4938,18 @@
           <t>명시</t>
         </is>
       </c>
-      <c r="O31" s="7" t="inlineStr">
+      <c r="O31" s="7">
+        <f>IF(H31="식물성","Y","N")</f>
+        <v/>
+      </c>
+      <c r="P31" s="7" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P31" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q31" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+      <c r="Q31" s="7">
+        <f>IF(AND(J31="취약",I31&lt;&gt;"있음",OR(M31="없음",M31="미상")),"Y","N")</f>
+        <v/>
       </c>
       <c r="R31" s="8">
         <f>IF(NOT(ISNUMBER(D31)),0,IF(D31&gt;=300,20,IF(D31&gt;=200,15,IF(D31&gt;=100,10,5))))+IF(NOT(ISNUMBER(E31)),0,IF(E31&gt;=60,10,IF(E31&gt;=40,6,3)))+IFERROR(VLOOKUP(F31,기준!$B$4:$C$7,2,FALSE),0)</f>
@@ -5130,20 +5070,18 @@
           <t>미상</t>
         </is>
       </c>
-      <c r="O32" s="7" t="inlineStr">
+      <c r="O32" s="7">
+        <f>IF(H32="식물성","Y","N")</f>
+        <v/>
+      </c>
+      <c r="P32" s="7" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P32" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q32" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+      <c r="Q32" s="7">
+        <f>IF(AND(J32="취약",I32&lt;&gt;"있음",OR(M32="없음",M32="미상")),"Y","N")</f>
+        <v/>
       </c>
       <c r="R32" s="8">
         <f>IF(NOT(ISNUMBER(D32)),0,IF(D32&gt;=300,20,IF(D32&gt;=200,15,IF(D32&gt;=100,10,5))))+IF(NOT(ISNUMBER(E32)),0,IF(E32&gt;=60,10,IF(E32&gt;=40,6,3)))+IFERROR(VLOOKUP(F32,기준!$B$4:$C$7,2,FALSE),0)</f>
@@ -5264,20 +5202,18 @@
           <t>명시</t>
         </is>
       </c>
-      <c r="O33" s="7" t="inlineStr">
+      <c r="O33" s="7">
+        <f>IF(H33="식물성","Y","N")</f>
+        <v/>
+      </c>
+      <c r="P33" s="7" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P33" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q33" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+      <c r="Q33" s="7">
+        <f>IF(AND(J33="취약",I33&lt;&gt;"있음",OR(M33="없음",M33="미상")),"Y","N")</f>
+        <v/>
       </c>
       <c r="R33" s="8">
         <f>IF(NOT(ISNUMBER(D33)),0,IF(D33&gt;=300,20,IF(D33&gt;=200,15,IF(D33&gt;=100,10,5))))+IF(NOT(ISNUMBER(E33)),0,IF(E33&gt;=60,10,IF(E33&gt;=40,6,3)))+IFERROR(VLOOKUP(F33,기준!$B$4:$C$7,2,FALSE),0)</f>
@@ -5396,20 +5332,18 @@
           <t>명시</t>
         </is>
       </c>
-      <c r="O34" s="7" t="inlineStr">
+      <c r="O34" s="7">
+        <f>IF(H34="식물성","Y","N")</f>
+        <v/>
+      </c>
+      <c r="P34" s="7" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P34" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q34" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+      <c r="Q34" s="7">
+        <f>IF(AND(J34="취약",I34&lt;&gt;"있음",OR(M34="없음",M34="미상")),"Y","N")</f>
+        <v/>
       </c>
       <c r="R34" s="8">
         <f>IF(NOT(ISNUMBER(D34)),0,IF(D34&gt;=300,20,IF(D34&gt;=200,15,IF(D34&gt;=100,10,5))))+IF(NOT(ISNUMBER(E34)),0,IF(E34&gt;=60,10,IF(E34&gt;=40,6,3)))+IFERROR(VLOOKUP(F34,기준!$B$4:$C$7,2,FALSE),0)</f>

--- a/고양이_오메가3_제품_채점표.xlsx
+++ b/고양이_오메가3_제품_채점표.xlsx
@@ -490,7 +490,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>가중치 성분35/산패30/원료·형태20/투명성15 | 안전상한 비해양성(ALA)→20·대구간유→40·산패고위험→50 | 조류오일=정상, 폴락=어체유(간유 아님)</t>
+          <t>가중치 성분35/산패30/원료·형태20/투명성15 | 안전상한 비해양성(ALA)→20·대구간유/비타민A·D→40·산패고위험→50 | 조류오일=정상, 폴락=어체유(간유 아님)</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC34"/>
+  <dimension ref="A1:AD34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -968,18 +968,19 @@
     <col width="8" customWidth="1" min="15" max="15"/>
     <col width="6" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="9" customWidth="1" min="18" max="18"/>
     <col width="8" customWidth="1" min="19" max="19"/>
-    <col width="11" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
-    <col width="7" customWidth="1" min="22" max="22"/>
-    <col width="9" customWidth="1" min="23" max="23"/>
+    <col width="8" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="7" customWidth="1" min="23" max="23"/>
     <col width="9" customWidth="1" min="24" max="24"/>
     <col width="9" customWidth="1" min="25" max="25"/>
-    <col width="11" customWidth="1" min="26" max="26"/>
-    <col width="9" customWidth="1" min="27" max="27"/>
-    <col width="11" customWidth="1" min="28" max="28"/>
-    <col width="44" customWidth="1" min="29" max="29"/>
+    <col width="9" customWidth="1" min="26" max="26"/>
+    <col width="11" customWidth="1" min="27" max="27"/>
+    <col width="9" customWidth="1" min="28" max="28"/>
+    <col width="11" customWidth="1" min="29" max="29"/>
+    <col width="44" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1" ht="42" customHeight="1">
@@ -1070,60 +1071,65 @@
       </c>
       <c r="R1" s="5" t="inlineStr">
         <is>
+          <t>비타민AD</t>
+        </is>
+      </c>
+      <c r="S1" s="5" t="inlineStr">
+        <is>
           <t>성분/35</t>
         </is>
       </c>
-      <c r="S1" s="5" t="inlineStr">
+      <c r="T1" s="5" t="inlineStr">
         <is>
           <t>산패/30</t>
         </is>
       </c>
-      <c r="T1" s="5" t="inlineStr">
+      <c r="U1" s="5" t="inlineStr">
         <is>
           <t>원료형태/20</t>
         </is>
       </c>
-      <c r="U1" s="5" t="inlineStr">
+      <c r="V1" s="5" t="inlineStr">
         <is>
           <t>투명성/15</t>
         </is>
       </c>
-      <c r="V1" s="5" t="inlineStr">
+      <c r="W1" s="5" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="W1" s="5" t="inlineStr">
+      <c r="X1" s="5" t="inlineStr">
         <is>
           <t>안전상한</t>
         </is>
       </c>
-      <c r="X1" s="5" t="inlineStr">
+      <c r="Y1" s="5" t="inlineStr">
         <is>
           <t>최종점수</t>
         </is>
       </c>
-      <c r="Y1" s="5" t="inlineStr">
+      <c r="Z1" s="5" t="inlineStr">
         <is>
           <t>잠정순위</t>
         </is>
       </c>
-      <c r="Z1" s="5" t="inlineStr">
+      <c r="AA1" s="5" t="inlineStr">
         <is>
           <t>정보검증</t>
         </is>
       </c>
-      <c r="AA1" s="5" t="inlineStr">
+      <c r="AB1" s="5" t="inlineStr">
         <is>
           <t>적합성</t>
         </is>
       </c>
-      <c r="AB1" s="5" t="inlineStr">
+      <c r="AC1" s="5" t="inlineStr">
         <is>
           <t>데이터충실도</t>
         </is>
       </c>
-      <c r="AC1" s="5" t="inlineStr">
+      <c r="AD1" s="5" t="inlineStr">
         <is>
           <t>출처·비고</t>
         </is>
@@ -1209,53 +1215,58 @@
         <f>IF(AND(J2="취약",I2&lt;&gt;"있음",OR(M2="없음",M2="미상")),"Y","N")</f>
         <v/>
       </c>
-      <c r="R2" s="8">
+      <c r="R2" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S2" s="8">
         <f>IF(NOT(ISNUMBER(D2)),0,IF(D2&gt;=300,20,IF(D2&gt;=200,15,IF(D2&gt;=100,10,5))))+IF(NOT(ISNUMBER(E2)),0,IF(E2&gt;=60,10,IF(E2&gt;=40,6,3)))+IFERROR(VLOOKUP(F2,기준!$B$4:$C$7,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="S2" s="8">
+      <c r="T2" s="8">
         <f>IFERROR(VLOOKUP(I2,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J2,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K2,기준!$B$34:$C$40,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="T2" s="8">
+      <c r="U2" s="8">
         <f>IFERROR(VLOOKUP(G2,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H2,기준!$B$16:$C$20,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="U2" s="8">
+      <c r="V2" s="8">
         <f>IFERROR(VLOOKUP(L2,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M2,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N2,기준!$B$54:$C$57,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="V2" s="8">
-        <f>SUM(R2:U2)</f>
-        <v/>
-      </c>
       <c r="W2" s="8">
-        <f>MIN(IF(O2="Y",20,100),IF(P2="Y",40,100),IF(Q2="Y",50,100))</f>
+        <f>SUM(S2:V2)</f>
         <v/>
       </c>
       <c r="X2" s="8">
-        <f>MIN(V2,W2)</f>
+        <f>MIN(IF(O2="Y",20,100),IF(P2="Y",40,100),IF(Q2="Y",50,100),IF(R2="Y",40,100))</f>
         <v/>
       </c>
       <c r="Y2" s="8">
-        <f>RANK(X2,$X$2:$X$34,0)</f>
-        <v/>
-      </c>
-      <c r="Z2" s="7" t="inlineStr">
+        <f>MIN(W2,X2)</f>
+        <v/>
+      </c>
+      <c r="Z2" s="8">
+        <f>RANK(Y2,$Y$2:$Y$34,0)</f>
+        <v/>
+      </c>
+      <c r="AA2" s="7" t="inlineStr">
         <is>
           <t>공개·검증</t>
         </is>
       </c>
-      <c r="AA2" s="7" t="inlineStr">
+      <c r="AB2" s="7" t="inlineStr">
         <is>
           <t>관절·신장(EPA우세)</t>
         </is>
       </c>
-      <c r="AB2" s="6">
+      <c r="AC2" s="6">
         <f>(IF(ISNUMBER(D2),1,0)+IF(ISNUMBER(E2),1,0)+IF(F2&lt;&gt;"미상",1,0)+IF(G2&lt;&gt;"미상",1,0)+IF(H2&lt;&gt;"미상",1,0)+IF(I2&lt;&gt;"미상",1,0)+IF(J2&lt;&gt;"미상",1,0)+IF(K2&lt;&gt;"미상",1,0)+IF(L2&lt;&gt;"미상",1,0)+IF(M2&lt;&gt;"미상",1,0)+IF(N2&lt;&gt;"미상",1,0))&amp;"/11"</f>
         <v/>
       </c>
-      <c r="AC2" s="6" t="inlineStr">
+      <c r="AD2" s="6" t="inlineStr">
         <is>
           <t>1캡슐 EPA120+DHA80=200mg·순도80%·rTG·멸치/정어리·d-토코페롤·PVDC블리스터·IFOS5★완제품(TOTOX10.32·산가0.17·중금속통과)·KD파마/로빈슨파마 (상세페이지 실측)</t>
         </is>
@@ -1339,53 +1350,58 @@
         <f>IF(AND(J3="취약",I3&lt;&gt;"있음",OR(M3="없음",M3="미상")),"Y","N")</f>
         <v/>
       </c>
-      <c r="R3" s="8">
+      <c r="R3" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S3" s="8">
         <f>IF(NOT(ISNUMBER(D3)),0,IF(D3&gt;=300,20,IF(D3&gt;=200,15,IF(D3&gt;=100,10,5))))+IF(NOT(ISNUMBER(E3)),0,IF(E3&gt;=60,10,IF(E3&gt;=40,6,3)))+IFERROR(VLOOKUP(F3,기준!$B$4:$C$7,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="S3" s="8">
+      <c r="T3" s="8">
         <f>IFERROR(VLOOKUP(I3,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J3,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K3,기준!$B$34:$C$40,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="T3" s="8">
+      <c r="U3" s="8">
         <f>IFERROR(VLOOKUP(G3,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H3,기준!$B$16:$C$20,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="U3" s="8">
+      <c r="V3" s="8">
         <f>IFERROR(VLOOKUP(L3,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M3,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N3,기준!$B$54:$C$57,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="V3" s="8">
-        <f>SUM(R3:U3)</f>
-        <v/>
-      </c>
       <c r="W3" s="8">
-        <f>MIN(IF(O3="Y",20,100),IF(P3="Y",40,100),IF(Q3="Y",50,100))</f>
+        <f>SUM(S3:V3)</f>
         <v/>
       </c>
       <c r="X3" s="8">
-        <f>MIN(V3,W3)</f>
+        <f>MIN(IF(O3="Y",20,100),IF(P3="Y",40,100),IF(Q3="Y",50,100),IF(R3="Y",40,100))</f>
         <v/>
       </c>
       <c r="Y3" s="8">
-        <f>RANK(X3,$X$2:$X$34,0)</f>
-        <v/>
-      </c>
-      <c r="Z3" s="7" t="inlineStr">
+        <f>MIN(W3,X3)</f>
+        <v/>
+      </c>
+      <c r="Z3" s="8">
+        <f>RANK(Y3,$Y$2:$Y$34,0)</f>
+        <v/>
+      </c>
+      <c r="AA3" s="7" t="inlineStr">
         <is>
           <t>공개·검증</t>
         </is>
       </c>
-      <c r="AA3" s="7" t="inlineStr">
+      <c r="AB3" s="7" t="inlineStr">
         <is>
           <t>미정</t>
         </is>
       </c>
-      <c r="AB3" s="6">
+      <c r="AC3" s="6">
         <f>(IF(ISNUMBER(D3),1,0)+IF(ISNUMBER(E3),1,0)+IF(F3&lt;&gt;"미상",1,0)+IF(G3&lt;&gt;"미상",1,0)+IF(H3&lt;&gt;"미상",1,0)+IF(I3&lt;&gt;"미상",1,0)+IF(J3&lt;&gt;"미상",1,0)+IF(K3&lt;&gt;"미상",1,0)+IF(L3&lt;&gt;"미상",1,0)+IF(M3&lt;&gt;"미상",1,0)+IF(N3&lt;&gt;"미상",1,0))&amp;"/11"</f>
         <v/>
       </c>
-      <c r="AC3" s="6" t="inlineStr">
+      <c r="AD3" s="6" t="inlineStr">
         <is>
           <t>IFOS 5-star·Solutex·순도80%+ (모굿인)</t>
         </is>
@@ -1471,53 +1487,58 @@
         <f>IF(AND(J4="취약",I4&lt;&gt;"있음",OR(M4="없음",M4="미상")),"Y","N")</f>
         <v/>
       </c>
-      <c r="R4" s="8">
+      <c r="R4" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S4" s="8">
         <f>IF(NOT(ISNUMBER(D4)),0,IF(D4&gt;=300,20,IF(D4&gt;=200,15,IF(D4&gt;=100,10,5))))+IF(NOT(ISNUMBER(E4)),0,IF(E4&gt;=60,10,IF(E4&gt;=40,6,3)))+IFERROR(VLOOKUP(F4,기준!$B$4:$C$7,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="S4" s="8">
+      <c r="T4" s="8">
         <f>IFERROR(VLOOKUP(I4,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J4,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K4,기준!$B$34:$C$40,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="T4" s="8">
+      <c r="U4" s="8">
         <f>IFERROR(VLOOKUP(G4,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H4,기준!$B$16:$C$20,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="U4" s="8">
+      <c r="V4" s="8">
         <f>IFERROR(VLOOKUP(L4,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M4,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N4,기준!$B$54:$C$57,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="V4" s="8">
-        <f>SUM(R4:U4)</f>
-        <v/>
-      </c>
       <c r="W4" s="8">
-        <f>MIN(IF(O4="Y",20,100),IF(P4="Y",40,100),IF(Q4="Y",50,100))</f>
+        <f>SUM(S4:V4)</f>
         <v/>
       </c>
       <c r="X4" s="8">
-        <f>MIN(V4,W4)</f>
+        <f>MIN(IF(O4="Y",20,100),IF(P4="Y",40,100),IF(Q4="Y",50,100),IF(R4="Y",40,100))</f>
         <v/>
       </c>
       <c r="Y4" s="8">
-        <f>RANK(X4,$X$2:$X$34,0)</f>
-        <v/>
-      </c>
-      <c r="Z4" s="7" t="inlineStr">
+        <f>MIN(W4,X4)</f>
+        <v/>
+      </c>
+      <c r="Z4" s="8">
+        <f>RANK(Y4,$Y$2:$Y$34,0)</f>
+        <v/>
+      </c>
+      <c r="AA4" s="7" t="inlineStr">
         <is>
           <t>공개·검증</t>
         </is>
       </c>
-      <c r="AA4" s="7" t="inlineStr">
+      <c r="AB4" s="7" t="inlineStr">
         <is>
           <t>일반유지·피부(아스타잔틴)</t>
         </is>
       </c>
-      <c r="AB4" s="6">
+      <c r="AC4" s="6">
         <f>(IF(ISNUMBER(D4),1,0)+IF(ISNUMBER(E4),1,0)+IF(F4&lt;&gt;"미상",1,0)+IF(G4&lt;&gt;"미상",1,0)+IF(H4&lt;&gt;"미상",1,0)+IF(I4&lt;&gt;"미상",1,0)+IF(J4&lt;&gt;"미상",1,0)+IF(K4&lt;&gt;"미상",1,0)+IF(L4&lt;&gt;"미상",1,0)+IF(M4&lt;&gt;"미상",1,0)+IF(N4&lt;&gt;"미상",1,0))&amp;"/11"</f>
         <v/>
       </c>
-      <c r="AC4" s="6" t="inlineStr">
+      <c r="AD4" s="6" t="inlineStr">
         <is>
           <t>1캡슐 EPA66+DHA44=110mg(rTG오일137.6mg·순도80%)·멸치류 소형어·아스타잔틴5mg+d-토코페롤·블리스터개별포장·원료+완제품IFOS5★(TOTOX16.49·산가0.27·중금속통과)·Solutex/Viva제조·고양이1알 (상세페이지 실측)</t>
         </is>
@@ -1603,53 +1624,58 @@
         <f>IF(AND(J5="취약",I5&lt;&gt;"있음",OR(M5="없음",M5="미상")),"Y","N")</f>
         <v/>
       </c>
-      <c r="R5" s="8">
+      <c r="R5" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S5" s="8">
         <f>IF(NOT(ISNUMBER(D5)),0,IF(D5&gt;=300,20,IF(D5&gt;=200,15,IF(D5&gt;=100,10,5))))+IF(NOT(ISNUMBER(E5)),0,IF(E5&gt;=60,10,IF(E5&gt;=40,6,3)))+IFERROR(VLOOKUP(F5,기준!$B$4:$C$7,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="S5" s="8">
+      <c r="T5" s="8">
         <f>IFERROR(VLOOKUP(I5,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J5,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K5,기준!$B$34:$C$40,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="T5" s="8">
+      <c r="U5" s="8">
         <f>IFERROR(VLOOKUP(G5,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H5,기준!$B$16:$C$20,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="U5" s="8">
+      <c r="V5" s="8">
         <f>IFERROR(VLOOKUP(L5,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M5,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N5,기준!$B$54:$C$57,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="V5" s="8">
-        <f>SUM(R5:U5)</f>
-        <v/>
-      </c>
       <c r="W5" s="8">
-        <f>MIN(IF(O5="Y",20,100),IF(P5="Y",40,100),IF(Q5="Y",50,100))</f>
+        <f>SUM(S5:V5)</f>
         <v/>
       </c>
       <c r="X5" s="8">
-        <f>MIN(V5,W5)</f>
+        <f>MIN(IF(O5="Y",20,100),IF(P5="Y",40,100),IF(Q5="Y",50,100),IF(R5="Y",40,100))</f>
         <v/>
       </c>
       <c r="Y5" s="8">
-        <f>RANK(X5,$X$2:$X$34,0)</f>
-        <v/>
-      </c>
-      <c r="Z5" s="7" t="inlineStr">
+        <f>MIN(W5,X5)</f>
+        <v/>
+      </c>
+      <c r="Z5" s="8">
+        <f>RANK(Y5,$Y$2:$Y$34,0)</f>
+        <v/>
+      </c>
+      <c r="AA5" s="7" t="inlineStr">
         <is>
           <t>공개·검증</t>
         </is>
       </c>
-      <c r="AA5" s="7" t="inlineStr">
+      <c r="AB5" s="7" t="inlineStr">
         <is>
           <t>일반유지(EPA 2:1)</t>
         </is>
       </c>
-      <c r="AB5" s="6">
+      <c r="AC5" s="6">
         <f>(IF(ISNUMBER(D5),1,0)+IF(ISNUMBER(E5),1,0)+IF(F5&lt;&gt;"미상",1,0)+IF(G5&lt;&gt;"미상",1,0)+IF(H5&lt;&gt;"미상",1,0)+IF(I5&lt;&gt;"미상",1,0)+IF(J5&lt;&gt;"미상",1,0)+IF(K5&lt;&gt;"미상",1,0)+IF(L5&lt;&gt;"미상",1,0)+IF(M5&lt;&gt;"미상",1,0)+IF(N5&lt;&gt;"미상",1,0))&amp;"/11"</f>
         <v/>
       </c>
-      <c r="AC5" s="6" t="inlineStr">
+      <c r="AD5" s="6" t="inlineStr">
         <is>
           <t>1캡슐 EPA73.3+DHA36.7=110mg(rTG오일146.67mg·순도75%)·멸치류 소형어·d-토코페롤5.4mg·90캡슐 병포장·원료+완제품IFOS5★(TOTOX16.48·산가0.11·중금속통과)·Solutex Omegatex·고양이1알 (상세페이지 실측)</t>
         </is>
@@ -1735,53 +1761,58 @@
         <f>IF(AND(J6="취약",I6&lt;&gt;"있음",OR(M6="없음",M6="미상")),"Y","N")</f>
         <v/>
       </c>
-      <c r="R6" s="8">
+      <c r="R6" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S6" s="8">
         <f>IF(NOT(ISNUMBER(D6)),0,IF(D6&gt;=300,20,IF(D6&gt;=200,15,IF(D6&gt;=100,10,5))))+IF(NOT(ISNUMBER(E6)),0,IF(E6&gt;=60,10,IF(E6&gt;=40,6,3)))+IFERROR(VLOOKUP(F6,기준!$B$4:$C$7,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="S6" s="8">
+      <c r="T6" s="8">
         <f>IFERROR(VLOOKUP(I6,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J6,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K6,기준!$B$34:$C$40,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="T6" s="8">
+      <c r="U6" s="8">
         <f>IFERROR(VLOOKUP(G6,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H6,기준!$B$16:$C$20,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="U6" s="8">
+      <c r="V6" s="8">
         <f>IFERROR(VLOOKUP(L6,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M6,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N6,기준!$B$54:$C$57,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="V6" s="8">
-        <f>SUM(R6:U6)</f>
-        <v/>
-      </c>
       <c r="W6" s="8">
-        <f>MIN(IF(O6="Y",20,100),IF(P6="Y",40,100),IF(Q6="Y",50,100))</f>
+        <f>SUM(S6:V6)</f>
         <v/>
       </c>
       <c r="X6" s="8">
-        <f>MIN(V6,W6)</f>
+        <f>MIN(IF(O6="Y",20,100),IF(P6="Y",40,100),IF(Q6="Y",50,100),IF(R6="Y",40,100))</f>
         <v/>
       </c>
       <c r="Y6" s="8">
-        <f>RANK(X6,$X$2:$X$34,0)</f>
-        <v/>
-      </c>
-      <c r="Z6" s="7" t="inlineStr">
+        <f>MIN(W6,X6)</f>
+        <v/>
+      </c>
+      <c r="Z6" s="8">
+        <f>RANK(Y6,$Y$2:$Y$34,0)</f>
+        <v/>
+      </c>
+      <c r="AA6" s="7" t="inlineStr">
         <is>
           <t>공개·검증</t>
         </is>
       </c>
-      <c r="AA6" s="7" t="inlineStr">
+      <c r="AB6" s="7" t="inlineStr">
         <is>
           <t>관절·신장(EPA우세)</t>
         </is>
       </c>
-      <c r="AB6" s="6">
+      <c r="AC6" s="6">
         <f>(IF(ISNUMBER(D6),1,0)+IF(ISNUMBER(E6),1,0)+IF(F6&lt;&gt;"미상",1,0)+IF(G6&lt;&gt;"미상",1,0)+IF(H6&lt;&gt;"미상",1,0)+IF(I6&lt;&gt;"미상",1,0)+IF(J6&lt;&gt;"미상",1,0)+IF(K6&lt;&gt;"미상",1,0)+IF(L6&lt;&gt;"미상",1,0)+IF(M6&lt;&gt;"미상",1,0)+IF(N6&lt;&gt;"미상",1,0))&amp;"/11"</f>
         <v/>
       </c>
-      <c r="AC6" s="6" t="inlineStr">
+      <c r="AD6" s="6" t="inlineStr">
         <is>
           <t>1캡슐 EPA192+DHA128=320mg(정제어유400mg·순도80%)·rTG·멸치/정어리/고등어·d-토코페롤·PVDC개별포장·IFOS5★완제품+RTCP(TOTOX13.07·산가0.20·중금속통과)·KD파마480320TG (상세페이지 실측)</t>
         </is>
@@ -1867,53 +1898,58 @@
         <f>IF(AND(J7="취약",I7&lt;&gt;"있음",OR(M7="없음",M7="미상")),"Y","N")</f>
         <v/>
       </c>
-      <c r="R7" s="8">
+      <c r="R7" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S7" s="8">
         <f>IF(NOT(ISNUMBER(D7)),0,IF(D7&gt;=300,20,IF(D7&gt;=200,15,IF(D7&gt;=100,10,5))))+IF(NOT(ISNUMBER(E7)),0,IF(E7&gt;=60,10,IF(E7&gt;=40,6,3)))+IFERROR(VLOOKUP(F7,기준!$B$4:$C$7,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="S7" s="8">
+      <c r="T7" s="8">
         <f>IFERROR(VLOOKUP(I7,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J7,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K7,기준!$B$34:$C$40,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="T7" s="8">
+      <c r="U7" s="8">
         <f>IFERROR(VLOOKUP(G7,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H7,기준!$B$16:$C$20,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="U7" s="8">
+      <c r="V7" s="8">
         <f>IFERROR(VLOOKUP(L7,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M7,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N7,기준!$B$54:$C$57,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="V7" s="8">
-        <f>SUM(R7:U7)</f>
-        <v/>
-      </c>
       <c r="W7" s="8">
-        <f>MIN(IF(O7="Y",20,100),IF(P7="Y",40,100),IF(Q7="Y",50,100))</f>
+        <f>SUM(S7:V7)</f>
         <v/>
       </c>
       <c r="X7" s="8">
-        <f>MIN(V7,W7)</f>
+        <f>MIN(IF(O7="Y",20,100),IF(P7="Y",40,100),IF(Q7="Y",50,100),IF(R7="Y",40,100))</f>
         <v/>
       </c>
       <c r="Y7" s="8">
-        <f>RANK(X7,$X$2:$X$34,0)</f>
-        <v/>
-      </c>
-      <c r="Z7" s="7" t="inlineStr">
+        <f>MIN(W7,X7)</f>
+        <v/>
+      </c>
+      <c r="Z7" s="8">
+        <f>RANK(Y7,$Y$2:$Y$34,0)</f>
+        <v/>
+      </c>
+      <c r="AA7" s="7" t="inlineStr">
         <is>
           <t>공개·검증</t>
         </is>
       </c>
-      <c r="AA7" s="7" t="inlineStr">
+      <c r="AB7" s="7" t="inlineStr">
         <is>
           <t>미정</t>
         </is>
       </c>
-      <c r="AB7" s="6">
+      <c r="AC7" s="6">
         <f>(IF(ISNUMBER(D7),1,0)+IF(ISNUMBER(E7),1,0)+IF(F7&lt;&gt;"미상",1,0)+IF(G7&lt;&gt;"미상",1,0)+IF(H7&lt;&gt;"미상",1,0)+IF(I7&lt;&gt;"미상",1,0)+IF(J7&lt;&gt;"미상",1,0)+IF(K7&lt;&gt;"미상",1,0)+IF(L7&lt;&gt;"미상",1,0)+IF(M7&lt;&gt;"미상",1,0)+IF(N7&lt;&gt;"미상",1,0))&amp;"/11"</f>
         <v/>
       </c>
-      <c r="AC7" s="6" t="inlineStr">
+      <c r="AD7" s="6" t="inlineStr">
         <is>
           <t>1소프트젤 EPA155+DHA100=255mg·멸치/정어리/고등어/청어·TG·토코페롤·배치별 시험공개 (onlynaturalpet/petco)</t>
         </is>
@@ -1995,53 +2031,58 @@
         <f>IF(AND(J8="취약",I8&lt;&gt;"있음",OR(M8="없음",M8="미상")),"Y","N")</f>
         <v/>
       </c>
-      <c r="R8" s="8">
+      <c r="R8" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S8" s="8">
         <f>IF(NOT(ISNUMBER(D8)),0,IF(D8&gt;=300,20,IF(D8&gt;=200,15,IF(D8&gt;=100,10,5))))+IF(NOT(ISNUMBER(E8)),0,IF(E8&gt;=60,10,IF(E8&gt;=40,6,3)))+IFERROR(VLOOKUP(F8,기준!$B$4:$C$7,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="S8" s="8">
+      <c r="T8" s="8">
         <f>IFERROR(VLOOKUP(I8,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J8,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K8,기준!$B$34:$C$40,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="T8" s="8">
+      <c r="U8" s="8">
         <f>IFERROR(VLOOKUP(G8,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H8,기준!$B$16:$C$20,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="U8" s="8">
+      <c r="V8" s="8">
         <f>IFERROR(VLOOKUP(L8,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M8,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N8,기준!$B$54:$C$57,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="V8" s="8">
-        <f>SUM(R8:U8)</f>
-        <v/>
-      </c>
       <c r="W8" s="8">
-        <f>MIN(IF(O8="Y",20,100),IF(P8="Y",40,100),IF(Q8="Y",50,100))</f>
+        <f>SUM(S8:V8)</f>
         <v/>
       </c>
       <c r="X8" s="8">
-        <f>MIN(V8,W8)</f>
+        <f>MIN(IF(O8="Y",20,100),IF(P8="Y",40,100),IF(Q8="Y",50,100),IF(R8="Y",40,100))</f>
         <v/>
       </c>
       <c r="Y8" s="8">
-        <f>RANK(X8,$X$2:$X$34,0)</f>
-        <v/>
-      </c>
-      <c r="Z8" s="7" t="inlineStr">
-        <is>
-          <t>미상</t>
-        </is>
+        <f>MIN(W8,X8)</f>
+        <v/>
+      </c>
+      <c r="Z8" s="8">
+        <f>RANK(Y8,$Y$2:$Y$34,0)</f>
+        <v/>
       </c>
       <c r="AA8" s="7" t="inlineStr">
         <is>
+          <t>미상</t>
+        </is>
+      </c>
+      <c r="AB8" s="7" t="inlineStr">
+        <is>
           <t>미정</t>
         </is>
       </c>
-      <c r="AB8" s="6">
+      <c r="AC8" s="6">
         <f>(IF(ISNUMBER(D8),1,0)+IF(ISNUMBER(E8),1,0)+IF(F8&lt;&gt;"미상",1,0)+IF(G8&lt;&gt;"미상",1,0)+IF(H8&lt;&gt;"미상",1,0)+IF(I8&lt;&gt;"미상",1,0)+IF(J8&lt;&gt;"미상",1,0)+IF(K8&lt;&gt;"미상",1,0)+IF(L8&lt;&gt;"미상",1,0)+IF(M8&lt;&gt;"미상",1,0)+IF(N8&lt;&gt;"미상",1,0))&amp;"/11"</f>
         <v/>
       </c>
-      <c r="AC8" s="6" t="inlineStr">
+      <c r="AD8" s="6" t="inlineStr">
         <is>
           <t>씹는 츄·스펙 수집중</t>
         </is>
@@ -2123,53 +2164,58 @@
         <f>IF(AND(J9="취약",I9&lt;&gt;"있음",OR(M9="없음",M9="미상")),"Y","N")</f>
         <v/>
       </c>
-      <c r="R9" s="8">
+      <c r="R9" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S9" s="8">
         <f>IF(NOT(ISNUMBER(D9)),0,IF(D9&gt;=300,20,IF(D9&gt;=200,15,IF(D9&gt;=100,10,5))))+IF(NOT(ISNUMBER(E9)),0,IF(E9&gt;=60,10,IF(E9&gt;=40,6,3)))+IFERROR(VLOOKUP(F9,기준!$B$4:$C$7,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="S9" s="8">
+      <c r="T9" s="8">
         <f>IFERROR(VLOOKUP(I9,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J9,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K9,기준!$B$34:$C$40,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="T9" s="8">
+      <c r="U9" s="8">
         <f>IFERROR(VLOOKUP(G9,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H9,기준!$B$16:$C$20,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="U9" s="8">
+      <c r="V9" s="8">
         <f>IFERROR(VLOOKUP(L9,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M9,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N9,기준!$B$54:$C$57,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="V9" s="8">
-        <f>SUM(R9:U9)</f>
-        <v/>
-      </c>
       <c r="W9" s="8">
-        <f>MIN(IF(O9="Y",20,100),IF(P9="Y",40,100),IF(Q9="Y",50,100))</f>
+        <f>SUM(S9:V9)</f>
         <v/>
       </c>
       <c r="X9" s="8">
-        <f>MIN(V9,W9)</f>
+        <f>MIN(IF(O9="Y",20,100),IF(P9="Y",40,100),IF(Q9="Y",50,100),IF(R9="Y",40,100))</f>
         <v/>
       </c>
       <c r="Y9" s="8">
-        <f>RANK(X9,$X$2:$X$34,0)</f>
-        <v/>
-      </c>
-      <c r="Z9" s="7" t="inlineStr">
-        <is>
-          <t>미상</t>
-        </is>
+        <f>MIN(W9,X9)</f>
+        <v/>
+      </c>
+      <c r="Z9" s="8">
+        <f>RANK(Y9,$Y$2:$Y$34,0)</f>
+        <v/>
       </c>
       <c r="AA9" s="7" t="inlineStr">
         <is>
+          <t>미상</t>
+        </is>
+      </c>
+      <c r="AB9" s="7" t="inlineStr">
+        <is>
           <t>미정</t>
         </is>
       </c>
-      <c r="AB9" s="6">
+      <c r="AC9" s="6">
         <f>(IF(ISNUMBER(D9),1,0)+IF(ISNUMBER(E9),1,0)+IF(F9&lt;&gt;"미상",1,0)+IF(G9&lt;&gt;"미상",1,0)+IF(H9&lt;&gt;"미상",1,0)+IF(I9&lt;&gt;"미상",1,0)+IF(J9&lt;&gt;"미상",1,0)+IF(K9&lt;&gt;"미상",1,0)+IF(L9&lt;&gt;"미상",1,0)+IF(M9&lt;&gt;"미상",1,0)+IF(N9&lt;&gt;"미상",1,0))&amp;"/11"</f>
         <v/>
       </c>
-      <c r="AC9" s="6" t="inlineStr">
+      <c r="AD9" s="6" t="inlineStr">
         <is>
           <t>표시 500mg(오일 추정)·EPA+DHA 미상</t>
         </is>
@@ -2251,53 +2297,58 @@
         <f>IF(AND(J10="취약",I10&lt;&gt;"있음",OR(M10="없음",M10="미상")),"Y","N")</f>
         <v/>
       </c>
-      <c r="R10" s="8">
+      <c r="R10" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S10" s="8">
         <f>IF(NOT(ISNUMBER(D10)),0,IF(D10&gt;=300,20,IF(D10&gt;=200,15,IF(D10&gt;=100,10,5))))+IF(NOT(ISNUMBER(E10)),0,IF(E10&gt;=60,10,IF(E10&gt;=40,6,3)))+IFERROR(VLOOKUP(F10,기준!$B$4:$C$7,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="S10" s="8">
+      <c r="T10" s="8">
         <f>IFERROR(VLOOKUP(I10,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J10,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K10,기준!$B$34:$C$40,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="T10" s="8">
+      <c r="U10" s="8">
         <f>IFERROR(VLOOKUP(G10,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H10,기준!$B$16:$C$20,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="U10" s="8">
+      <c r="V10" s="8">
         <f>IFERROR(VLOOKUP(L10,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M10,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N10,기준!$B$54:$C$57,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="V10" s="8">
-        <f>SUM(R10:U10)</f>
-        <v/>
-      </c>
       <c r="W10" s="8">
-        <f>MIN(IF(O10="Y",20,100),IF(P10="Y",40,100),IF(Q10="Y",50,100))</f>
+        <f>SUM(S10:V10)</f>
         <v/>
       </c>
       <c r="X10" s="8">
-        <f>MIN(V10,W10)</f>
+        <f>MIN(IF(O10="Y",20,100),IF(P10="Y",40,100),IF(Q10="Y",50,100),IF(R10="Y",40,100))</f>
         <v/>
       </c>
       <c r="Y10" s="8">
-        <f>RANK(X10,$X$2:$X$34,0)</f>
-        <v/>
-      </c>
-      <c r="Z10" s="7" t="inlineStr">
-        <is>
-          <t>미상</t>
-        </is>
+        <f>MIN(W10,X10)</f>
+        <v/>
+      </c>
+      <c r="Z10" s="8">
+        <f>RANK(Y10,$Y$2:$Y$34,0)</f>
+        <v/>
       </c>
       <c r="AA10" s="7" t="inlineStr">
         <is>
+          <t>미상</t>
+        </is>
+      </c>
+      <c r="AB10" s="7" t="inlineStr">
+        <is>
           <t>미정</t>
         </is>
       </c>
-      <c r="AB10" s="6">
+      <c r="AC10" s="6">
         <f>(IF(ISNUMBER(D10),1,0)+IF(ISNUMBER(E10),1,0)+IF(F10&lt;&gt;"미상",1,0)+IF(G10&lt;&gt;"미상",1,0)+IF(H10&lt;&gt;"미상",1,0)+IF(I10&lt;&gt;"미상",1,0)+IF(J10&lt;&gt;"미상",1,0)+IF(K10&lt;&gt;"미상",1,0)+IF(L10&lt;&gt;"미상",1,0)+IF(M10&lt;&gt;"미상",1,0)+IF(N10&lt;&gt;"미상",1,0))&amp;"/11"</f>
         <v/>
       </c>
-      <c r="AC10" s="6" t="inlineStr">
+      <c r="AD10" s="6" t="inlineStr">
         <is>
           <t>스펙 수집중</t>
         </is>
@@ -2379,53 +2430,58 @@
         <f>IF(AND(J11="취약",I11&lt;&gt;"있음",OR(M11="없음",M11="미상")),"Y","N")</f>
         <v/>
       </c>
-      <c r="R11" s="8">
+      <c r="R11" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S11" s="8">
         <f>IF(NOT(ISNUMBER(D11)),0,IF(D11&gt;=300,20,IF(D11&gt;=200,15,IF(D11&gt;=100,10,5))))+IF(NOT(ISNUMBER(E11)),0,IF(E11&gt;=60,10,IF(E11&gt;=40,6,3)))+IFERROR(VLOOKUP(F11,기준!$B$4:$C$7,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="S11" s="8">
+      <c r="T11" s="8">
         <f>IFERROR(VLOOKUP(I11,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J11,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K11,기준!$B$34:$C$40,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="T11" s="8">
+      <c r="U11" s="8">
         <f>IFERROR(VLOOKUP(G11,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H11,기준!$B$16:$C$20,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="U11" s="8">
+      <c r="V11" s="8">
         <f>IFERROR(VLOOKUP(L11,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M11,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N11,기준!$B$54:$C$57,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="V11" s="8">
-        <f>SUM(R11:U11)</f>
-        <v/>
-      </c>
       <c r="W11" s="8">
-        <f>MIN(IF(O11="Y",20,100),IF(P11="Y",40,100),IF(Q11="Y",50,100))</f>
+        <f>SUM(S11:V11)</f>
         <v/>
       </c>
       <c r="X11" s="8">
-        <f>MIN(V11,W11)</f>
+        <f>MIN(IF(O11="Y",20,100),IF(P11="Y",40,100),IF(Q11="Y",50,100),IF(R11="Y",40,100))</f>
         <v/>
       </c>
       <c r="Y11" s="8">
-        <f>RANK(X11,$X$2:$X$34,0)</f>
-        <v/>
-      </c>
-      <c r="Z11" s="7" t="inlineStr">
-        <is>
-          <t>미상</t>
-        </is>
+        <f>MIN(W11,X11)</f>
+        <v/>
+      </c>
+      <c r="Z11" s="8">
+        <f>RANK(Y11,$Y$2:$Y$34,0)</f>
+        <v/>
       </c>
       <c r="AA11" s="7" t="inlineStr">
         <is>
+          <t>미상</t>
+        </is>
+      </c>
+      <c r="AB11" s="7" t="inlineStr">
+        <is>
           <t>미정</t>
         </is>
       </c>
-      <c r="AB11" s="6">
+      <c r="AC11" s="6">
         <f>(IF(ISNUMBER(D11),1,0)+IF(ISNUMBER(E11),1,0)+IF(F11&lt;&gt;"미상",1,0)+IF(G11&lt;&gt;"미상",1,0)+IF(H11&lt;&gt;"미상",1,0)+IF(I11&lt;&gt;"미상",1,0)+IF(J11&lt;&gt;"미상",1,0)+IF(K11&lt;&gt;"미상",1,0)+IF(L11&lt;&gt;"미상",1,0)+IF(M11&lt;&gt;"미상",1,0)+IF(N11&lt;&gt;"미상",1,0))&amp;"/11"</f>
         <v/>
       </c>
-      <c r="AC11" s="6" t="inlineStr">
+      <c r="AD11" s="6" t="inlineStr">
         <is>
           <t>스펙 수집중</t>
         </is>
@@ -2507,53 +2563,58 @@
         <f>IF(AND(J12="취약",I12&lt;&gt;"있음",OR(M12="없음",M12="미상")),"Y","N")</f>
         <v/>
       </c>
-      <c r="R12" s="8">
+      <c r="R12" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S12" s="8">
         <f>IF(NOT(ISNUMBER(D12)),0,IF(D12&gt;=300,20,IF(D12&gt;=200,15,IF(D12&gt;=100,10,5))))+IF(NOT(ISNUMBER(E12)),0,IF(E12&gt;=60,10,IF(E12&gt;=40,6,3)))+IFERROR(VLOOKUP(F12,기준!$B$4:$C$7,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="S12" s="8">
+      <c r="T12" s="8">
         <f>IFERROR(VLOOKUP(I12,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J12,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K12,기준!$B$34:$C$40,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="T12" s="8">
+      <c r="U12" s="8">
         <f>IFERROR(VLOOKUP(G12,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H12,기준!$B$16:$C$20,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="U12" s="8">
+      <c r="V12" s="8">
         <f>IFERROR(VLOOKUP(L12,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M12,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N12,기준!$B$54:$C$57,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="V12" s="8">
-        <f>SUM(R12:U12)</f>
-        <v/>
-      </c>
       <c r="W12" s="8">
-        <f>MIN(IF(O12="Y",20,100),IF(P12="Y",40,100),IF(Q12="Y",50,100))</f>
+        <f>SUM(S12:V12)</f>
         <v/>
       </c>
       <c r="X12" s="8">
-        <f>MIN(V12,W12)</f>
+        <f>MIN(IF(O12="Y",20,100),IF(P12="Y",40,100),IF(Q12="Y",50,100),IF(R12="Y",40,100))</f>
         <v/>
       </c>
       <c r="Y12" s="8">
-        <f>RANK(X12,$X$2:$X$34,0)</f>
-        <v/>
-      </c>
-      <c r="Z12" s="7" t="inlineStr">
-        <is>
-          <t>미상</t>
-        </is>
+        <f>MIN(W12,X12)</f>
+        <v/>
+      </c>
+      <c r="Z12" s="8">
+        <f>RANK(Y12,$Y$2:$Y$34,0)</f>
+        <v/>
       </c>
       <c r="AA12" s="7" t="inlineStr">
         <is>
+          <t>미상</t>
+        </is>
+      </c>
+      <c r="AB12" s="7" t="inlineStr">
+        <is>
           <t>미정</t>
         </is>
       </c>
-      <c r="AB12" s="6">
+      <c r="AC12" s="6">
         <f>(IF(ISNUMBER(D12),1,0)+IF(ISNUMBER(E12),1,0)+IF(F12&lt;&gt;"미상",1,0)+IF(G12&lt;&gt;"미상",1,0)+IF(H12&lt;&gt;"미상",1,0)+IF(I12&lt;&gt;"미상",1,0)+IF(J12&lt;&gt;"미상",1,0)+IF(K12&lt;&gt;"미상",1,0)+IF(L12&lt;&gt;"미상",1,0)+IF(M12&lt;&gt;"미상",1,0)+IF(N12&lt;&gt;"미상",1,0))&amp;"/11"</f>
         <v/>
       </c>
-      <c r="AC12" s="6" t="inlineStr">
+      <c r="AD12" s="6" t="inlineStr">
         <is>
           <t>스펙 수집중</t>
         </is>
@@ -2635,53 +2696,58 @@
         <f>IF(AND(J13="취약",I13&lt;&gt;"있음",OR(M13="없음",M13="미상")),"Y","N")</f>
         <v/>
       </c>
-      <c r="R13" s="8">
+      <c r="R13" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S13" s="8">
         <f>IF(NOT(ISNUMBER(D13)),0,IF(D13&gt;=300,20,IF(D13&gt;=200,15,IF(D13&gt;=100,10,5))))+IF(NOT(ISNUMBER(E13)),0,IF(E13&gt;=60,10,IF(E13&gt;=40,6,3)))+IFERROR(VLOOKUP(F13,기준!$B$4:$C$7,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="S13" s="8">
+      <c r="T13" s="8">
         <f>IFERROR(VLOOKUP(I13,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J13,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K13,기준!$B$34:$C$40,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="T13" s="8">
+      <c r="U13" s="8">
         <f>IFERROR(VLOOKUP(G13,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H13,기준!$B$16:$C$20,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="U13" s="8">
+      <c r="V13" s="8">
         <f>IFERROR(VLOOKUP(L13,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M13,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N13,기준!$B$54:$C$57,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="V13" s="8">
-        <f>SUM(R13:U13)</f>
-        <v/>
-      </c>
       <c r="W13" s="8">
-        <f>MIN(IF(O13="Y",20,100),IF(P13="Y",40,100),IF(Q13="Y",50,100))</f>
+        <f>SUM(S13:V13)</f>
         <v/>
       </c>
       <c r="X13" s="8">
-        <f>MIN(V13,W13)</f>
+        <f>MIN(IF(O13="Y",20,100),IF(P13="Y",40,100),IF(Q13="Y",50,100),IF(R13="Y",40,100))</f>
         <v/>
       </c>
       <c r="Y13" s="8">
-        <f>RANK(X13,$X$2:$X$34,0)</f>
-        <v/>
-      </c>
-      <c r="Z13" s="7" t="inlineStr">
-        <is>
-          <t>미상</t>
-        </is>
+        <f>MIN(W13,X13)</f>
+        <v/>
+      </c>
+      <c r="Z13" s="8">
+        <f>RANK(Y13,$Y$2:$Y$34,0)</f>
+        <v/>
       </c>
       <c r="AA13" s="7" t="inlineStr">
         <is>
+          <t>미상</t>
+        </is>
+      </c>
+      <c r="AB13" s="7" t="inlineStr">
+        <is>
           <t>미정</t>
         </is>
       </c>
-      <c r="AB13" s="6">
+      <c r="AC13" s="6">
         <f>(IF(ISNUMBER(D13),1,0)+IF(ISNUMBER(E13),1,0)+IF(F13&lt;&gt;"미상",1,0)+IF(G13&lt;&gt;"미상",1,0)+IF(H13&lt;&gt;"미상",1,0)+IF(I13&lt;&gt;"미상",1,0)+IF(J13&lt;&gt;"미상",1,0)+IF(K13&lt;&gt;"미상",1,0)+IF(L13&lt;&gt;"미상",1,0)+IF(M13&lt;&gt;"미상",1,0)+IF(N13&lt;&gt;"미상",1,0))&amp;"/11"</f>
         <v/>
       </c>
-      <c r="AC13" s="6" t="inlineStr">
+      <c r="AD13" s="6" t="inlineStr">
         <is>
           <t>스펙 수집중</t>
         </is>
@@ -2763,53 +2829,58 @@
         <f>IF(AND(J14="취약",I14&lt;&gt;"있음",OR(M14="없음",M14="미상")),"Y","N")</f>
         <v/>
       </c>
-      <c r="R14" s="8">
+      <c r="R14" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S14" s="8">
         <f>IF(NOT(ISNUMBER(D14)),0,IF(D14&gt;=300,20,IF(D14&gt;=200,15,IF(D14&gt;=100,10,5))))+IF(NOT(ISNUMBER(E14)),0,IF(E14&gt;=60,10,IF(E14&gt;=40,6,3)))+IFERROR(VLOOKUP(F14,기준!$B$4:$C$7,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="S14" s="8">
+      <c r="T14" s="8">
         <f>IFERROR(VLOOKUP(I14,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J14,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K14,기준!$B$34:$C$40,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="T14" s="8">
+      <c r="U14" s="8">
         <f>IFERROR(VLOOKUP(G14,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H14,기준!$B$16:$C$20,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="U14" s="8">
+      <c r="V14" s="8">
         <f>IFERROR(VLOOKUP(L14,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M14,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N14,기준!$B$54:$C$57,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="V14" s="8">
-        <f>SUM(R14:U14)</f>
-        <v/>
-      </c>
       <c r="W14" s="8">
-        <f>MIN(IF(O14="Y",20,100),IF(P14="Y",40,100),IF(Q14="Y",50,100))</f>
+        <f>SUM(S14:V14)</f>
         <v/>
       </c>
       <c r="X14" s="8">
-        <f>MIN(V14,W14)</f>
+        <f>MIN(IF(O14="Y",20,100),IF(P14="Y",40,100),IF(Q14="Y",50,100),IF(R14="Y",40,100))</f>
         <v/>
       </c>
       <c r="Y14" s="8">
-        <f>RANK(X14,$X$2:$X$34,0)</f>
-        <v/>
-      </c>
-      <c r="Z14" s="7" t="inlineStr">
+        <f>MIN(W14,X14)</f>
+        <v/>
+      </c>
+      <c r="Z14" s="8">
+        <f>RANK(Y14,$Y$2:$Y$34,0)</f>
+        <v/>
+      </c>
+      <c r="AA14" s="7" t="inlineStr">
         <is>
           <t>라벨만</t>
         </is>
       </c>
-      <c r="AA14" s="7" t="inlineStr">
+      <c r="AB14" s="7" t="inlineStr">
         <is>
           <t>미정</t>
         </is>
       </c>
-      <c r="AB14" s="6">
+      <c r="AC14" s="6">
         <f>(IF(ISNUMBER(D14),1,0)+IF(ISNUMBER(E14),1,0)+IF(F14&lt;&gt;"미상",1,0)+IF(G14&lt;&gt;"미상",1,0)+IF(H14&lt;&gt;"미상",1,0)+IF(I14&lt;&gt;"미상",1,0)+IF(J14&lt;&gt;"미상",1,0)+IF(K14&lt;&gt;"미상",1,0)+IF(L14&lt;&gt;"미상",1,0)+IF(M14&lt;&gt;"미상",1,0)+IF(N14&lt;&gt;"미상",1,0))&amp;"/11"</f>
         <v/>
       </c>
-      <c r="AC14" s="6" t="inlineStr">
+      <c r="AD14" s="6" t="inlineStr">
         <is>
           <t>수의사 설계 스틱·초고함량 표방·수치 미상 (이퀄)</t>
         </is>
@@ -2891,53 +2962,58 @@
         <f>IF(AND(J15="취약",I15&lt;&gt;"있음",OR(M15="없음",M15="미상")),"Y","N")</f>
         <v/>
       </c>
-      <c r="R15" s="8">
+      <c r="R15" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S15" s="8">
         <f>IF(NOT(ISNUMBER(D15)),0,IF(D15&gt;=300,20,IF(D15&gt;=200,15,IF(D15&gt;=100,10,5))))+IF(NOT(ISNUMBER(E15)),0,IF(E15&gt;=60,10,IF(E15&gt;=40,6,3)))+IFERROR(VLOOKUP(F15,기준!$B$4:$C$7,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="S15" s="8">
+      <c r="T15" s="8">
         <f>IFERROR(VLOOKUP(I15,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J15,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K15,기준!$B$34:$C$40,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="T15" s="8">
+      <c r="U15" s="8">
         <f>IFERROR(VLOOKUP(G15,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H15,기준!$B$16:$C$20,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="U15" s="8">
+      <c r="V15" s="8">
         <f>IFERROR(VLOOKUP(L15,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M15,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N15,기준!$B$54:$C$57,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="V15" s="8">
-        <f>SUM(R15:U15)</f>
-        <v/>
-      </c>
       <c r="W15" s="8">
-        <f>MIN(IF(O15="Y",20,100),IF(P15="Y",40,100),IF(Q15="Y",50,100))</f>
+        <f>SUM(S15:V15)</f>
         <v/>
       </c>
       <c r="X15" s="8">
-        <f>MIN(V15,W15)</f>
+        <f>MIN(IF(O15="Y",20,100),IF(P15="Y",40,100),IF(Q15="Y",50,100),IF(R15="Y",40,100))</f>
         <v/>
       </c>
       <c r="Y15" s="8">
-        <f>RANK(X15,$X$2:$X$34,0)</f>
-        <v/>
-      </c>
-      <c r="Z15" s="7" t="inlineStr">
+        <f>MIN(W15,X15)</f>
+        <v/>
+      </c>
+      <c r="Z15" s="8">
+        <f>RANK(Y15,$Y$2:$Y$34,0)</f>
+        <v/>
+      </c>
+      <c r="AA15" s="7" t="inlineStr">
         <is>
           <t>라벨만</t>
         </is>
       </c>
-      <c r="AA15" s="7" t="inlineStr">
+      <c r="AB15" s="7" t="inlineStr">
         <is>
           <t>미정</t>
         </is>
       </c>
-      <c r="AB15" s="6">
+      <c r="AC15" s="6">
         <f>(IF(ISNUMBER(D15),1,0)+IF(ISNUMBER(E15),1,0)+IF(F15&lt;&gt;"미상",1,0)+IF(G15&lt;&gt;"미상",1,0)+IF(H15&lt;&gt;"미상",1,0)+IF(I15&lt;&gt;"미상",1,0)+IF(J15&lt;&gt;"미상",1,0)+IF(K15&lt;&gt;"미상",1,0)+IF(L15&lt;&gt;"미상",1,0)+IF(M15&lt;&gt;"미상",1,0)+IF(N15&lt;&gt;"미상",1,0))&amp;"/11"</f>
         <v/>
       </c>
-      <c r="AC15" s="6" t="inlineStr">
+      <c r="AD15" s="6" t="inlineStr">
         <is>
           <t>동물병원협회 추천 (비타트라)</t>
         </is>
@@ -3019,53 +3095,58 @@
         <f>IF(AND(J16="취약",I16&lt;&gt;"있음",OR(M16="없음",M16="미상")),"Y","N")</f>
         <v/>
       </c>
-      <c r="R16" s="8">
+      <c r="R16" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S16" s="8">
         <f>IF(NOT(ISNUMBER(D16)),0,IF(D16&gt;=300,20,IF(D16&gt;=200,15,IF(D16&gt;=100,10,5))))+IF(NOT(ISNUMBER(E16)),0,IF(E16&gt;=60,10,IF(E16&gt;=40,6,3)))+IFERROR(VLOOKUP(F16,기준!$B$4:$C$7,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="S16" s="8">
+      <c r="T16" s="8">
         <f>IFERROR(VLOOKUP(I16,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J16,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K16,기준!$B$34:$C$40,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="T16" s="8">
+      <c r="U16" s="8">
         <f>IFERROR(VLOOKUP(G16,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H16,기준!$B$16:$C$20,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="U16" s="8">
+      <c r="V16" s="8">
         <f>IFERROR(VLOOKUP(L16,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M16,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N16,기준!$B$54:$C$57,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="V16" s="8">
-        <f>SUM(R16:U16)</f>
-        <v/>
-      </c>
       <c r="W16" s="8">
-        <f>MIN(IF(O16="Y",20,100),IF(P16="Y",40,100),IF(Q16="Y",50,100))</f>
+        <f>SUM(S16:V16)</f>
         <v/>
       </c>
       <c r="X16" s="8">
-        <f>MIN(V16,W16)</f>
+        <f>MIN(IF(O16="Y",20,100),IF(P16="Y",40,100),IF(Q16="Y",50,100),IF(R16="Y",40,100))</f>
         <v/>
       </c>
       <c r="Y16" s="8">
-        <f>RANK(X16,$X$2:$X$34,0)</f>
-        <v/>
-      </c>
-      <c r="Z16" s="7" t="inlineStr">
-        <is>
-          <t>미상</t>
-        </is>
+        <f>MIN(W16,X16)</f>
+        <v/>
+      </c>
+      <c r="Z16" s="8">
+        <f>RANK(Y16,$Y$2:$Y$34,0)</f>
+        <v/>
       </c>
       <c r="AA16" s="7" t="inlineStr">
         <is>
+          <t>미상</t>
+        </is>
+      </c>
+      <c r="AB16" s="7" t="inlineStr">
+        <is>
           <t>미정</t>
         </is>
       </c>
-      <c r="AB16" s="6">
+      <c r="AC16" s="6">
         <f>(IF(ISNUMBER(D16),1,0)+IF(ISNUMBER(E16),1,0)+IF(F16&lt;&gt;"미상",1,0)+IF(G16&lt;&gt;"미상",1,0)+IF(H16&lt;&gt;"미상",1,0)+IF(I16&lt;&gt;"미상",1,0)+IF(J16&lt;&gt;"미상",1,0)+IF(K16&lt;&gt;"미상",1,0)+IF(L16&lt;&gt;"미상",1,0)+IF(M16&lt;&gt;"미상",1,0)+IF(N16&lt;&gt;"미상",1,0))&amp;"/11"</f>
         <v/>
       </c>
-      <c r="AC16" s="6" t="inlineStr">
+      <c r="AD16" s="6" t="inlineStr">
         <is>
           <t>미니 SKU·스펙 수집중</t>
         </is>
@@ -3147,53 +3228,58 @@
         <f>IF(AND(J17="취약",I17&lt;&gt;"있음",OR(M17="없음",M17="미상")),"Y","N")</f>
         <v/>
       </c>
-      <c r="R17" s="8">
+      <c r="R17" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S17" s="8">
         <f>IF(NOT(ISNUMBER(D17)),0,IF(D17&gt;=300,20,IF(D17&gt;=200,15,IF(D17&gt;=100,10,5))))+IF(NOT(ISNUMBER(E17)),0,IF(E17&gt;=60,10,IF(E17&gt;=40,6,3)))+IFERROR(VLOOKUP(F17,기준!$B$4:$C$7,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="S17" s="8">
+      <c r="T17" s="8">
         <f>IFERROR(VLOOKUP(I17,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J17,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K17,기준!$B$34:$C$40,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="T17" s="8">
+      <c r="U17" s="8">
         <f>IFERROR(VLOOKUP(G17,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H17,기준!$B$16:$C$20,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="U17" s="8">
+      <c r="V17" s="8">
         <f>IFERROR(VLOOKUP(L17,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M17,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N17,기준!$B$54:$C$57,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="V17" s="8">
-        <f>SUM(R17:U17)</f>
-        <v/>
-      </c>
       <c r="W17" s="8">
-        <f>MIN(IF(O17="Y",20,100),IF(P17="Y",40,100),IF(Q17="Y",50,100))</f>
+        <f>SUM(S17:V17)</f>
         <v/>
       </c>
       <c r="X17" s="8">
-        <f>MIN(V17,W17)</f>
+        <f>MIN(IF(O17="Y",20,100),IF(P17="Y",40,100),IF(Q17="Y",50,100),IF(R17="Y",40,100))</f>
         <v/>
       </c>
       <c r="Y17" s="8">
-        <f>RANK(X17,$X$2:$X$34,0)</f>
-        <v/>
-      </c>
-      <c r="Z17" s="7" t="inlineStr">
+        <f>MIN(W17,X17)</f>
+        <v/>
+      </c>
+      <c r="Z17" s="8">
+        <f>RANK(Y17,$Y$2:$Y$34,0)</f>
+        <v/>
+      </c>
+      <c r="AA17" s="7" t="inlineStr">
         <is>
           <t>라벨만</t>
         </is>
       </c>
-      <c r="AA17" s="7" t="inlineStr">
+      <c r="AB17" s="7" t="inlineStr">
         <is>
           <t>미정</t>
         </is>
       </c>
-      <c r="AB17" s="6">
+      <c r="AC17" s="6">
         <f>(IF(ISNUMBER(D17),1,0)+IF(ISNUMBER(E17),1,0)+IF(F17&lt;&gt;"미상",1,0)+IF(G17&lt;&gt;"미상",1,0)+IF(H17&lt;&gt;"미상",1,0)+IF(I17&lt;&gt;"미상",1,0)+IF(J17&lt;&gt;"미상",1,0)+IF(K17&lt;&gt;"미상",1,0)+IF(L17&lt;&gt;"미상",1,0)+IF(M17&lt;&gt;"미상",1,0)+IF(N17&lt;&gt;"미상",1,0))&amp;"/11"</f>
         <v/>
       </c>
-      <c r="AC17" s="6" t="inlineStr">
+      <c r="AD17" s="6" t="inlineStr">
         <is>
           <t>카이쿠라(KAIKOORA) 청어100%·아이슬란드산·EU특허 비산화구조·250/150ml 액상펌프·per회분 EPA+DHA mg 미상(이미지잠금) (kaikoora.com/펫프렌즈)</t>
         </is>
@@ -3275,53 +3361,58 @@
         <f>IF(AND(J18="취약",I18&lt;&gt;"있음",OR(M18="없음",M18="미상")),"Y","N")</f>
         <v/>
       </c>
-      <c r="R18" s="8">
+      <c r="R18" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S18" s="8">
         <f>IF(NOT(ISNUMBER(D18)),0,IF(D18&gt;=300,20,IF(D18&gt;=200,15,IF(D18&gt;=100,10,5))))+IF(NOT(ISNUMBER(E18)),0,IF(E18&gt;=60,10,IF(E18&gt;=40,6,3)))+IFERROR(VLOOKUP(F18,기준!$B$4:$C$7,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="S18" s="8">
+      <c r="T18" s="8">
         <f>IFERROR(VLOOKUP(I18,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J18,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K18,기준!$B$34:$C$40,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="T18" s="8">
+      <c r="U18" s="8">
         <f>IFERROR(VLOOKUP(G18,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H18,기준!$B$16:$C$20,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="U18" s="8">
+      <c r="V18" s="8">
         <f>IFERROR(VLOOKUP(L18,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M18,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N18,기준!$B$54:$C$57,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="V18" s="8">
-        <f>SUM(R18:U18)</f>
-        <v/>
-      </c>
       <c r="W18" s="8">
-        <f>MIN(IF(O18="Y",20,100),IF(P18="Y",40,100),IF(Q18="Y",50,100))</f>
+        <f>SUM(S18:V18)</f>
         <v/>
       </c>
       <c r="X18" s="8">
-        <f>MIN(V18,W18)</f>
+        <f>MIN(IF(O18="Y",20,100),IF(P18="Y",40,100),IF(Q18="Y",50,100),IF(R18="Y",40,100))</f>
         <v/>
       </c>
       <c r="Y18" s="8">
-        <f>RANK(X18,$X$2:$X$34,0)</f>
-        <v/>
-      </c>
-      <c r="Z18" s="7" t="inlineStr">
+        <f>MIN(W18,X18)</f>
+        <v/>
+      </c>
+      <c r="Z18" s="8">
+        <f>RANK(Y18,$Y$2:$Y$34,0)</f>
+        <v/>
+      </c>
+      <c r="AA18" s="7" t="inlineStr">
         <is>
           <t>라벨만</t>
         </is>
       </c>
-      <c r="AA18" s="7" t="inlineStr">
+      <c r="AB18" s="7" t="inlineStr">
         <is>
           <t>미정</t>
         </is>
       </c>
-      <c r="AB18" s="6">
+      <c r="AC18" s="6">
         <f>(IF(ISNUMBER(D18),1,0)+IF(ISNUMBER(E18),1,0)+IF(F18&lt;&gt;"미상",1,0)+IF(G18&lt;&gt;"미상",1,0)+IF(H18&lt;&gt;"미상",1,0)+IF(I18&lt;&gt;"미상",1,0)+IF(J18&lt;&gt;"미상",1,0)+IF(K18&lt;&gt;"미상",1,0)+IF(L18&lt;&gt;"미상",1,0)+IF(M18&lt;&gt;"미상",1,0)+IF(N18&lt;&gt;"미상",1,0))&amp;"/11"</f>
         <v/>
       </c>
-      <c r="AC18" s="6" t="inlineStr">
+      <c r="AD18" s="6" t="inlineStr">
         <is>
           <t>연어·액상·공기차단특허</t>
         </is>
@@ -3403,53 +3494,58 @@
         <f>IF(AND(J19="취약",I19&lt;&gt;"있음",OR(M19="없음",M19="미상")),"Y","N")</f>
         <v/>
       </c>
-      <c r="R19" s="8">
+      <c r="R19" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S19" s="8">
         <f>IF(NOT(ISNUMBER(D19)),0,IF(D19&gt;=300,20,IF(D19&gt;=200,15,IF(D19&gt;=100,10,5))))+IF(NOT(ISNUMBER(E19)),0,IF(E19&gt;=60,10,IF(E19&gt;=40,6,3)))+IFERROR(VLOOKUP(F19,기준!$B$4:$C$7,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="S19" s="8">
+      <c r="T19" s="8">
         <f>IFERROR(VLOOKUP(I19,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J19,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K19,기준!$B$34:$C$40,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="T19" s="8">
+      <c r="U19" s="8">
         <f>IFERROR(VLOOKUP(G19,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H19,기준!$B$16:$C$20,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="U19" s="8">
+      <c r="V19" s="8">
         <f>IFERROR(VLOOKUP(L19,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M19,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N19,기준!$B$54:$C$57,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="V19" s="8">
-        <f>SUM(R19:U19)</f>
-        <v/>
-      </c>
       <c r="W19" s="8">
-        <f>MIN(IF(O19="Y",20,100),IF(P19="Y",40,100),IF(Q19="Y",50,100))</f>
+        <f>SUM(S19:V19)</f>
         <v/>
       </c>
       <c r="X19" s="8">
-        <f>MIN(V19,W19)</f>
+        <f>MIN(IF(O19="Y",20,100),IF(P19="Y",40,100),IF(Q19="Y",50,100),IF(R19="Y",40,100))</f>
         <v/>
       </c>
       <c r="Y19" s="8">
-        <f>RANK(X19,$X$2:$X$34,0)</f>
-        <v/>
-      </c>
-      <c r="Z19" s="7" t="inlineStr">
+        <f>MIN(W19,X19)</f>
+        <v/>
+      </c>
+      <c r="Z19" s="8">
+        <f>RANK(Y19,$Y$2:$Y$34,0)</f>
+        <v/>
+      </c>
+      <c r="AA19" s="7" t="inlineStr">
         <is>
           <t>라벨만</t>
         </is>
       </c>
-      <c r="AA19" s="7" t="inlineStr">
+      <c r="AB19" s="7" t="inlineStr">
         <is>
           <t>미정</t>
         </is>
       </c>
-      <c r="AB19" s="6">
+      <c r="AC19" s="6">
         <f>(IF(ISNUMBER(D19),1,0)+IF(ISNUMBER(E19),1,0)+IF(F19&lt;&gt;"미상",1,0)+IF(G19&lt;&gt;"미상",1,0)+IF(H19&lt;&gt;"미상",1,0)+IF(I19&lt;&gt;"미상",1,0)+IF(J19&lt;&gt;"미상",1,0)+IF(K19&lt;&gt;"미상",1,0)+IF(L19&lt;&gt;"미상",1,0)+IF(M19&lt;&gt;"미상",1,0)+IF(N19&lt;&gt;"미상",1,0))&amp;"/11"</f>
         <v/>
       </c>
-      <c r="AC19" s="6" t="inlineStr">
+      <c r="AD19" s="6" t="inlineStr">
         <is>
           <t>연어오일 1000ml 대용량 (핏펫)</t>
         </is>
@@ -3531,53 +3627,58 @@
         <f>IF(AND(J20="취약",I20&lt;&gt;"있음",OR(M20="없음",M20="미상")),"Y","N")</f>
         <v/>
       </c>
-      <c r="R20" s="8">
+      <c r="R20" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S20" s="8">
         <f>IF(NOT(ISNUMBER(D20)),0,IF(D20&gt;=300,20,IF(D20&gt;=200,15,IF(D20&gt;=100,10,5))))+IF(NOT(ISNUMBER(E20)),0,IF(E20&gt;=60,10,IF(E20&gt;=40,6,3)))+IFERROR(VLOOKUP(F20,기준!$B$4:$C$7,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="S20" s="8">
+      <c r="T20" s="8">
         <f>IFERROR(VLOOKUP(I20,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J20,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K20,기준!$B$34:$C$40,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="T20" s="8">
+      <c r="U20" s="8">
         <f>IFERROR(VLOOKUP(G20,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H20,기준!$B$16:$C$20,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="U20" s="8">
+      <c r="V20" s="8">
         <f>IFERROR(VLOOKUP(L20,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M20,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N20,기준!$B$54:$C$57,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="V20" s="8">
-        <f>SUM(R20:U20)</f>
-        <v/>
-      </c>
       <c r="W20" s="8">
-        <f>MIN(IF(O20="Y",20,100),IF(P20="Y",40,100),IF(Q20="Y",50,100))</f>
+        <f>SUM(S20:V20)</f>
         <v/>
       </c>
       <c r="X20" s="8">
-        <f>MIN(V20,W20)</f>
+        <f>MIN(IF(O20="Y",20,100),IF(P20="Y",40,100),IF(Q20="Y",50,100),IF(R20="Y",40,100))</f>
         <v/>
       </c>
       <c r="Y20" s="8">
-        <f>RANK(X20,$X$2:$X$34,0)</f>
-        <v/>
-      </c>
-      <c r="Z20" s="7" t="inlineStr">
-        <is>
-          <t>미상</t>
-        </is>
+        <f>MIN(W20,X20)</f>
+        <v/>
+      </c>
+      <c r="Z20" s="8">
+        <f>RANK(Y20,$Y$2:$Y$34,0)</f>
+        <v/>
       </c>
       <c r="AA20" s="7" t="inlineStr">
         <is>
+          <t>미상</t>
+        </is>
+      </c>
+      <c r="AB20" s="7" t="inlineStr">
+        <is>
           <t>미정</t>
         </is>
       </c>
-      <c r="AB20" s="6">
+      <c r="AC20" s="6">
         <f>(IF(ISNUMBER(D20),1,0)+IF(ISNUMBER(E20),1,0)+IF(F20&lt;&gt;"미상",1,0)+IF(G20&lt;&gt;"미상",1,0)+IF(H20&lt;&gt;"미상",1,0)+IF(I20&lt;&gt;"미상",1,0)+IF(J20&lt;&gt;"미상",1,0)+IF(K20&lt;&gt;"미상",1,0)+IF(L20&lt;&gt;"미상",1,0)+IF(M20&lt;&gt;"미상",1,0)+IF(N20&lt;&gt;"미상",1,0))&amp;"/11"</f>
         <v/>
       </c>
-      <c r="AC20" s="6" t="inlineStr">
+      <c r="AD20" s="6" t="inlineStr">
         <is>
           <t>노르웨이 연어오일·스펙 수집중</t>
         </is>
@@ -3659,53 +3760,58 @@
         <f>IF(AND(J21="취약",I21&lt;&gt;"있음",OR(M21="없음",M21="미상")),"Y","N")</f>
         <v/>
       </c>
-      <c r="R21" s="8">
+      <c r="R21" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S21" s="8">
         <f>IF(NOT(ISNUMBER(D21)),0,IF(D21&gt;=300,20,IF(D21&gt;=200,15,IF(D21&gt;=100,10,5))))+IF(NOT(ISNUMBER(E21)),0,IF(E21&gt;=60,10,IF(E21&gt;=40,6,3)))+IFERROR(VLOOKUP(F21,기준!$B$4:$C$7,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="S21" s="8">
+      <c r="T21" s="8">
         <f>IFERROR(VLOOKUP(I21,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J21,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K21,기준!$B$34:$C$40,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="T21" s="8">
+      <c r="U21" s="8">
         <f>IFERROR(VLOOKUP(G21,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H21,기준!$B$16:$C$20,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="U21" s="8">
+      <c r="V21" s="8">
         <f>IFERROR(VLOOKUP(L21,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M21,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N21,기준!$B$54:$C$57,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="V21" s="8">
-        <f>SUM(R21:U21)</f>
-        <v/>
-      </c>
       <c r="W21" s="8">
-        <f>MIN(IF(O21="Y",20,100),IF(P21="Y",40,100),IF(Q21="Y",50,100))</f>
+        <f>SUM(S21:V21)</f>
         <v/>
       </c>
       <c r="X21" s="8">
-        <f>MIN(V21,W21)</f>
+        <f>MIN(IF(O21="Y",20,100),IF(P21="Y",40,100),IF(Q21="Y",50,100),IF(R21="Y",40,100))</f>
         <v/>
       </c>
       <c r="Y21" s="8">
-        <f>RANK(X21,$X$2:$X$34,0)</f>
-        <v/>
-      </c>
-      <c r="Z21" s="7" t="inlineStr">
+        <f>MIN(W21,X21)</f>
+        <v/>
+      </c>
+      <c r="Z21" s="8">
+        <f>RANK(Y21,$Y$2:$Y$34,0)</f>
+        <v/>
+      </c>
+      <c r="AA21" s="7" t="inlineStr">
         <is>
           <t>라벨만</t>
         </is>
       </c>
-      <c r="AA21" s="7" t="inlineStr">
+      <c r="AB21" s="7" t="inlineStr">
         <is>
           <t>미정</t>
         </is>
       </c>
-      <c r="AB21" s="6">
+      <c r="AC21" s="6">
         <f>(IF(ISNUMBER(D21),1,0)+IF(ISNUMBER(E21),1,0)+IF(F21&lt;&gt;"미상",1,0)+IF(G21&lt;&gt;"미상",1,0)+IF(H21&lt;&gt;"미상",1,0)+IF(I21&lt;&gt;"미상",1,0)+IF(J21&lt;&gt;"미상",1,0)+IF(K21&lt;&gt;"미상",1,0)+IF(L21&lt;&gt;"미상",1,0)+IF(M21&lt;&gt;"미상",1,0)+IF(N21&lt;&gt;"미상",1,0))&amp;"/11"</f>
         <v/>
       </c>
-      <c r="AC21" s="6" t="inlineStr">
+      <c r="AD21" s="6" t="inlineStr">
         <is>
           <t>연어+폴락(대구과 어체유, 간유 아님)→비타민A/D 상한 부적용 (핏펫)</t>
         </is>
@@ -3787,53 +3893,58 @@
         <f>IF(AND(J22="취약",I22&lt;&gt;"있음",OR(M22="없음",M22="미상")),"Y","N")</f>
         <v/>
       </c>
-      <c r="R22" s="8">
+      <c r="R22" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S22" s="8">
         <f>IF(NOT(ISNUMBER(D22)),0,IF(D22&gt;=300,20,IF(D22&gt;=200,15,IF(D22&gt;=100,10,5))))+IF(NOT(ISNUMBER(E22)),0,IF(E22&gt;=60,10,IF(E22&gt;=40,6,3)))+IFERROR(VLOOKUP(F22,기준!$B$4:$C$7,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="S22" s="8">
+      <c r="T22" s="8">
         <f>IFERROR(VLOOKUP(I22,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J22,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K22,기준!$B$34:$C$40,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="T22" s="8">
+      <c r="U22" s="8">
         <f>IFERROR(VLOOKUP(G22,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H22,기준!$B$16:$C$20,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="U22" s="8">
+      <c r="V22" s="8">
         <f>IFERROR(VLOOKUP(L22,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M22,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N22,기준!$B$54:$C$57,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="V22" s="8">
-        <f>SUM(R22:U22)</f>
-        <v/>
-      </c>
       <c r="W22" s="8">
-        <f>MIN(IF(O22="Y",20,100),IF(P22="Y",40,100),IF(Q22="Y",50,100))</f>
+        <f>SUM(S22:V22)</f>
         <v/>
       </c>
       <c r="X22" s="8">
-        <f>MIN(V22,W22)</f>
+        <f>MIN(IF(O22="Y",20,100),IF(P22="Y",40,100),IF(Q22="Y",50,100),IF(R22="Y",40,100))</f>
         <v/>
       </c>
       <c r="Y22" s="8">
-        <f>RANK(X22,$X$2:$X$34,0)</f>
-        <v/>
-      </c>
-      <c r="Z22" s="7" t="inlineStr">
-        <is>
-          <t>미상</t>
-        </is>
+        <f>MIN(W22,X22)</f>
+        <v/>
+      </c>
+      <c r="Z22" s="8">
+        <f>RANK(Y22,$Y$2:$Y$34,0)</f>
+        <v/>
       </c>
       <c r="AA22" s="7" t="inlineStr">
         <is>
+          <t>미상</t>
+        </is>
+      </c>
+      <c r="AB22" s="7" t="inlineStr">
+        <is>
           <t>미정</t>
         </is>
       </c>
-      <c r="AB22" s="6">
+      <c r="AC22" s="6">
         <f>(IF(ISNUMBER(D22),1,0)+IF(ISNUMBER(E22),1,0)+IF(F22&lt;&gt;"미상",1,0)+IF(G22&lt;&gt;"미상",1,0)+IF(H22&lt;&gt;"미상",1,0)+IF(I22&lt;&gt;"미상",1,0)+IF(J22&lt;&gt;"미상",1,0)+IF(K22&lt;&gt;"미상",1,0)+IF(L22&lt;&gt;"미상",1,0)+IF(M22&lt;&gt;"미상",1,0)+IF(N22&lt;&gt;"미상",1,0))&amp;"/11"</f>
         <v/>
       </c>
-      <c r="AC22" s="6" t="inlineStr">
+      <c r="AD22" s="6" t="inlineStr">
         <is>
           <t>물개오일+루테인·해양성·스펙 미상 (핏펫)</t>
         </is>
@@ -3917,53 +4028,58 @@
         <f>IF(AND(J23="취약",I23&lt;&gt;"있음",OR(M23="없음",M23="미상")),"Y","N")</f>
         <v/>
       </c>
-      <c r="R23" s="8">
+      <c r="R23" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S23" s="8">
         <f>IF(NOT(ISNUMBER(D23)),0,IF(D23&gt;=300,20,IF(D23&gt;=200,15,IF(D23&gt;=100,10,5))))+IF(NOT(ISNUMBER(E23)),0,IF(E23&gt;=60,10,IF(E23&gt;=40,6,3)))+IFERROR(VLOOKUP(F23,기준!$B$4:$C$7,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="S23" s="8">
+      <c r="T23" s="8">
         <f>IFERROR(VLOOKUP(I23,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J23,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K23,기준!$B$34:$C$40,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="T23" s="8">
+      <c r="U23" s="8">
         <f>IFERROR(VLOOKUP(G23,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H23,기준!$B$16:$C$20,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="U23" s="8">
+      <c r="V23" s="8">
         <f>IFERROR(VLOOKUP(L23,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M23,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N23,기준!$B$54:$C$57,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="V23" s="8">
-        <f>SUM(R23:U23)</f>
-        <v/>
-      </c>
       <c r="W23" s="8">
-        <f>MIN(IF(O23="Y",20,100),IF(P23="Y",40,100),IF(Q23="Y",50,100))</f>
+        <f>SUM(S23:V23)</f>
         <v/>
       </c>
       <c r="X23" s="8">
-        <f>MIN(V23,W23)</f>
+        <f>MIN(IF(O23="Y",20,100),IF(P23="Y",40,100),IF(Q23="Y",50,100),IF(R23="Y",40,100))</f>
         <v/>
       </c>
       <c r="Y23" s="8">
-        <f>RANK(X23,$X$2:$X$34,0)</f>
-        <v/>
-      </c>
-      <c r="Z23" s="7" t="inlineStr">
+        <f>MIN(W23,X23)</f>
+        <v/>
+      </c>
+      <c r="Z23" s="8">
+        <f>RANK(Y23,$Y$2:$Y$34,0)</f>
+        <v/>
+      </c>
+      <c r="AA23" s="7" t="inlineStr">
         <is>
           <t>라벨만</t>
         </is>
       </c>
-      <c r="AA23" s="7" t="inlineStr">
+      <c r="AB23" s="7" t="inlineStr">
         <is>
           <t>DHA중심(조류)</t>
         </is>
       </c>
-      <c r="AB23" s="6">
+      <c r="AC23" s="6">
         <f>(IF(ISNUMBER(D23),1,0)+IF(ISNUMBER(E23),1,0)+IF(F23&lt;&gt;"미상",1,0)+IF(G23&lt;&gt;"미상",1,0)+IF(H23&lt;&gt;"미상",1,0)+IF(I23&lt;&gt;"미상",1,0)+IF(J23&lt;&gt;"미상",1,0)+IF(K23&lt;&gt;"미상",1,0)+IF(L23&lt;&gt;"미상",1,0)+IF(M23&lt;&gt;"미상",1,0)+IF(N23&lt;&gt;"미상",1,0))&amp;"/11"</f>
         <v/>
       </c>
-      <c r="AC23" s="6" t="inlineStr">
+      <c r="AD23" s="6" t="inlineStr">
         <is>
           <t>미세조류 추출 식물성→조류(정상·상한해제 확정)·1g당 EPA+DHA 645mg→순도64.5%·per캡슐mg 미상(이미지잠금) (drmune.com/etnews 20260210)</t>
         </is>
@@ -4045,53 +4161,58 @@
         <f>IF(AND(J24="취약",I24&lt;&gt;"있음",OR(M24="없음",M24="미상")),"Y","N")</f>
         <v/>
       </c>
-      <c r="R24" s="8">
+      <c r="R24" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S24" s="8">
         <f>IF(NOT(ISNUMBER(D24)),0,IF(D24&gt;=300,20,IF(D24&gt;=200,15,IF(D24&gt;=100,10,5))))+IF(NOT(ISNUMBER(E24)),0,IF(E24&gt;=60,10,IF(E24&gt;=40,6,3)))+IFERROR(VLOOKUP(F24,기준!$B$4:$C$7,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="S24" s="8">
+      <c r="T24" s="8">
         <f>IFERROR(VLOOKUP(I24,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J24,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K24,기준!$B$34:$C$40,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="T24" s="8">
+      <c r="U24" s="8">
         <f>IFERROR(VLOOKUP(G24,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H24,기준!$B$16:$C$20,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="U24" s="8">
+      <c r="V24" s="8">
         <f>IFERROR(VLOOKUP(L24,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M24,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N24,기준!$B$54:$C$57,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="V24" s="8">
-        <f>SUM(R24:U24)</f>
-        <v/>
-      </c>
       <c r="W24" s="8">
-        <f>MIN(IF(O24="Y",20,100),IF(P24="Y",40,100),IF(Q24="Y",50,100))</f>
+        <f>SUM(S24:V24)</f>
         <v/>
       </c>
       <c r="X24" s="8">
-        <f>MIN(V24,W24)</f>
+        <f>MIN(IF(O24="Y",20,100),IF(P24="Y",40,100),IF(Q24="Y",50,100),IF(R24="Y",40,100))</f>
         <v/>
       </c>
       <c r="Y24" s="8">
-        <f>RANK(X24,$X$2:$X$34,0)</f>
-        <v/>
-      </c>
-      <c r="Z24" s="7" t="inlineStr">
+        <f>MIN(W24,X24)</f>
+        <v/>
+      </c>
+      <c r="Z24" s="8">
+        <f>RANK(Y24,$Y$2:$Y$34,0)</f>
+        <v/>
+      </c>
+      <c r="AA24" s="7" t="inlineStr">
         <is>
           <t>라벨만</t>
         </is>
       </c>
-      <c r="AA24" s="7" t="inlineStr">
+      <c r="AB24" s="7" t="inlineStr">
         <is>
           <t>DHA중심(조류)</t>
         </is>
       </c>
-      <c r="AB24" s="6">
+      <c r="AC24" s="6">
         <f>(IF(ISNUMBER(D24),1,0)+IF(ISNUMBER(E24),1,0)+IF(F24&lt;&gt;"미상",1,0)+IF(G24&lt;&gt;"미상",1,0)+IF(H24&lt;&gt;"미상",1,0)+IF(I24&lt;&gt;"미상",1,0)+IF(J24&lt;&gt;"미상",1,0)+IF(K24&lt;&gt;"미상",1,0)+IF(L24&lt;&gt;"미상",1,0)+IF(M24&lt;&gt;"미상",1,0)+IF(N24&lt;&gt;"미상",1,0))&amp;"/11"</f>
         <v/>
       </c>
-      <c r="AC24" s="6" t="inlineStr">
+      <c r="AD24" s="6" t="inlineStr">
         <is>
           <t>식물성 rTG=미세조류 DHA(EPA 거의 없음)·상한 부적용·DHA 편중(브랜드 식물성라인 순도~80%) (소셜타임스)</t>
         </is>
@@ -4173,53 +4294,58 @@
         <f>IF(AND(J25="취약",I25&lt;&gt;"있음",OR(M25="없음",M25="미상")),"Y","N")</f>
         <v/>
       </c>
-      <c r="R25" s="8">
+      <c r="R25" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S25" s="8">
         <f>IF(NOT(ISNUMBER(D25)),0,IF(D25&gt;=300,20,IF(D25&gt;=200,15,IF(D25&gt;=100,10,5))))+IF(NOT(ISNUMBER(E25)),0,IF(E25&gt;=60,10,IF(E25&gt;=40,6,3)))+IFERROR(VLOOKUP(F25,기준!$B$4:$C$7,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="S25" s="8">
+      <c r="T25" s="8">
         <f>IFERROR(VLOOKUP(I25,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J25,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K25,기준!$B$34:$C$40,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="T25" s="8">
+      <c r="U25" s="8">
         <f>IFERROR(VLOOKUP(G25,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H25,기준!$B$16:$C$20,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="U25" s="8">
+      <c r="V25" s="8">
         <f>IFERROR(VLOOKUP(L25,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M25,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N25,기준!$B$54:$C$57,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="V25" s="8">
-        <f>SUM(R25:U25)</f>
-        <v/>
-      </c>
       <c r="W25" s="8">
-        <f>MIN(IF(O25="Y",20,100),IF(P25="Y",40,100),IF(Q25="Y",50,100))</f>
+        <f>SUM(S25:V25)</f>
         <v/>
       </c>
       <c r="X25" s="8">
-        <f>MIN(V25,W25)</f>
+        <f>MIN(IF(O25="Y",20,100),IF(P25="Y",40,100),IF(Q25="Y",50,100),IF(R25="Y",40,100))</f>
         <v/>
       </c>
       <c r="Y25" s="8">
-        <f>RANK(X25,$X$2:$X$34,0)</f>
-        <v/>
-      </c>
-      <c r="Z25" s="7" t="inlineStr">
-        <is>
-          <t>미상</t>
-        </is>
+        <f>MIN(W25,X25)</f>
+        <v/>
+      </c>
+      <c r="Z25" s="8">
+        <f>RANK(Y25,$Y$2:$Y$34,0)</f>
+        <v/>
       </c>
       <c r="AA25" s="7" t="inlineStr">
         <is>
+          <t>미상</t>
+        </is>
+      </c>
+      <c r="AB25" s="7" t="inlineStr">
+        <is>
           <t>미정</t>
         </is>
       </c>
-      <c r="AB25" s="6">
+      <c r="AC25" s="6">
         <f>(IF(ISNUMBER(D25),1,0)+IF(ISNUMBER(E25),1,0)+IF(F25&lt;&gt;"미상",1,0)+IF(G25&lt;&gt;"미상",1,0)+IF(H25&lt;&gt;"미상",1,0)+IF(I25&lt;&gt;"미상",1,0)+IF(J25&lt;&gt;"미상",1,0)+IF(K25&lt;&gt;"미상",1,0)+IF(L25&lt;&gt;"미상",1,0)+IF(M25&lt;&gt;"미상",1,0)+IF(N25&lt;&gt;"미상",1,0))&amp;"/11"</f>
         <v/>
       </c>
-      <c r="AC25" s="6" t="inlineStr">
+      <c r="AD25" s="6" t="inlineStr">
         <is>
           <t>병원/클리닉 채널·공개정보 적음·수집중</t>
         </is>
@@ -4301,53 +4427,58 @@
         <f>IF(AND(J26="취약",I26&lt;&gt;"있음",OR(M26="없음",M26="미상")),"Y","N")</f>
         <v/>
       </c>
-      <c r="R26" s="8">
+      <c r="R26" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S26" s="8">
         <f>IF(NOT(ISNUMBER(D26)),0,IF(D26&gt;=300,20,IF(D26&gt;=200,15,IF(D26&gt;=100,10,5))))+IF(NOT(ISNUMBER(E26)),0,IF(E26&gt;=60,10,IF(E26&gt;=40,6,3)))+IFERROR(VLOOKUP(F26,기준!$B$4:$C$7,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="S26" s="8">
+      <c r="T26" s="8">
         <f>IFERROR(VLOOKUP(I26,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J26,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K26,기준!$B$34:$C$40,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="T26" s="8">
+      <c r="U26" s="8">
         <f>IFERROR(VLOOKUP(G26,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H26,기준!$B$16:$C$20,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="U26" s="8">
+      <c r="V26" s="8">
         <f>IFERROR(VLOOKUP(L26,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M26,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N26,기준!$B$54:$C$57,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="V26" s="8">
-        <f>SUM(R26:U26)</f>
-        <v/>
-      </c>
       <c r="W26" s="8">
-        <f>MIN(IF(O26="Y",20,100),IF(P26="Y",40,100),IF(Q26="Y",50,100))</f>
+        <f>SUM(S26:V26)</f>
         <v/>
       </c>
       <c r="X26" s="8">
-        <f>MIN(V26,W26)</f>
+        <f>MIN(IF(O26="Y",20,100),IF(P26="Y",40,100),IF(Q26="Y",50,100),IF(R26="Y",40,100))</f>
         <v/>
       </c>
       <c r="Y26" s="8">
-        <f>RANK(X26,$X$2:$X$34,0)</f>
-        <v/>
-      </c>
-      <c r="Z26" s="7" t="inlineStr">
-        <is>
-          <t>미상</t>
-        </is>
+        <f>MIN(W26,X26)</f>
+        <v/>
+      </c>
+      <c r="Z26" s="8">
+        <f>RANK(Y26,$Y$2:$Y$34,0)</f>
+        <v/>
       </c>
       <c r="AA26" s="7" t="inlineStr">
         <is>
+          <t>미상</t>
+        </is>
+      </c>
+      <c r="AB26" s="7" t="inlineStr">
+        <is>
           <t>미정</t>
         </is>
       </c>
-      <c r="AB26" s="6">
+      <c r="AC26" s="6">
         <f>(IF(ISNUMBER(D26),1,0)+IF(ISNUMBER(E26),1,0)+IF(F26&lt;&gt;"미상",1,0)+IF(G26&lt;&gt;"미상",1,0)+IF(H26&lt;&gt;"미상",1,0)+IF(I26&lt;&gt;"미상",1,0)+IF(J26&lt;&gt;"미상",1,0)+IF(K26&lt;&gt;"미상",1,0)+IF(L26&lt;&gt;"미상",1,0)+IF(M26&lt;&gt;"미상",1,0)+IF(N26&lt;&gt;"미상",1,0))&amp;"/11"</f>
         <v/>
       </c>
-      <c r="AC26" s="6" t="inlineStr">
+      <c r="AD26" s="6" t="inlineStr">
         <is>
           <t>병원 납품·공개정보 적음·수집중</t>
         </is>
@@ -4433,53 +4564,58 @@
         <f>IF(AND(J27="취약",I27&lt;&gt;"있음",OR(M27="없음",M27="미상")),"Y","N")</f>
         <v/>
       </c>
-      <c r="R27" s="8">
+      <c r="R27" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S27" s="8">
         <f>IF(NOT(ISNUMBER(D27)),0,IF(D27&gt;=300,20,IF(D27&gt;=200,15,IF(D27&gt;=100,10,5))))+IF(NOT(ISNUMBER(E27)),0,IF(E27&gt;=60,10,IF(E27&gt;=40,6,3)))+IFERROR(VLOOKUP(F27,기준!$B$4:$C$7,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="S27" s="8">
+      <c r="T27" s="8">
         <f>IFERROR(VLOOKUP(I27,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J27,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K27,기준!$B$34:$C$40,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="T27" s="8">
+      <c r="U27" s="8">
         <f>IFERROR(VLOOKUP(G27,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H27,기준!$B$16:$C$20,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="U27" s="8">
+      <c r="V27" s="8">
         <f>IFERROR(VLOOKUP(L27,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M27,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N27,기준!$B$54:$C$57,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="V27" s="8">
-        <f>SUM(R27:U27)</f>
-        <v/>
-      </c>
       <c r="W27" s="8">
-        <f>MIN(IF(O27="Y",20,100),IF(P27="Y",40,100),IF(Q27="Y",50,100))</f>
+        <f>SUM(S27:V27)</f>
         <v/>
       </c>
       <c r="X27" s="8">
-        <f>MIN(V27,W27)</f>
+        <f>MIN(IF(O27="Y",20,100),IF(P27="Y",40,100),IF(Q27="Y",50,100),IF(R27="Y",40,100))</f>
         <v/>
       </c>
       <c r="Y27" s="8">
-        <f>RANK(X27,$X$2:$X$34,0)</f>
-        <v/>
-      </c>
-      <c r="Z27" s="7" t="inlineStr">
+        <f>MIN(W27,X27)</f>
+        <v/>
+      </c>
+      <c r="Z27" s="8">
+        <f>RANK(Y27,$Y$2:$Y$34,0)</f>
+        <v/>
+      </c>
+      <c r="AA27" s="7" t="inlineStr">
         <is>
           <t>공개·검증</t>
         </is>
       </c>
-      <c r="AA27" s="7" t="inlineStr">
+      <c r="AB27" s="7" t="inlineStr">
         <is>
           <t>미정</t>
         </is>
       </c>
-      <c r="AB27" s="6">
+      <c r="AC27" s="6">
         <f>(IF(ISNUMBER(D27),1,0)+IF(ISNUMBER(E27),1,0)+IF(F27&lt;&gt;"미상",1,0)+IF(G27&lt;&gt;"미상",1,0)+IF(H27&lt;&gt;"미상",1,0)+IF(I27&lt;&gt;"미상",1,0)+IF(J27&lt;&gt;"미상",1,0)+IF(K27&lt;&gt;"미상",1,0)+IF(L27&lt;&gt;"미상",1,0)+IF(M27&lt;&gt;"미상",1,0)+IF(N27&lt;&gt;"미상",1,0))&amp;"/11"</f>
         <v/>
       </c>
-      <c r="AC27" s="6" t="inlineStr">
+      <c r="AD27" s="6" t="inlineStr">
         <is>
           <t>EPA+DHA 937/캡슐·순도~75%·AlaskaOmega·IFOS·병포장 (필라이즈)</t>
         </is>
@@ -4563,53 +4699,58 @@
         <f>IF(AND(J28="취약",I28&lt;&gt;"있음",OR(M28="없음",M28="미상")),"Y","N")</f>
         <v/>
       </c>
-      <c r="R28" s="8">
+      <c r="R28" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S28" s="8">
         <f>IF(NOT(ISNUMBER(D28)),0,IF(D28&gt;=300,20,IF(D28&gt;=200,15,IF(D28&gt;=100,10,5))))+IF(NOT(ISNUMBER(E28)),0,IF(E28&gt;=60,10,IF(E28&gt;=40,6,3)))+IFERROR(VLOOKUP(F28,기준!$B$4:$C$7,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="S28" s="8">
+      <c r="T28" s="8">
         <f>IFERROR(VLOOKUP(I28,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J28,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K28,기준!$B$34:$C$40,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="T28" s="8">
+      <c r="U28" s="8">
         <f>IFERROR(VLOOKUP(G28,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H28,기준!$B$16:$C$20,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="U28" s="8">
+      <c r="V28" s="8">
         <f>IFERROR(VLOOKUP(L28,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M28,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N28,기준!$B$54:$C$57,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="V28" s="8">
-        <f>SUM(R28:U28)</f>
-        <v/>
-      </c>
       <c r="W28" s="8">
-        <f>MIN(IF(O28="Y",20,100),IF(P28="Y",40,100),IF(Q28="Y",50,100))</f>
+        <f>SUM(S28:V28)</f>
         <v/>
       </c>
       <c r="X28" s="8">
-        <f>MIN(V28,W28)</f>
+        <f>MIN(IF(O28="Y",20,100),IF(P28="Y",40,100),IF(Q28="Y",50,100),IF(R28="Y",40,100))</f>
         <v/>
       </c>
       <c r="Y28" s="8">
-        <f>RANK(X28,$X$2:$X$34,0)</f>
-        <v/>
-      </c>
-      <c r="Z28" s="7" t="inlineStr">
+        <f>MIN(W28,X28)</f>
+        <v/>
+      </c>
+      <c r="Z28" s="8">
+        <f>RANK(Y28,$Y$2:$Y$34,0)</f>
+        <v/>
+      </c>
+      <c r="AA28" s="7" t="inlineStr">
         <is>
           <t>라벨만</t>
         </is>
       </c>
-      <c r="AA28" s="7" t="inlineStr">
+      <c r="AB28" s="7" t="inlineStr">
         <is>
           <t>미정</t>
         </is>
       </c>
-      <c r="AB28" s="6">
+      <c r="AC28" s="6">
         <f>(IF(ISNUMBER(D28),1,0)+IF(ISNUMBER(E28),1,0)+IF(F28&lt;&gt;"미상",1,0)+IF(G28&lt;&gt;"미상",1,0)+IF(H28&lt;&gt;"미상",1,0)+IF(I28&lt;&gt;"미상",1,0)+IF(J28&lt;&gt;"미상",1,0)+IF(K28&lt;&gt;"미상",1,0)+IF(L28&lt;&gt;"미상",1,0)+IF(M28&lt;&gt;"미상",1,0)+IF(N28&lt;&gt;"미상",1,0))&amp;"/11"</f>
         <v/>
       </c>
-      <c r="AC28" s="6" t="inlineStr">
+      <c r="AD28" s="6" t="inlineStr">
         <is>
           <t>1캡슐 EPA+DHA 300mg·rTG·AlaskaOmega(알래스카 명태유=일반어)·비타민A 첨가(눈건강 기능성)·식약처 이중기능성 (ckdhcmall/필라이즈)</t>
         </is>
@@ -4691,53 +4832,58 @@
         <f>IF(AND(J29="취약",I29&lt;&gt;"있음",OR(M29="없음",M29="미상")),"Y","N")</f>
         <v/>
       </c>
-      <c r="R29" s="8">
+      <c r="R29" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S29" s="8">
         <f>IF(NOT(ISNUMBER(D29)),0,IF(D29&gt;=300,20,IF(D29&gt;=200,15,IF(D29&gt;=100,10,5))))+IF(NOT(ISNUMBER(E29)),0,IF(E29&gt;=60,10,IF(E29&gt;=40,6,3)))+IFERROR(VLOOKUP(F29,기준!$B$4:$C$7,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="S29" s="8">
+      <c r="T29" s="8">
         <f>IFERROR(VLOOKUP(I29,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J29,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K29,기준!$B$34:$C$40,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="T29" s="8">
+      <c r="U29" s="8">
         <f>IFERROR(VLOOKUP(G29,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H29,기준!$B$16:$C$20,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="U29" s="8">
+      <c r="V29" s="8">
         <f>IFERROR(VLOOKUP(L29,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M29,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N29,기준!$B$54:$C$57,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="V29" s="8">
-        <f>SUM(R29:U29)</f>
-        <v/>
-      </c>
       <c r="W29" s="8">
-        <f>MIN(IF(O29="Y",20,100),IF(P29="Y",40,100),IF(Q29="Y",50,100))</f>
+        <f>SUM(S29:V29)</f>
         <v/>
       </c>
       <c r="X29" s="8">
-        <f>MIN(V29,W29)</f>
+        <f>MIN(IF(O29="Y",20,100),IF(P29="Y",40,100),IF(Q29="Y",50,100),IF(R29="Y",40,100))</f>
         <v/>
       </c>
       <c r="Y29" s="8">
-        <f>RANK(X29,$X$2:$X$34,0)</f>
-        <v/>
-      </c>
-      <c r="Z29" s="7" t="inlineStr">
+        <f>MIN(W29,X29)</f>
+        <v/>
+      </c>
+      <c r="Z29" s="8">
+        <f>RANK(Y29,$Y$2:$Y$34,0)</f>
+        <v/>
+      </c>
+      <c r="AA29" s="7" t="inlineStr">
         <is>
           <t>라벨만</t>
         </is>
       </c>
-      <c r="AA29" s="7" t="inlineStr">
+      <c r="AB29" s="7" t="inlineStr">
         <is>
           <t>미정</t>
         </is>
       </c>
-      <c r="AB29" s="6">
+      <c r="AC29" s="6">
         <f>(IF(ISNUMBER(D29),1,0)+IF(ISNUMBER(E29),1,0)+IF(F29&lt;&gt;"미상",1,0)+IF(G29&lt;&gt;"미상",1,0)+IF(H29&lt;&gt;"미상",1,0)+IF(I29&lt;&gt;"미상",1,0)+IF(J29&lt;&gt;"미상",1,0)+IF(K29&lt;&gt;"미상",1,0)+IF(L29&lt;&gt;"미상",1,0)+IF(M29&lt;&gt;"미상",1,0)+IF(N29&lt;&gt;"미상",1,0))&amp;"/11"</f>
         <v/>
       </c>
-      <c r="AC29" s="6" t="inlineStr">
+      <c r="AD29" s="6" t="inlineStr">
         <is>
           <t>rTG·Pollack(명태/대구속 어체유=간유아님→대구상한X·일반어)·PVDC개별포장(우수)·비타민D3·per캡슐 EPA+DHA mg 미상 (dawnfactory 블로그·라벨확인필요)</t>
         </is>
@@ -4821,53 +4967,58 @@
         <f>IF(AND(J30="취약",I30&lt;&gt;"있음",OR(M30="없음",M30="미상")),"Y","N")</f>
         <v/>
       </c>
-      <c r="R30" s="8">
+      <c r="R30" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S30" s="8">
         <f>IF(NOT(ISNUMBER(D30)),0,IF(D30&gt;=300,20,IF(D30&gt;=200,15,IF(D30&gt;=100,10,5))))+IF(NOT(ISNUMBER(E30)),0,IF(E30&gt;=60,10,IF(E30&gt;=40,6,3)))+IFERROR(VLOOKUP(F30,기준!$B$4:$C$7,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="S30" s="8">
+      <c r="T30" s="8">
         <f>IFERROR(VLOOKUP(I30,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J30,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K30,기준!$B$34:$C$40,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="T30" s="8">
+      <c r="U30" s="8">
         <f>IFERROR(VLOOKUP(G30,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H30,기준!$B$16:$C$20,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="U30" s="8">
+      <c r="V30" s="8">
         <f>IFERROR(VLOOKUP(L30,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M30,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N30,기준!$B$54:$C$57,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="V30" s="8">
-        <f>SUM(R30:U30)</f>
-        <v/>
-      </c>
       <c r="W30" s="8">
-        <f>MIN(IF(O30="Y",20,100),IF(P30="Y",40,100),IF(Q30="Y",50,100))</f>
+        <f>SUM(S30:V30)</f>
         <v/>
       </c>
       <c r="X30" s="8">
-        <f>MIN(V30,W30)</f>
+        <f>MIN(IF(O30="Y",20,100),IF(P30="Y",40,100),IF(Q30="Y",50,100),IF(R30="Y",40,100))</f>
         <v/>
       </c>
       <c r="Y30" s="8">
-        <f>RANK(X30,$X$2:$X$34,0)</f>
-        <v/>
-      </c>
-      <c r="Z30" s="7" t="inlineStr">
+        <f>MIN(W30,X30)</f>
+        <v/>
+      </c>
+      <c r="Z30" s="8">
+        <f>RANK(Y30,$Y$2:$Y$34,0)</f>
+        <v/>
+      </c>
+      <c r="AA30" s="7" t="inlineStr">
         <is>
           <t>라벨만</t>
         </is>
       </c>
-      <c r="AA30" s="7" t="inlineStr">
+      <c r="AB30" s="7" t="inlineStr">
         <is>
           <t>미정</t>
         </is>
       </c>
-      <c r="AB30" s="6">
+      <c r="AC30" s="6">
         <f>(IF(ISNUMBER(D30),1,0)+IF(ISNUMBER(E30),1,0)+IF(F30&lt;&gt;"미상",1,0)+IF(G30&lt;&gt;"미상",1,0)+IF(H30&lt;&gt;"미상",1,0)+IF(I30&lt;&gt;"미상",1,0)+IF(J30&lt;&gt;"미상",1,0)+IF(K30&lt;&gt;"미상",1,0)+IF(L30&lt;&gt;"미상",1,0)+IF(M30&lt;&gt;"미상",1,0)+IF(N30&lt;&gt;"미상",1,0))&amp;"/11"</f>
         <v/>
       </c>
-      <c r="AC30" s="6" t="inlineStr">
+      <c r="AD30" s="6" t="inlineStr">
         <is>
           <t>1캡슐 EPA800+DHA400=1200mg·100%멸치어유(소형어)·rTG·IFOS5STAR·비타민D 1000IU·90캡슐(3개월) (drdoctors.co.kr/11번가/필라이즈)</t>
         </is>
@@ -4951,53 +5102,58 @@
         <f>IF(AND(J31="취약",I31&lt;&gt;"있음",OR(M31="없음",M31="미상")),"Y","N")</f>
         <v/>
       </c>
-      <c r="R31" s="8">
+      <c r="R31" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S31" s="8">
         <f>IF(NOT(ISNUMBER(D31)),0,IF(D31&gt;=300,20,IF(D31&gt;=200,15,IF(D31&gt;=100,10,5))))+IF(NOT(ISNUMBER(E31)),0,IF(E31&gt;=60,10,IF(E31&gt;=40,6,3)))+IFERROR(VLOOKUP(F31,기준!$B$4:$C$7,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="S31" s="8">
+      <c r="T31" s="8">
         <f>IFERROR(VLOOKUP(I31,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J31,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K31,기준!$B$34:$C$40,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="T31" s="8">
+      <c r="U31" s="8">
         <f>IFERROR(VLOOKUP(G31,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H31,기준!$B$16:$C$20,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="U31" s="8">
+      <c r="V31" s="8">
         <f>IFERROR(VLOOKUP(L31,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M31,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N31,기준!$B$54:$C$57,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="V31" s="8">
-        <f>SUM(R31:U31)</f>
-        <v/>
-      </c>
       <c r="W31" s="8">
-        <f>MIN(IF(O31="Y",20,100),IF(P31="Y",40,100),IF(Q31="Y",50,100))</f>
+        <f>SUM(S31:V31)</f>
         <v/>
       </c>
       <c r="X31" s="8">
-        <f>MIN(V31,W31)</f>
+        <f>MIN(IF(O31="Y",20,100),IF(P31="Y",40,100),IF(Q31="Y",50,100),IF(R31="Y",40,100))</f>
         <v/>
       </c>
       <c r="Y31" s="8">
-        <f>RANK(X31,$X$2:$X$34,0)</f>
-        <v/>
-      </c>
-      <c r="Z31" s="7" t="inlineStr">
+        <f>MIN(W31,X31)</f>
+        <v/>
+      </c>
+      <c r="Z31" s="8">
+        <f>RANK(Y31,$Y$2:$Y$34,0)</f>
+        <v/>
+      </c>
+      <c r="AA31" s="7" t="inlineStr">
         <is>
           <t>공개·검증</t>
         </is>
       </c>
-      <c r="AA31" s="7" t="inlineStr">
+      <c r="AB31" s="7" t="inlineStr">
         <is>
           <t>미정</t>
         </is>
       </c>
-      <c r="AB31" s="6">
+      <c r="AC31" s="6">
         <f>(IF(ISNUMBER(D31),1,0)+IF(ISNUMBER(E31),1,0)+IF(F31&lt;&gt;"미상",1,0)+IF(G31&lt;&gt;"미상",1,0)+IF(H31&lt;&gt;"미상",1,0)+IF(I31&lt;&gt;"미상",1,0)+IF(J31&lt;&gt;"미상",1,0)+IF(K31&lt;&gt;"미상",1,0)+IF(L31&lt;&gt;"미상",1,0)+IF(M31&lt;&gt;"미상",1,0)+IF(N31&lt;&gt;"미상",1,0))&amp;"/11"</f>
         <v/>
       </c>
-      <c r="AC31" s="6" t="inlineStr">
+      <c r="AD31" s="6" t="inlineStr">
         <is>
           <t>완제품 IFOS·EPA+DHA 980mg·rTG·KD파마 원료(원료+완제품IFOS5★)·별도SKU 1280mg 존재 (weetamin.co.kr)</t>
         </is>
@@ -5083,53 +5239,58 @@
         <f>IF(AND(J32="취약",I32&lt;&gt;"있음",OR(M32="없음",M32="미상")),"Y","N")</f>
         <v/>
       </c>
-      <c r="R32" s="8">
+      <c r="R32" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S32" s="8">
         <f>IF(NOT(ISNUMBER(D32)),0,IF(D32&gt;=300,20,IF(D32&gt;=200,15,IF(D32&gt;=100,10,5))))+IF(NOT(ISNUMBER(E32)),0,IF(E32&gt;=60,10,IF(E32&gt;=40,6,3)))+IFERROR(VLOOKUP(F32,기준!$B$4:$C$7,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="S32" s="8">
+      <c r="T32" s="8">
         <f>IFERROR(VLOOKUP(I32,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J32,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K32,기준!$B$34:$C$40,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="T32" s="8">
+      <c r="U32" s="8">
         <f>IFERROR(VLOOKUP(G32,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H32,기준!$B$16:$C$20,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="U32" s="8">
+      <c r="V32" s="8">
         <f>IFERROR(VLOOKUP(L32,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M32,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N32,기준!$B$54:$C$57,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="V32" s="8">
-        <f>SUM(R32:U32)</f>
-        <v/>
-      </c>
       <c r="W32" s="8">
-        <f>MIN(IF(O32="Y",20,100),IF(P32="Y",40,100),IF(Q32="Y",50,100))</f>
+        <f>SUM(S32:V32)</f>
         <v/>
       </c>
       <c r="X32" s="8">
-        <f>MIN(V32,W32)</f>
+        <f>MIN(IF(O32="Y",20,100),IF(P32="Y",40,100),IF(Q32="Y",50,100),IF(R32="Y",40,100))</f>
         <v/>
       </c>
       <c r="Y32" s="8">
-        <f>RANK(X32,$X$2:$X$34,0)</f>
-        <v/>
-      </c>
-      <c r="Z32" s="7" t="inlineStr">
+        <f>MIN(W32,X32)</f>
+        <v/>
+      </c>
+      <c r="Z32" s="8">
+        <f>RANK(Y32,$Y$2:$Y$34,0)</f>
+        <v/>
+      </c>
+      <c r="AA32" s="7" t="inlineStr">
         <is>
           <t>공개·검증</t>
         </is>
       </c>
-      <c r="AA32" s="7" t="inlineStr">
+      <c r="AB32" s="7" t="inlineStr">
         <is>
           <t>미정</t>
         </is>
       </c>
-      <c r="AB32" s="6">
+      <c r="AC32" s="6">
         <f>(IF(ISNUMBER(D32),1,0)+IF(ISNUMBER(E32),1,0)+IF(F32&lt;&gt;"미상",1,0)+IF(G32&lt;&gt;"미상",1,0)+IF(H32&lt;&gt;"미상",1,0)+IF(I32&lt;&gt;"미상",1,0)+IF(J32&lt;&gt;"미상",1,0)+IF(K32&lt;&gt;"미상",1,0)+IF(L32&lt;&gt;"미상",1,0)+IF(M32&lt;&gt;"미상",1,0)+IF(N32&lt;&gt;"미상",1,0))&amp;"/11"</f>
         <v/>
       </c>
-      <c r="AC32" s="6" t="inlineStr">
+      <c r="AD32" s="6" t="inlineStr">
         <is>
           <t>1캡슐 EPA180+DHA120=300mg(총500mg·순도60%)·멸치/고등어/정어리/참치·농축TG·비타민E·중금속/PCB시험 (iHerb)</t>
         </is>
@@ -5215,53 +5376,58 @@
         <f>IF(AND(J33="취약",I33&lt;&gt;"있음",OR(M33="없음",M33="미상")),"Y","N")</f>
         <v/>
       </c>
-      <c r="R33" s="8">
+      <c r="R33" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S33" s="8">
         <f>IF(NOT(ISNUMBER(D33)),0,IF(D33&gt;=300,20,IF(D33&gt;=200,15,IF(D33&gt;=100,10,5))))+IF(NOT(ISNUMBER(E33)),0,IF(E33&gt;=60,10,IF(E33&gt;=40,6,3)))+IFERROR(VLOOKUP(F33,기준!$B$4:$C$7,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="S33" s="8">
+      <c r="T33" s="8">
         <f>IFERROR(VLOOKUP(I33,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J33,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K33,기준!$B$34:$C$40,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="T33" s="8">
+      <c r="U33" s="8">
         <f>IFERROR(VLOOKUP(G33,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H33,기준!$B$16:$C$20,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="U33" s="8">
+      <c r="V33" s="8">
         <f>IFERROR(VLOOKUP(L33,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M33,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N33,기준!$B$54:$C$57,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="V33" s="8">
-        <f>SUM(R33:U33)</f>
-        <v/>
-      </c>
       <c r="W33" s="8">
-        <f>MIN(IF(O33="Y",20,100),IF(P33="Y",40,100),IF(Q33="Y",50,100))</f>
+        <f>SUM(S33:V33)</f>
         <v/>
       </c>
       <c r="X33" s="8">
-        <f>MIN(V33,W33)</f>
+        <f>MIN(IF(O33="Y",20,100),IF(P33="Y",40,100),IF(Q33="Y",50,100),IF(R33="Y",40,100))</f>
         <v/>
       </c>
       <c r="Y33" s="8">
-        <f>RANK(X33,$X$2:$X$34,0)</f>
-        <v/>
-      </c>
-      <c r="Z33" s="7" t="inlineStr">
+        <f>MIN(W33,X33)</f>
+        <v/>
+      </c>
+      <c r="Z33" s="8">
+        <f>RANK(Y33,$Y$2:$Y$34,0)</f>
+        <v/>
+      </c>
+      <c r="AA33" s="7" t="inlineStr">
         <is>
           <t>공개·검증</t>
         </is>
       </c>
-      <c r="AA33" s="7" t="inlineStr">
+      <c r="AB33" s="7" t="inlineStr">
         <is>
           <t>미정</t>
         </is>
       </c>
-      <c r="AB33" s="6">
+      <c r="AC33" s="6">
         <f>(IF(ISNUMBER(D33),1,0)+IF(ISNUMBER(E33),1,0)+IF(F33&lt;&gt;"미상",1,0)+IF(G33&lt;&gt;"미상",1,0)+IF(H33&lt;&gt;"미상",1,0)+IF(I33&lt;&gt;"미상",1,0)+IF(J33&lt;&gt;"미상",1,0)+IF(K33&lt;&gt;"미상",1,0)+IF(L33&lt;&gt;"미상",1,0)+IF(M33&lt;&gt;"미상",1,0)+IF(N33&lt;&gt;"미상",1,0))&amp;"/11"</f>
         <v/>
       </c>
-      <c r="AC33" s="6" t="inlineStr">
+      <c r="AD33" s="6" t="inlineStr">
         <is>
           <t>EPA+DHA 1000mg/1255mg캡슐(순도79.7%)·KD파마 원료·초임계rTG·완제품IFOS·비타민D 15μg·AlpiBio제조 (dambaekharu/danawa/필라이즈)</t>
         </is>
@@ -5345,53 +5511,58 @@
         <f>IF(AND(J34="취약",I34&lt;&gt;"있음",OR(M34="없음",M34="미상")),"Y","N")</f>
         <v/>
       </c>
-      <c r="R34" s="8">
+      <c r="R34" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S34" s="8">
         <f>IF(NOT(ISNUMBER(D34)),0,IF(D34&gt;=300,20,IF(D34&gt;=200,15,IF(D34&gt;=100,10,5))))+IF(NOT(ISNUMBER(E34)),0,IF(E34&gt;=60,10,IF(E34&gt;=40,6,3)))+IFERROR(VLOOKUP(F34,기준!$B$4:$C$7,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="S34" s="8">
+      <c r="T34" s="8">
         <f>IFERROR(VLOOKUP(I34,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J34,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K34,기준!$B$34:$C$40,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="T34" s="8">
+      <c r="U34" s="8">
         <f>IFERROR(VLOOKUP(G34,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H34,기준!$B$16:$C$20,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="U34" s="8">
+      <c r="V34" s="8">
         <f>IFERROR(VLOOKUP(L34,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M34,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N34,기준!$B$54:$C$57,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="V34" s="8">
-        <f>SUM(R34:U34)</f>
-        <v/>
-      </c>
       <c r="W34" s="8">
-        <f>MIN(IF(O34="Y",20,100),IF(P34="Y",40,100),IF(Q34="Y",50,100))</f>
+        <f>SUM(S34:V34)</f>
         <v/>
       </c>
       <c r="X34" s="8">
-        <f>MIN(V34,W34)</f>
+        <f>MIN(IF(O34="Y",20,100),IF(P34="Y",40,100),IF(Q34="Y",50,100),IF(R34="Y",40,100))</f>
         <v/>
       </c>
       <c r="Y34" s="8">
-        <f>RANK(X34,$X$2:$X$34,0)</f>
-        <v/>
-      </c>
-      <c r="Z34" s="7" t="inlineStr">
+        <f>MIN(W34,X34)</f>
+        <v/>
+      </c>
+      <c r="Z34" s="8">
+        <f>RANK(Y34,$Y$2:$Y$34,0)</f>
+        <v/>
+      </c>
+      <c r="AA34" s="7" t="inlineStr">
         <is>
           <t>라벨만</t>
         </is>
       </c>
-      <c r="AA34" s="7" t="inlineStr">
+      <c r="AB34" s="7" t="inlineStr">
         <is>
           <t>DHA중심(조류)</t>
         </is>
       </c>
-      <c r="AB34" s="6">
+      <c r="AC34" s="6">
         <f>(IF(ISNUMBER(D34),1,0)+IF(ISNUMBER(E34),1,0)+IF(F34&lt;&gt;"미상",1,0)+IF(G34&lt;&gt;"미상",1,0)+IF(H34&lt;&gt;"미상",1,0)+IF(I34&lt;&gt;"미상",1,0)+IF(J34&lt;&gt;"미상",1,0)+IF(K34&lt;&gt;"미상",1,0)+IF(L34&lt;&gt;"미상",1,0)+IF(M34&lt;&gt;"미상",1,0)+IF(N34&lt;&gt;"미상",1,0))&amp;"/11"</f>
         <v/>
       </c>
-      <c r="AC34" s="6" t="inlineStr">
+      <c r="AD34" s="6" t="inlineStr">
         <is>
           <t>무균배양 미세조류(DSM 원료·순도75%)·rTG·EPA/DHA 균형·상한 부적용·per캡슐mg SKU별 상이(기억력+ 900mg) (고려은단/메디파나/소셜타임스)</t>
         </is>

--- a/고양이_오메가3_제품_채점표.xlsx
+++ b/고양이_오메가3_제품_채점표.xlsx
@@ -1263,7 +1263,7 @@
         </is>
       </c>
       <c r="AC2" s="6">
-        <f>(IF(ISNUMBER(D2),1,0)+IF(ISNUMBER(E2),1,0)+IF(F2&lt;&gt;"미상",1,0)+IF(G2&lt;&gt;"미상",1,0)+IF(H2&lt;&gt;"미상",1,0)+IF(I2&lt;&gt;"미상",1,0)+IF(J2&lt;&gt;"미상",1,0)+IF(K2&lt;&gt;"미상",1,0)+IF(L2&lt;&gt;"미상",1,0)+IF(M2&lt;&gt;"미상",1,0)+IF(N2&lt;&gt;"미상",1,0))&amp;"/11"</f>
+        <f>(IF(ISNUMBER(D2),1,0)+IF(ISNUMBER(E2),1,0)+IF(AND(F2&lt;&gt;"미상",F2&lt;&gt;""),1,0)+IF(AND(G2&lt;&gt;"미상",G2&lt;&gt;""),1,0)+IF(AND(H2&lt;&gt;"미상",H2&lt;&gt;""),1,0)+IF(AND(I2&lt;&gt;"미상",I2&lt;&gt;""),1,0)+IF(AND(J2&lt;&gt;"미상",J2&lt;&gt;""),1,0)+IF(AND(K2&lt;&gt;"미상",K2&lt;&gt;""),1,0)+IF(AND(L2&lt;&gt;"미상",L2&lt;&gt;""),1,0)+IF(AND(M2&lt;&gt;"미상",M2&lt;&gt;""),1,0)+IF(AND(N2&lt;&gt;"미상",N2&lt;&gt;""),1,0))&amp;"/11"</f>
         <v/>
       </c>
       <c r="AD2" s="6" t="inlineStr">
@@ -1398,7 +1398,7 @@
         </is>
       </c>
       <c r="AC3" s="6">
-        <f>(IF(ISNUMBER(D3),1,0)+IF(ISNUMBER(E3),1,0)+IF(F3&lt;&gt;"미상",1,0)+IF(G3&lt;&gt;"미상",1,0)+IF(H3&lt;&gt;"미상",1,0)+IF(I3&lt;&gt;"미상",1,0)+IF(J3&lt;&gt;"미상",1,0)+IF(K3&lt;&gt;"미상",1,0)+IF(L3&lt;&gt;"미상",1,0)+IF(M3&lt;&gt;"미상",1,0)+IF(N3&lt;&gt;"미상",1,0))&amp;"/11"</f>
+        <f>(IF(ISNUMBER(D3),1,0)+IF(ISNUMBER(E3),1,0)+IF(AND(F3&lt;&gt;"미상",F3&lt;&gt;""),1,0)+IF(AND(G3&lt;&gt;"미상",G3&lt;&gt;""),1,0)+IF(AND(H3&lt;&gt;"미상",H3&lt;&gt;""),1,0)+IF(AND(I3&lt;&gt;"미상",I3&lt;&gt;""),1,0)+IF(AND(J3&lt;&gt;"미상",J3&lt;&gt;""),1,0)+IF(AND(K3&lt;&gt;"미상",K3&lt;&gt;""),1,0)+IF(AND(L3&lt;&gt;"미상",L3&lt;&gt;""),1,0)+IF(AND(M3&lt;&gt;"미상",M3&lt;&gt;""),1,0)+IF(AND(N3&lt;&gt;"미상",N3&lt;&gt;""),1,0))&amp;"/11"</f>
         <v/>
       </c>
       <c r="AD3" s="6" t="inlineStr">
@@ -1535,7 +1535,7 @@
         </is>
       </c>
       <c r="AC4" s="6">
-        <f>(IF(ISNUMBER(D4),1,0)+IF(ISNUMBER(E4),1,0)+IF(F4&lt;&gt;"미상",1,0)+IF(G4&lt;&gt;"미상",1,0)+IF(H4&lt;&gt;"미상",1,0)+IF(I4&lt;&gt;"미상",1,0)+IF(J4&lt;&gt;"미상",1,0)+IF(K4&lt;&gt;"미상",1,0)+IF(L4&lt;&gt;"미상",1,0)+IF(M4&lt;&gt;"미상",1,0)+IF(N4&lt;&gt;"미상",1,0))&amp;"/11"</f>
+        <f>(IF(ISNUMBER(D4),1,0)+IF(ISNUMBER(E4),1,0)+IF(AND(F4&lt;&gt;"미상",F4&lt;&gt;""),1,0)+IF(AND(G4&lt;&gt;"미상",G4&lt;&gt;""),1,0)+IF(AND(H4&lt;&gt;"미상",H4&lt;&gt;""),1,0)+IF(AND(I4&lt;&gt;"미상",I4&lt;&gt;""),1,0)+IF(AND(J4&lt;&gt;"미상",J4&lt;&gt;""),1,0)+IF(AND(K4&lt;&gt;"미상",K4&lt;&gt;""),1,0)+IF(AND(L4&lt;&gt;"미상",L4&lt;&gt;""),1,0)+IF(AND(M4&lt;&gt;"미상",M4&lt;&gt;""),1,0)+IF(AND(N4&lt;&gt;"미상",N4&lt;&gt;""),1,0))&amp;"/11"</f>
         <v/>
       </c>
       <c r="AD4" s="6" t="inlineStr">
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="AC5" s="6">
-        <f>(IF(ISNUMBER(D5),1,0)+IF(ISNUMBER(E5),1,0)+IF(F5&lt;&gt;"미상",1,0)+IF(G5&lt;&gt;"미상",1,0)+IF(H5&lt;&gt;"미상",1,0)+IF(I5&lt;&gt;"미상",1,0)+IF(J5&lt;&gt;"미상",1,0)+IF(K5&lt;&gt;"미상",1,0)+IF(L5&lt;&gt;"미상",1,0)+IF(M5&lt;&gt;"미상",1,0)+IF(N5&lt;&gt;"미상",1,0))&amp;"/11"</f>
+        <f>(IF(ISNUMBER(D5),1,0)+IF(ISNUMBER(E5),1,0)+IF(AND(F5&lt;&gt;"미상",F5&lt;&gt;""),1,0)+IF(AND(G5&lt;&gt;"미상",G5&lt;&gt;""),1,0)+IF(AND(H5&lt;&gt;"미상",H5&lt;&gt;""),1,0)+IF(AND(I5&lt;&gt;"미상",I5&lt;&gt;""),1,0)+IF(AND(J5&lt;&gt;"미상",J5&lt;&gt;""),1,0)+IF(AND(K5&lt;&gt;"미상",K5&lt;&gt;""),1,0)+IF(AND(L5&lt;&gt;"미상",L5&lt;&gt;""),1,0)+IF(AND(M5&lt;&gt;"미상",M5&lt;&gt;""),1,0)+IF(AND(N5&lt;&gt;"미상",N5&lt;&gt;""),1,0))&amp;"/11"</f>
         <v/>
       </c>
       <c r="AD5" s="6" t="inlineStr">
@@ -1809,7 +1809,7 @@
         </is>
       </c>
       <c r="AC6" s="6">
-        <f>(IF(ISNUMBER(D6),1,0)+IF(ISNUMBER(E6),1,0)+IF(F6&lt;&gt;"미상",1,0)+IF(G6&lt;&gt;"미상",1,0)+IF(H6&lt;&gt;"미상",1,0)+IF(I6&lt;&gt;"미상",1,0)+IF(J6&lt;&gt;"미상",1,0)+IF(K6&lt;&gt;"미상",1,0)+IF(L6&lt;&gt;"미상",1,0)+IF(M6&lt;&gt;"미상",1,0)+IF(N6&lt;&gt;"미상",1,0))&amp;"/11"</f>
+        <f>(IF(ISNUMBER(D6),1,0)+IF(ISNUMBER(E6),1,0)+IF(AND(F6&lt;&gt;"미상",F6&lt;&gt;""),1,0)+IF(AND(G6&lt;&gt;"미상",G6&lt;&gt;""),1,0)+IF(AND(H6&lt;&gt;"미상",H6&lt;&gt;""),1,0)+IF(AND(I6&lt;&gt;"미상",I6&lt;&gt;""),1,0)+IF(AND(J6&lt;&gt;"미상",J6&lt;&gt;""),1,0)+IF(AND(K6&lt;&gt;"미상",K6&lt;&gt;""),1,0)+IF(AND(L6&lt;&gt;"미상",L6&lt;&gt;""),1,0)+IF(AND(M6&lt;&gt;"미상",M6&lt;&gt;""),1,0)+IF(AND(N6&lt;&gt;"미상",N6&lt;&gt;""),1,0))&amp;"/11"</f>
         <v/>
       </c>
       <c r="AD6" s="6" t="inlineStr">
@@ -1946,7 +1946,7 @@
         </is>
       </c>
       <c r="AC7" s="6">
-        <f>(IF(ISNUMBER(D7),1,0)+IF(ISNUMBER(E7),1,0)+IF(F7&lt;&gt;"미상",1,0)+IF(G7&lt;&gt;"미상",1,0)+IF(H7&lt;&gt;"미상",1,0)+IF(I7&lt;&gt;"미상",1,0)+IF(J7&lt;&gt;"미상",1,0)+IF(K7&lt;&gt;"미상",1,0)+IF(L7&lt;&gt;"미상",1,0)+IF(M7&lt;&gt;"미상",1,0)+IF(N7&lt;&gt;"미상",1,0))&amp;"/11"</f>
+        <f>(IF(ISNUMBER(D7),1,0)+IF(ISNUMBER(E7),1,0)+IF(AND(F7&lt;&gt;"미상",F7&lt;&gt;""),1,0)+IF(AND(G7&lt;&gt;"미상",G7&lt;&gt;""),1,0)+IF(AND(H7&lt;&gt;"미상",H7&lt;&gt;""),1,0)+IF(AND(I7&lt;&gt;"미상",I7&lt;&gt;""),1,0)+IF(AND(J7&lt;&gt;"미상",J7&lt;&gt;""),1,0)+IF(AND(K7&lt;&gt;"미상",K7&lt;&gt;""),1,0)+IF(AND(L7&lt;&gt;"미상",L7&lt;&gt;""),1,0)+IF(AND(M7&lt;&gt;"미상",M7&lt;&gt;""),1,0)+IF(AND(N7&lt;&gt;"미상",N7&lt;&gt;""),1,0))&amp;"/11"</f>
         <v/>
       </c>
       <c r="AD7" s="6" t="inlineStr">
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="AC8" s="6">
-        <f>(IF(ISNUMBER(D8),1,0)+IF(ISNUMBER(E8),1,0)+IF(F8&lt;&gt;"미상",1,0)+IF(G8&lt;&gt;"미상",1,0)+IF(H8&lt;&gt;"미상",1,0)+IF(I8&lt;&gt;"미상",1,0)+IF(J8&lt;&gt;"미상",1,0)+IF(K8&lt;&gt;"미상",1,0)+IF(L8&lt;&gt;"미상",1,0)+IF(M8&lt;&gt;"미상",1,0)+IF(N8&lt;&gt;"미상",1,0))&amp;"/11"</f>
+        <f>(IF(ISNUMBER(D8),1,0)+IF(ISNUMBER(E8),1,0)+IF(AND(F8&lt;&gt;"미상",F8&lt;&gt;""),1,0)+IF(AND(G8&lt;&gt;"미상",G8&lt;&gt;""),1,0)+IF(AND(H8&lt;&gt;"미상",H8&lt;&gt;""),1,0)+IF(AND(I8&lt;&gt;"미상",I8&lt;&gt;""),1,0)+IF(AND(J8&lt;&gt;"미상",J8&lt;&gt;""),1,0)+IF(AND(K8&lt;&gt;"미상",K8&lt;&gt;""),1,0)+IF(AND(L8&lt;&gt;"미상",L8&lt;&gt;""),1,0)+IF(AND(M8&lt;&gt;"미상",M8&lt;&gt;""),1,0)+IF(AND(N8&lt;&gt;"미상",N8&lt;&gt;""),1,0))&amp;"/11"</f>
         <v/>
       </c>
       <c r="AD8" s="6" t="inlineStr">
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="AC9" s="6">
-        <f>(IF(ISNUMBER(D9),1,0)+IF(ISNUMBER(E9),1,0)+IF(F9&lt;&gt;"미상",1,0)+IF(G9&lt;&gt;"미상",1,0)+IF(H9&lt;&gt;"미상",1,0)+IF(I9&lt;&gt;"미상",1,0)+IF(J9&lt;&gt;"미상",1,0)+IF(K9&lt;&gt;"미상",1,0)+IF(L9&lt;&gt;"미상",1,0)+IF(M9&lt;&gt;"미상",1,0)+IF(N9&lt;&gt;"미상",1,0))&amp;"/11"</f>
+        <f>(IF(ISNUMBER(D9),1,0)+IF(ISNUMBER(E9),1,0)+IF(AND(F9&lt;&gt;"미상",F9&lt;&gt;""),1,0)+IF(AND(G9&lt;&gt;"미상",G9&lt;&gt;""),1,0)+IF(AND(H9&lt;&gt;"미상",H9&lt;&gt;""),1,0)+IF(AND(I9&lt;&gt;"미상",I9&lt;&gt;""),1,0)+IF(AND(J9&lt;&gt;"미상",J9&lt;&gt;""),1,0)+IF(AND(K9&lt;&gt;"미상",K9&lt;&gt;""),1,0)+IF(AND(L9&lt;&gt;"미상",L9&lt;&gt;""),1,0)+IF(AND(M9&lt;&gt;"미상",M9&lt;&gt;""),1,0)+IF(AND(N9&lt;&gt;"미상",N9&lt;&gt;""),1,0))&amp;"/11"</f>
         <v/>
       </c>
       <c r="AD9" s="6" t="inlineStr">
@@ -2345,7 +2345,7 @@
         </is>
       </c>
       <c r="AC10" s="6">
-        <f>(IF(ISNUMBER(D10),1,0)+IF(ISNUMBER(E10),1,0)+IF(F10&lt;&gt;"미상",1,0)+IF(G10&lt;&gt;"미상",1,0)+IF(H10&lt;&gt;"미상",1,0)+IF(I10&lt;&gt;"미상",1,0)+IF(J10&lt;&gt;"미상",1,0)+IF(K10&lt;&gt;"미상",1,0)+IF(L10&lt;&gt;"미상",1,0)+IF(M10&lt;&gt;"미상",1,0)+IF(N10&lt;&gt;"미상",1,0))&amp;"/11"</f>
+        <f>(IF(ISNUMBER(D10),1,0)+IF(ISNUMBER(E10),1,0)+IF(AND(F10&lt;&gt;"미상",F10&lt;&gt;""),1,0)+IF(AND(G10&lt;&gt;"미상",G10&lt;&gt;""),1,0)+IF(AND(H10&lt;&gt;"미상",H10&lt;&gt;""),1,0)+IF(AND(I10&lt;&gt;"미상",I10&lt;&gt;""),1,0)+IF(AND(J10&lt;&gt;"미상",J10&lt;&gt;""),1,0)+IF(AND(K10&lt;&gt;"미상",K10&lt;&gt;""),1,0)+IF(AND(L10&lt;&gt;"미상",L10&lt;&gt;""),1,0)+IF(AND(M10&lt;&gt;"미상",M10&lt;&gt;""),1,0)+IF(AND(N10&lt;&gt;"미상",N10&lt;&gt;""),1,0))&amp;"/11"</f>
         <v/>
       </c>
       <c r="AD10" s="6" t="inlineStr">
@@ -2478,7 +2478,7 @@
         </is>
       </c>
       <c r="AC11" s="6">
-        <f>(IF(ISNUMBER(D11),1,0)+IF(ISNUMBER(E11),1,0)+IF(F11&lt;&gt;"미상",1,0)+IF(G11&lt;&gt;"미상",1,0)+IF(H11&lt;&gt;"미상",1,0)+IF(I11&lt;&gt;"미상",1,0)+IF(J11&lt;&gt;"미상",1,0)+IF(K11&lt;&gt;"미상",1,0)+IF(L11&lt;&gt;"미상",1,0)+IF(M11&lt;&gt;"미상",1,0)+IF(N11&lt;&gt;"미상",1,0))&amp;"/11"</f>
+        <f>(IF(ISNUMBER(D11),1,0)+IF(ISNUMBER(E11),1,0)+IF(AND(F11&lt;&gt;"미상",F11&lt;&gt;""),1,0)+IF(AND(G11&lt;&gt;"미상",G11&lt;&gt;""),1,0)+IF(AND(H11&lt;&gt;"미상",H11&lt;&gt;""),1,0)+IF(AND(I11&lt;&gt;"미상",I11&lt;&gt;""),1,0)+IF(AND(J11&lt;&gt;"미상",J11&lt;&gt;""),1,0)+IF(AND(K11&lt;&gt;"미상",K11&lt;&gt;""),1,0)+IF(AND(L11&lt;&gt;"미상",L11&lt;&gt;""),1,0)+IF(AND(M11&lt;&gt;"미상",M11&lt;&gt;""),1,0)+IF(AND(N11&lt;&gt;"미상",N11&lt;&gt;""),1,0))&amp;"/11"</f>
         <v/>
       </c>
       <c r="AD11" s="6" t="inlineStr">
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="AC12" s="6">
-        <f>(IF(ISNUMBER(D12),1,0)+IF(ISNUMBER(E12),1,0)+IF(F12&lt;&gt;"미상",1,0)+IF(G12&lt;&gt;"미상",1,0)+IF(H12&lt;&gt;"미상",1,0)+IF(I12&lt;&gt;"미상",1,0)+IF(J12&lt;&gt;"미상",1,0)+IF(K12&lt;&gt;"미상",1,0)+IF(L12&lt;&gt;"미상",1,0)+IF(M12&lt;&gt;"미상",1,0)+IF(N12&lt;&gt;"미상",1,0))&amp;"/11"</f>
+        <f>(IF(ISNUMBER(D12),1,0)+IF(ISNUMBER(E12),1,0)+IF(AND(F12&lt;&gt;"미상",F12&lt;&gt;""),1,0)+IF(AND(G12&lt;&gt;"미상",G12&lt;&gt;""),1,0)+IF(AND(H12&lt;&gt;"미상",H12&lt;&gt;""),1,0)+IF(AND(I12&lt;&gt;"미상",I12&lt;&gt;""),1,0)+IF(AND(J12&lt;&gt;"미상",J12&lt;&gt;""),1,0)+IF(AND(K12&lt;&gt;"미상",K12&lt;&gt;""),1,0)+IF(AND(L12&lt;&gt;"미상",L12&lt;&gt;""),1,0)+IF(AND(M12&lt;&gt;"미상",M12&lt;&gt;""),1,0)+IF(AND(N12&lt;&gt;"미상",N12&lt;&gt;""),1,0))&amp;"/11"</f>
         <v/>
       </c>
       <c r="AD12" s="6" t="inlineStr">
@@ -2744,7 +2744,7 @@
         </is>
       </c>
       <c r="AC13" s="6">
-        <f>(IF(ISNUMBER(D13),1,0)+IF(ISNUMBER(E13),1,0)+IF(F13&lt;&gt;"미상",1,0)+IF(G13&lt;&gt;"미상",1,0)+IF(H13&lt;&gt;"미상",1,0)+IF(I13&lt;&gt;"미상",1,0)+IF(J13&lt;&gt;"미상",1,0)+IF(K13&lt;&gt;"미상",1,0)+IF(L13&lt;&gt;"미상",1,0)+IF(M13&lt;&gt;"미상",1,0)+IF(N13&lt;&gt;"미상",1,0))&amp;"/11"</f>
+        <f>(IF(ISNUMBER(D13),1,0)+IF(ISNUMBER(E13),1,0)+IF(AND(F13&lt;&gt;"미상",F13&lt;&gt;""),1,0)+IF(AND(G13&lt;&gt;"미상",G13&lt;&gt;""),1,0)+IF(AND(H13&lt;&gt;"미상",H13&lt;&gt;""),1,0)+IF(AND(I13&lt;&gt;"미상",I13&lt;&gt;""),1,0)+IF(AND(J13&lt;&gt;"미상",J13&lt;&gt;""),1,0)+IF(AND(K13&lt;&gt;"미상",K13&lt;&gt;""),1,0)+IF(AND(L13&lt;&gt;"미상",L13&lt;&gt;""),1,0)+IF(AND(M13&lt;&gt;"미상",M13&lt;&gt;""),1,0)+IF(AND(N13&lt;&gt;"미상",N13&lt;&gt;""),1,0))&amp;"/11"</f>
         <v/>
       </c>
       <c r="AD13" s="6" t="inlineStr">
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="AC14" s="6">
-        <f>(IF(ISNUMBER(D14),1,0)+IF(ISNUMBER(E14),1,0)+IF(F14&lt;&gt;"미상",1,0)+IF(G14&lt;&gt;"미상",1,0)+IF(H14&lt;&gt;"미상",1,0)+IF(I14&lt;&gt;"미상",1,0)+IF(J14&lt;&gt;"미상",1,0)+IF(K14&lt;&gt;"미상",1,0)+IF(L14&lt;&gt;"미상",1,0)+IF(M14&lt;&gt;"미상",1,0)+IF(N14&lt;&gt;"미상",1,0))&amp;"/11"</f>
+        <f>(IF(ISNUMBER(D14),1,0)+IF(ISNUMBER(E14),1,0)+IF(AND(F14&lt;&gt;"미상",F14&lt;&gt;""),1,0)+IF(AND(G14&lt;&gt;"미상",G14&lt;&gt;""),1,0)+IF(AND(H14&lt;&gt;"미상",H14&lt;&gt;""),1,0)+IF(AND(I14&lt;&gt;"미상",I14&lt;&gt;""),1,0)+IF(AND(J14&lt;&gt;"미상",J14&lt;&gt;""),1,0)+IF(AND(K14&lt;&gt;"미상",K14&lt;&gt;""),1,0)+IF(AND(L14&lt;&gt;"미상",L14&lt;&gt;""),1,0)+IF(AND(M14&lt;&gt;"미상",M14&lt;&gt;""),1,0)+IF(AND(N14&lt;&gt;"미상",N14&lt;&gt;""),1,0))&amp;"/11"</f>
         <v/>
       </c>
       <c r="AD14" s="6" t="inlineStr">
@@ -3010,7 +3010,7 @@
         </is>
       </c>
       <c r="AC15" s="6">
-        <f>(IF(ISNUMBER(D15),1,0)+IF(ISNUMBER(E15),1,0)+IF(F15&lt;&gt;"미상",1,0)+IF(G15&lt;&gt;"미상",1,0)+IF(H15&lt;&gt;"미상",1,0)+IF(I15&lt;&gt;"미상",1,0)+IF(J15&lt;&gt;"미상",1,0)+IF(K15&lt;&gt;"미상",1,0)+IF(L15&lt;&gt;"미상",1,0)+IF(M15&lt;&gt;"미상",1,0)+IF(N15&lt;&gt;"미상",1,0))&amp;"/11"</f>
+        <f>(IF(ISNUMBER(D15),1,0)+IF(ISNUMBER(E15),1,0)+IF(AND(F15&lt;&gt;"미상",F15&lt;&gt;""),1,0)+IF(AND(G15&lt;&gt;"미상",G15&lt;&gt;""),1,0)+IF(AND(H15&lt;&gt;"미상",H15&lt;&gt;""),1,0)+IF(AND(I15&lt;&gt;"미상",I15&lt;&gt;""),1,0)+IF(AND(J15&lt;&gt;"미상",J15&lt;&gt;""),1,0)+IF(AND(K15&lt;&gt;"미상",K15&lt;&gt;""),1,0)+IF(AND(L15&lt;&gt;"미상",L15&lt;&gt;""),1,0)+IF(AND(M15&lt;&gt;"미상",M15&lt;&gt;""),1,0)+IF(AND(N15&lt;&gt;"미상",N15&lt;&gt;""),1,0))&amp;"/11"</f>
         <v/>
       </c>
       <c r="AD15" s="6" t="inlineStr">
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="AC16" s="6">
-        <f>(IF(ISNUMBER(D16),1,0)+IF(ISNUMBER(E16),1,0)+IF(F16&lt;&gt;"미상",1,0)+IF(G16&lt;&gt;"미상",1,0)+IF(H16&lt;&gt;"미상",1,0)+IF(I16&lt;&gt;"미상",1,0)+IF(J16&lt;&gt;"미상",1,0)+IF(K16&lt;&gt;"미상",1,0)+IF(L16&lt;&gt;"미상",1,0)+IF(M16&lt;&gt;"미상",1,0)+IF(N16&lt;&gt;"미상",1,0))&amp;"/11"</f>
+        <f>(IF(ISNUMBER(D16),1,0)+IF(ISNUMBER(E16),1,0)+IF(AND(F16&lt;&gt;"미상",F16&lt;&gt;""),1,0)+IF(AND(G16&lt;&gt;"미상",G16&lt;&gt;""),1,0)+IF(AND(H16&lt;&gt;"미상",H16&lt;&gt;""),1,0)+IF(AND(I16&lt;&gt;"미상",I16&lt;&gt;""),1,0)+IF(AND(J16&lt;&gt;"미상",J16&lt;&gt;""),1,0)+IF(AND(K16&lt;&gt;"미상",K16&lt;&gt;""),1,0)+IF(AND(L16&lt;&gt;"미상",L16&lt;&gt;""),1,0)+IF(AND(M16&lt;&gt;"미상",M16&lt;&gt;""),1,0)+IF(AND(N16&lt;&gt;"미상",N16&lt;&gt;""),1,0))&amp;"/11"</f>
         <v/>
       </c>
       <c r="AD16" s="6" t="inlineStr">
@@ -3276,7 +3276,7 @@
         </is>
       </c>
       <c r="AC17" s="6">
-        <f>(IF(ISNUMBER(D17),1,0)+IF(ISNUMBER(E17),1,0)+IF(F17&lt;&gt;"미상",1,0)+IF(G17&lt;&gt;"미상",1,0)+IF(H17&lt;&gt;"미상",1,0)+IF(I17&lt;&gt;"미상",1,0)+IF(J17&lt;&gt;"미상",1,0)+IF(K17&lt;&gt;"미상",1,0)+IF(L17&lt;&gt;"미상",1,0)+IF(M17&lt;&gt;"미상",1,0)+IF(N17&lt;&gt;"미상",1,0))&amp;"/11"</f>
+        <f>(IF(ISNUMBER(D17),1,0)+IF(ISNUMBER(E17),1,0)+IF(AND(F17&lt;&gt;"미상",F17&lt;&gt;""),1,0)+IF(AND(G17&lt;&gt;"미상",G17&lt;&gt;""),1,0)+IF(AND(H17&lt;&gt;"미상",H17&lt;&gt;""),1,0)+IF(AND(I17&lt;&gt;"미상",I17&lt;&gt;""),1,0)+IF(AND(J17&lt;&gt;"미상",J17&lt;&gt;""),1,0)+IF(AND(K17&lt;&gt;"미상",K17&lt;&gt;""),1,0)+IF(AND(L17&lt;&gt;"미상",L17&lt;&gt;""),1,0)+IF(AND(M17&lt;&gt;"미상",M17&lt;&gt;""),1,0)+IF(AND(N17&lt;&gt;"미상",N17&lt;&gt;""),1,0))&amp;"/11"</f>
         <v/>
       </c>
       <c r="AD17" s="6" t="inlineStr">
@@ -3409,7 +3409,7 @@
         </is>
       </c>
       <c r="AC18" s="6">
-        <f>(IF(ISNUMBER(D18),1,0)+IF(ISNUMBER(E18),1,0)+IF(F18&lt;&gt;"미상",1,0)+IF(G18&lt;&gt;"미상",1,0)+IF(H18&lt;&gt;"미상",1,0)+IF(I18&lt;&gt;"미상",1,0)+IF(J18&lt;&gt;"미상",1,0)+IF(K18&lt;&gt;"미상",1,0)+IF(L18&lt;&gt;"미상",1,0)+IF(M18&lt;&gt;"미상",1,0)+IF(N18&lt;&gt;"미상",1,0))&amp;"/11"</f>
+        <f>(IF(ISNUMBER(D18),1,0)+IF(ISNUMBER(E18),1,0)+IF(AND(F18&lt;&gt;"미상",F18&lt;&gt;""),1,0)+IF(AND(G18&lt;&gt;"미상",G18&lt;&gt;""),1,0)+IF(AND(H18&lt;&gt;"미상",H18&lt;&gt;""),1,0)+IF(AND(I18&lt;&gt;"미상",I18&lt;&gt;""),1,0)+IF(AND(J18&lt;&gt;"미상",J18&lt;&gt;""),1,0)+IF(AND(K18&lt;&gt;"미상",K18&lt;&gt;""),1,0)+IF(AND(L18&lt;&gt;"미상",L18&lt;&gt;""),1,0)+IF(AND(M18&lt;&gt;"미상",M18&lt;&gt;""),1,0)+IF(AND(N18&lt;&gt;"미상",N18&lt;&gt;""),1,0))&amp;"/11"</f>
         <v/>
       </c>
       <c r="AD18" s="6" t="inlineStr">
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="AC19" s="6">
-        <f>(IF(ISNUMBER(D19),1,0)+IF(ISNUMBER(E19),1,0)+IF(F19&lt;&gt;"미상",1,0)+IF(G19&lt;&gt;"미상",1,0)+IF(H19&lt;&gt;"미상",1,0)+IF(I19&lt;&gt;"미상",1,0)+IF(J19&lt;&gt;"미상",1,0)+IF(K19&lt;&gt;"미상",1,0)+IF(L19&lt;&gt;"미상",1,0)+IF(M19&lt;&gt;"미상",1,0)+IF(N19&lt;&gt;"미상",1,0))&amp;"/11"</f>
+        <f>(IF(ISNUMBER(D19),1,0)+IF(ISNUMBER(E19),1,0)+IF(AND(F19&lt;&gt;"미상",F19&lt;&gt;""),1,0)+IF(AND(G19&lt;&gt;"미상",G19&lt;&gt;""),1,0)+IF(AND(H19&lt;&gt;"미상",H19&lt;&gt;""),1,0)+IF(AND(I19&lt;&gt;"미상",I19&lt;&gt;""),1,0)+IF(AND(J19&lt;&gt;"미상",J19&lt;&gt;""),1,0)+IF(AND(K19&lt;&gt;"미상",K19&lt;&gt;""),1,0)+IF(AND(L19&lt;&gt;"미상",L19&lt;&gt;""),1,0)+IF(AND(M19&lt;&gt;"미상",M19&lt;&gt;""),1,0)+IF(AND(N19&lt;&gt;"미상",N19&lt;&gt;""),1,0))&amp;"/11"</f>
         <v/>
       </c>
       <c r="AD19" s="6" t="inlineStr">
@@ -3675,7 +3675,7 @@
         </is>
       </c>
       <c r="AC20" s="6">
-        <f>(IF(ISNUMBER(D20),1,0)+IF(ISNUMBER(E20),1,0)+IF(F20&lt;&gt;"미상",1,0)+IF(G20&lt;&gt;"미상",1,0)+IF(H20&lt;&gt;"미상",1,0)+IF(I20&lt;&gt;"미상",1,0)+IF(J20&lt;&gt;"미상",1,0)+IF(K20&lt;&gt;"미상",1,0)+IF(L20&lt;&gt;"미상",1,0)+IF(M20&lt;&gt;"미상",1,0)+IF(N20&lt;&gt;"미상",1,0))&amp;"/11"</f>
+        <f>(IF(ISNUMBER(D20),1,0)+IF(ISNUMBER(E20),1,0)+IF(AND(F20&lt;&gt;"미상",F20&lt;&gt;""),1,0)+IF(AND(G20&lt;&gt;"미상",G20&lt;&gt;""),1,0)+IF(AND(H20&lt;&gt;"미상",H20&lt;&gt;""),1,0)+IF(AND(I20&lt;&gt;"미상",I20&lt;&gt;""),1,0)+IF(AND(J20&lt;&gt;"미상",J20&lt;&gt;""),1,0)+IF(AND(K20&lt;&gt;"미상",K20&lt;&gt;""),1,0)+IF(AND(L20&lt;&gt;"미상",L20&lt;&gt;""),1,0)+IF(AND(M20&lt;&gt;"미상",M20&lt;&gt;""),1,0)+IF(AND(N20&lt;&gt;"미상",N20&lt;&gt;""),1,0))&amp;"/11"</f>
         <v/>
       </c>
       <c r="AD20" s="6" t="inlineStr">
@@ -3808,7 +3808,7 @@
         </is>
       </c>
       <c r="AC21" s="6">
-        <f>(IF(ISNUMBER(D21),1,0)+IF(ISNUMBER(E21),1,0)+IF(F21&lt;&gt;"미상",1,0)+IF(G21&lt;&gt;"미상",1,0)+IF(H21&lt;&gt;"미상",1,0)+IF(I21&lt;&gt;"미상",1,0)+IF(J21&lt;&gt;"미상",1,0)+IF(K21&lt;&gt;"미상",1,0)+IF(L21&lt;&gt;"미상",1,0)+IF(M21&lt;&gt;"미상",1,0)+IF(N21&lt;&gt;"미상",1,0))&amp;"/11"</f>
+        <f>(IF(ISNUMBER(D21),1,0)+IF(ISNUMBER(E21),1,0)+IF(AND(F21&lt;&gt;"미상",F21&lt;&gt;""),1,0)+IF(AND(G21&lt;&gt;"미상",G21&lt;&gt;""),1,0)+IF(AND(H21&lt;&gt;"미상",H21&lt;&gt;""),1,0)+IF(AND(I21&lt;&gt;"미상",I21&lt;&gt;""),1,0)+IF(AND(J21&lt;&gt;"미상",J21&lt;&gt;""),1,0)+IF(AND(K21&lt;&gt;"미상",K21&lt;&gt;""),1,0)+IF(AND(L21&lt;&gt;"미상",L21&lt;&gt;""),1,0)+IF(AND(M21&lt;&gt;"미상",M21&lt;&gt;""),1,0)+IF(AND(N21&lt;&gt;"미상",N21&lt;&gt;""),1,0))&amp;"/11"</f>
         <v/>
       </c>
       <c r="AD21" s="6" t="inlineStr">
@@ -3941,7 +3941,7 @@
         </is>
       </c>
       <c r="AC22" s="6">
-        <f>(IF(ISNUMBER(D22),1,0)+IF(ISNUMBER(E22),1,0)+IF(F22&lt;&gt;"미상",1,0)+IF(G22&lt;&gt;"미상",1,0)+IF(H22&lt;&gt;"미상",1,0)+IF(I22&lt;&gt;"미상",1,0)+IF(J22&lt;&gt;"미상",1,0)+IF(K22&lt;&gt;"미상",1,0)+IF(L22&lt;&gt;"미상",1,0)+IF(M22&lt;&gt;"미상",1,0)+IF(N22&lt;&gt;"미상",1,0))&amp;"/11"</f>
+        <f>(IF(ISNUMBER(D22),1,0)+IF(ISNUMBER(E22),1,0)+IF(AND(F22&lt;&gt;"미상",F22&lt;&gt;""),1,0)+IF(AND(G22&lt;&gt;"미상",G22&lt;&gt;""),1,0)+IF(AND(H22&lt;&gt;"미상",H22&lt;&gt;""),1,0)+IF(AND(I22&lt;&gt;"미상",I22&lt;&gt;""),1,0)+IF(AND(J22&lt;&gt;"미상",J22&lt;&gt;""),1,0)+IF(AND(K22&lt;&gt;"미상",K22&lt;&gt;""),1,0)+IF(AND(L22&lt;&gt;"미상",L22&lt;&gt;""),1,0)+IF(AND(M22&lt;&gt;"미상",M22&lt;&gt;""),1,0)+IF(AND(N22&lt;&gt;"미상",N22&lt;&gt;""),1,0))&amp;"/11"</f>
         <v/>
       </c>
       <c r="AD22" s="6" t="inlineStr">
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="AC23" s="6">
-        <f>(IF(ISNUMBER(D23),1,0)+IF(ISNUMBER(E23),1,0)+IF(F23&lt;&gt;"미상",1,0)+IF(G23&lt;&gt;"미상",1,0)+IF(H23&lt;&gt;"미상",1,0)+IF(I23&lt;&gt;"미상",1,0)+IF(J23&lt;&gt;"미상",1,0)+IF(K23&lt;&gt;"미상",1,0)+IF(L23&lt;&gt;"미상",1,0)+IF(M23&lt;&gt;"미상",1,0)+IF(N23&lt;&gt;"미상",1,0))&amp;"/11"</f>
+        <f>(IF(ISNUMBER(D23),1,0)+IF(ISNUMBER(E23),1,0)+IF(AND(F23&lt;&gt;"미상",F23&lt;&gt;""),1,0)+IF(AND(G23&lt;&gt;"미상",G23&lt;&gt;""),1,0)+IF(AND(H23&lt;&gt;"미상",H23&lt;&gt;""),1,0)+IF(AND(I23&lt;&gt;"미상",I23&lt;&gt;""),1,0)+IF(AND(J23&lt;&gt;"미상",J23&lt;&gt;""),1,0)+IF(AND(K23&lt;&gt;"미상",K23&lt;&gt;""),1,0)+IF(AND(L23&lt;&gt;"미상",L23&lt;&gt;""),1,0)+IF(AND(M23&lt;&gt;"미상",M23&lt;&gt;""),1,0)+IF(AND(N23&lt;&gt;"미상",N23&lt;&gt;""),1,0))&amp;"/11"</f>
         <v/>
       </c>
       <c r="AD23" s="6" t="inlineStr">
@@ -4209,7 +4209,7 @@
         </is>
       </c>
       <c r="AC24" s="6">
-        <f>(IF(ISNUMBER(D24),1,0)+IF(ISNUMBER(E24),1,0)+IF(F24&lt;&gt;"미상",1,0)+IF(G24&lt;&gt;"미상",1,0)+IF(H24&lt;&gt;"미상",1,0)+IF(I24&lt;&gt;"미상",1,0)+IF(J24&lt;&gt;"미상",1,0)+IF(K24&lt;&gt;"미상",1,0)+IF(L24&lt;&gt;"미상",1,0)+IF(M24&lt;&gt;"미상",1,0)+IF(N24&lt;&gt;"미상",1,0))&amp;"/11"</f>
+        <f>(IF(ISNUMBER(D24),1,0)+IF(ISNUMBER(E24),1,0)+IF(AND(F24&lt;&gt;"미상",F24&lt;&gt;""),1,0)+IF(AND(G24&lt;&gt;"미상",G24&lt;&gt;""),1,0)+IF(AND(H24&lt;&gt;"미상",H24&lt;&gt;""),1,0)+IF(AND(I24&lt;&gt;"미상",I24&lt;&gt;""),1,0)+IF(AND(J24&lt;&gt;"미상",J24&lt;&gt;""),1,0)+IF(AND(K24&lt;&gt;"미상",K24&lt;&gt;""),1,0)+IF(AND(L24&lt;&gt;"미상",L24&lt;&gt;""),1,0)+IF(AND(M24&lt;&gt;"미상",M24&lt;&gt;""),1,0)+IF(AND(N24&lt;&gt;"미상",N24&lt;&gt;""),1,0))&amp;"/11"</f>
         <v/>
       </c>
       <c r="AD24" s="6" t="inlineStr">
@@ -4342,7 +4342,7 @@
         </is>
       </c>
       <c r="AC25" s="6">
-        <f>(IF(ISNUMBER(D25),1,0)+IF(ISNUMBER(E25),1,0)+IF(F25&lt;&gt;"미상",1,0)+IF(G25&lt;&gt;"미상",1,0)+IF(H25&lt;&gt;"미상",1,0)+IF(I25&lt;&gt;"미상",1,0)+IF(J25&lt;&gt;"미상",1,0)+IF(K25&lt;&gt;"미상",1,0)+IF(L25&lt;&gt;"미상",1,0)+IF(M25&lt;&gt;"미상",1,0)+IF(N25&lt;&gt;"미상",1,0))&amp;"/11"</f>
+        <f>(IF(ISNUMBER(D25),1,0)+IF(ISNUMBER(E25),1,0)+IF(AND(F25&lt;&gt;"미상",F25&lt;&gt;""),1,0)+IF(AND(G25&lt;&gt;"미상",G25&lt;&gt;""),1,0)+IF(AND(H25&lt;&gt;"미상",H25&lt;&gt;""),1,0)+IF(AND(I25&lt;&gt;"미상",I25&lt;&gt;""),1,0)+IF(AND(J25&lt;&gt;"미상",J25&lt;&gt;""),1,0)+IF(AND(K25&lt;&gt;"미상",K25&lt;&gt;""),1,0)+IF(AND(L25&lt;&gt;"미상",L25&lt;&gt;""),1,0)+IF(AND(M25&lt;&gt;"미상",M25&lt;&gt;""),1,0)+IF(AND(N25&lt;&gt;"미상",N25&lt;&gt;""),1,0))&amp;"/11"</f>
         <v/>
       </c>
       <c r="AD25" s="6" t="inlineStr">
@@ -4475,7 +4475,7 @@
         </is>
       </c>
       <c r="AC26" s="6">
-        <f>(IF(ISNUMBER(D26),1,0)+IF(ISNUMBER(E26),1,0)+IF(F26&lt;&gt;"미상",1,0)+IF(G26&lt;&gt;"미상",1,0)+IF(H26&lt;&gt;"미상",1,0)+IF(I26&lt;&gt;"미상",1,0)+IF(J26&lt;&gt;"미상",1,0)+IF(K26&lt;&gt;"미상",1,0)+IF(L26&lt;&gt;"미상",1,0)+IF(M26&lt;&gt;"미상",1,0)+IF(N26&lt;&gt;"미상",1,0))&amp;"/11"</f>
+        <f>(IF(ISNUMBER(D26),1,0)+IF(ISNUMBER(E26),1,0)+IF(AND(F26&lt;&gt;"미상",F26&lt;&gt;""),1,0)+IF(AND(G26&lt;&gt;"미상",G26&lt;&gt;""),1,0)+IF(AND(H26&lt;&gt;"미상",H26&lt;&gt;""),1,0)+IF(AND(I26&lt;&gt;"미상",I26&lt;&gt;""),1,0)+IF(AND(J26&lt;&gt;"미상",J26&lt;&gt;""),1,0)+IF(AND(K26&lt;&gt;"미상",K26&lt;&gt;""),1,0)+IF(AND(L26&lt;&gt;"미상",L26&lt;&gt;""),1,0)+IF(AND(M26&lt;&gt;"미상",M26&lt;&gt;""),1,0)+IF(AND(N26&lt;&gt;"미상",N26&lt;&gt;""),1,0))&amp;"/11"</f>
         <v/>
       </c>
       <c r="AD26" s="6" t="inlineStr">
@@ -4612,7 +4612,7 @@
         </is>
       </c>
       <c r="AC27" s="6">
-        <f>(IF(ISNUMBER(D27),1,0)+IF(ISNUMBER(E27),1,0)+IF(F27&lt;&gt;"미상",1,0)+IF(G27&lt;&gt;"미상",1,0)+IF(H27&lt;&gt;"미상",1,0)+IF(I27&lt;&gt;"미상",1,0)+IF(J27&lt;&gt;"미상",1,0)+IF(K27&lt;&gt;"미상",1,0)+IF(L27&lt;&gt;"미상",1,0)+IF(M27&lt;&gt;"미상",1,0)+IF(N27&lt;&gt;"미상",1,0))&amp;"/11"</f>
+        <f>(IF(ISNUMBER(D27),1,0)+IF(ISNUMBER(E27),1,0)+IF(AND(F27&lt;&gt;"미상",F27&lt;&gt;""),1,0)+IF(AND(G27&lt;&gt;"미상",G27&lt;&gt;""),1,0)+IF(AND(H27&lt;&gt;"미상",H27&lt;&gt;""),1,0)+IF(AND(I27&lt;&gt;"미상",I27&lt;&gt;""),1,0)+IF(AND(J27&lt;&gt;"미상",J27&lt;&gt;""),1,0)+IF(AND(K27&lt;&gt;"미상",K27&lt;&gt;""),1,0)+IF(AND(L27&lt;&gt;"미상",L27&lt;&gt;""),1,0)+IF(AND(M27&lt;&gt;"미상",M27&lt;&gt;""),1,0)+IF(AND(N27&lt;&gt;"미상",N27&lt;&gt;""),1,0))&amp;"/11"</f>
         <v/>
       </c>
       <c r="AD27" s="6" t="inlineStr">
@@ -4747,7 +4747,7 @@
         </is>
       </c>
       <c r="AC28" s="6">
-        <f>(IF(ISNUMBER(D28),1,0)+IF(ISNUMBER(E28),1,0)+IF(F28&lt;&gt;"미상",1,0)+IF(G28&lt;&gt;"미상",1,0)+IF(H28&lt;&gt;"미상",1,0)+IF(I28&lt;&gt;"미상",1,0)+IF(J28&lt;&gt;"미상",1,0)+IF(K28&lt;&gt;"미상",1,0)+IF(L28&lt;&gt;"미상",1,0)+IF(M28&lt;&gt;"미상",1,0)+IF(N28&lt;&gt;"미상",1,0))&amp;"/11"</f>
+        <f>(IF(ISNUMBER(D28),1,0)+IF(ISNUMBER(E28),1,0)+IF(AND(F28&lt;&gt;"미상",F28&lt;&gt;""),1,0)+IF(AND(G28&lt;&gt;"미상",G28&lt;&gt;""),1,0)+IF(AND(H28&lt;&gt;"미상",H28&lt;&gt;""),1,0)+IF(AND(I28&lt;&gt;"미상",I28&lt;&gt;""),1,0)+IF(AND(J28&lt;&gt;"미상",J28&lt;&gt;""),1,0)+IF(AND(K28&lt;&gt;"미상",K28&lt;&gt;""),1,0)+IF(AND(L28&lt;&gt;"미상",L28&lt;&gt;""),1,0)+IF(AND(M28&lt;&gt;"미상",M28&lt;&gt;""),1,0)+IF(AND(N28&lt;&gt;"미상",N28&lt;&gt;""),1,0))&amp;"/11"</f>
         <v/>
       </c>
       <c r="AD28" s="6" t="inlineStr">
@@ -4880,7 +4880,7 @@
         </is>
       </c>
       <c r="AC29" s="6">
-        <f>(IF(ISNUMBER(D29),1,0)+IF(ISNUMBER(E29),1,0)+IF(F29&lt;&gt;"미상",1,0)+IF(G29&lt;&gt;"미상",1,0)+IF(H29&lt;&gt;"미상",1,0)+IF(I29&lt;&gt;"미상",1,0)+IF(J29&lt;&gt;"미상",1,0)+IF(K29&lt;&gt;"미상",1,0)+IF(L29&lt;&gt;"미상",1,0)+IF(M29&lt;&gt;"미상",1,0)+IF(N29&lt;&gt;"미상",1,0))&amp;"/11"</f>
+        <f>(IF(ISNUMBER(D29),1,0)+IF(ISNUMBER(E29),1,0)+IF(AND(F29&lt;&gt;"미상",F29&lt;&gt;""),1,0)+IF(AND(G29&lt;&gt;"미상",G29&lt;&gt;""),1,0)+IF(AND(H29&lt;&gt;"미상",H29&lt;&gt;""),1,0)+IF(AND(I29&lt;&gt;"미상",I29&lt;&gt;""),1,0)+IF(AND(J29&lt;&gt;"미상",J29&lt;&gt;""),1,0)+IF(AND(K29&lt;&gt;"미상",K29&lt;&gt;""),1,0)+IF(AND(L29&lt;&gt;"미상",L29&lt;&gt;""),1,0)+IF(AND(M29&lt;&gt;"미상",M29&lt;&gt;""),1,0)+IF(AND(N29&lt;&gt;"미상",N29&lt;&gt;""),1,0))&amp;"/11"</f>
         <v/>
       </c>
       <c r="AD29" s="6" t="inlineStr">
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="AC30" s="6">
-        <f>(IF(ISNUMBER(D30),1,0)+IF(ISNUMBER(E30),1,0)+IF(F30&lt;&gt;"미상",1,0)+IF(G30&lt;&gt;"미상",1,0)+IF(H30&lt;&gt;"미상",1,0)+IF(I30&lt;&gt;"미상",1,0)+IF(J30&lt;&gt;"미상",1,0)+IF(K30&lt;&gt;"미상",1,0)+IF(L30&lt;&gt;"미상",1,0)+IF(M30&lt;&gt;"미상",1,0)+IF(N30&lt;&gt;"미상",1,0))&amp;"/11"</f>
+        <f>(IF(ISNUMBER(D30),1,0)+IF(ISNUMBER(E30),1,0)+IF(AND(F30&lt;&gt;"미상",F30&lt;&gt;""),1,0)+IF(AND(G30&lt;&gt;"미상",G30&lt;&gt;""),1,0)+IF(AND(H30&lt;&gt;"미상",H30&lt;&gt;""),1,0)+IF(AND(I30&lt;&gt;"미상",I30&lt;&gt;""),1,0)+IF(AND(J30&lt;&gt;"미상",J30&lt;&gt;""),1,0)+IF(AND(K30&lt;&gt;"미상",K30&lt;&gt;""),1,0)+IF(AND(L30&lt;&gt;"미상",L30&lt;&gt;""),1,0)+IF(AND(M30&lt;&gt;"미상",M30&lt;&gt;""),1,0)+IF(AND(N30&lt;&gt;"미상",N30&lt;&gt;""),1,0))&amp;"/11"</f>
         <v/>
       </c>
       <c r="AD30" s="6" t="inlineStr">
@@ -5150,7 +5150,7 @@
         </is>
       </c>
       <c r="AC31" s="6">
-        <f>(IF(ISNUMBER(D31),1,0)+IF(ISNUMBER(E31),1,0)+IF(F31&lt;&gt;"미상",1,0)+IF(G31&lt;&gt;"미상",1,0)+IF(H31&lt;&gt;"미상",1,0)+IF(I31&lt;&gt;"미상",1,0)+IF(J31&lt;&gt;"미상",1,0)+IF(K31&lt;&gt;"미상",1,0)+IF(L31&lt;&gt;"미상",1,0)+IF(M31&lt;&gt;"미상",1,0)+IF(N31&lt;&gt;"미상",1,0))&amp;"/11"</f>
+        <f>(IF(ISNUMBER(D31),1,0)+IF(ISNUMBER(E31),1,0)+IF(AND(F31&lt;&gt;"미상",F31&lt;&gt;""),1,0)+IF(AND(G31&lt;&gt;"미상",G31&lt;&gt;""),1,0)+IF(AND(H31&lt;&gt;"미상",H31&lt;&gt;""),1,0)+IF(AND(I31&lt;&gt;"미상",I31&lt;&gt;""),1,0)+IF(AND(J31&lt;&gt;"미상",J31&lt;&gt;""),1,0)+IF(AND(K31&lt;&gt;"미상",K31&lt;&gt;""),1,0)+IF(AND(L31&lt;&gt;"미상",L31&lt;&gt;""),1,0)+IF(AND(M31&lt;&gt;"미상",M31&lt;&gt;""),1,0)+IF(AND(N31&lt;&gt;"미상",N31&lt;&gt;""),1,0))&amp;"/11"</f>
         <v/>
       </c>
       <c r="AD31" s="6" t="inlineStr">
@@ -5287,7 +5287,7 @@
         </is>
       </c>
       <c r="AC32" s="6">
-        <f>(IF(ISNUMBER(D32),1,0)+IF(ISNUMBER(E32),1,0)+IF(F32&lt;&gt;"미상",1,0)+IF(G32&lt;&gt;"미상",1,0)+IF(H32&lt;&gt;"미상",1,0)+IF(I32&lt;&gt;"미상",1,0)+IF(J32&lt;&gt;"미상",1,0)+IF(K32&lt;&gt;"미상",1,0)+IF(L32&lt;&gt;"미상",1,0)+IF(M32&lt;&gt;"미상",1,0)+IF(N32&lt;&gt;"미상",1,0))&amp;"/11"</f>
+        <f>(IF(ISNUMBER(D32),1,0)+IF(ISNUMBER(E32),1,0)+IF(AND(F32&lt;&gt;"미상",F32&lt;&gt;""),1,0)+IF(AND(G32&lt;&gt;"미상",G32&lt;&gt;""),1,0)+IF(AND(H32&lt;&gt;"미상",H32&lt;&gt;""),1,0)+IF(AND(I32&lt;&gt;"미상",I32&lt;&gt;""),1,0)+IF(AND(J32&lt;&gt;"미상",J32&lt;&gt;""),1,0)+IF(AND(K32&lt;&gt;"미상",K32&lt;&gt;""),1,0)+IF(AND(L32&lt;&gt;"미상",L32&lt;&gt;""),1,0)+IF(AND(M32&lt;&gt;"미상",M32&lt;&gt;""),1,0)+IF(AND(N32&lt;&gt;"미상",N32&lt;&gt;""),1,0))&amp;"/11"</f>
         <v/>
       </c>
       <c r="AD32" s="6" t="inlineStr">
@@ -5424,7 +5424,7 @@
         </is>
       </c>
       <c r="AC33" s="6">
-        <f>(IF(ISNUMBER(D33),1,0)+IF(ISNUMBER(E33),1,0)+IF(F33&lt;&gt;"미상",1,0)+IF(G33&lt;&gt;"미상",1,0)+IF(H33&lt;&gt;"미상",1,0)+IF(I33&lt;&gt;"미상",1,0)+IF(J33&lt;&gt;"미상",1,0)+IF(K33&lt;&gt;"미상",1,0)+IF(L33&lt;&gt;"미상",1,0)+IF(M33&lt;&gt;"미상",1,0)+IF(N33&lt;&gt;"미상",1,0))&amp;"/11"</f>
+        <f>(IF(ISNUMBER(D33),1,0)+IF(ISNUMBER(E33),1,0)+IF(AND(F33&lt;&gt;"미상",F33&lt;&gt;""),1,0)+IF(AND(G33&lt;&gt;"미상",G33&lt;&gt;""),1,0)+IF(AND(H33&lt;&gt;"미상",H33&lt;&gt;""),1,0)+IF(AND(I33&lt;&gt;"미상",I33&lt;&gt;""),1,0)+IF(AND(J33&lt;&gt;"미상",J33&lt;&gt;""),1,0)+IF(AND(K33&lt;&gt;"미상",K33&lt;&gt;""),1,0)+IF(AND(L33&lt;&gt;"미상",L33&lt;&gt;""),1,0)+IF(AND(M33&lt;&gt;"미상",M33&lt;&gt;""),1,0)+IF(AND(N33&lt;&gt;"미상",N33&lt;&gt;""),1,0))&amp;"/11"</f>
         <v/>
       </c>
       <c r="AD33" s="6" t="inlineStr">
@@ -5559,7 +5559,7 @@
         </is>
       </c>
       <c r="AC34" s="6">
-        <f>(IF(ISNUMBER(D34),1,0)+IF(ISNUMBER(E34),1,0)+IF(F34&lt;&gt;"미상",1,0)+IF(G34&lt;&gt;"미상",1,0)+IF(H34&lt;&gt;"미상",1,0)+IF(I34&lt;&gt;"미상",1,0)+IF(J34&lt;&gt;"미상",1,0)+IF(K34&lt;&gt;"미상",1,0)+IF(L34&lt;&gt;"미상",1,0)+IF(M34&lt;&gt;"미상",1,0)+IF(N34&lt;&gt;"미상",1,0))&amp;"/11"</f>
+        <f>(IF(ISNUMBER(D34),1,0)+IF(ISNUMBER(E34),1,0)+IF(AND(F34&lt;&gt;"미상",F34&lt;&gt;""),1,0)+IF(AND(G34&lt;&gt;"미상",G34&lt;&gt;""),1,0)+IF(AND(H34&lt;&gt;"미상",H34&lt;&gt;""),1,0)+IF(AND(I34&lt;&gt;"미상",I34&lt;&gt;""),1,0)+IF(AND(J34&lt;&gt;"미상",J34&lt;&gt;""),1,0)+IF(AND(K34&lt;&gt;"미상",K34&lt;&gt;""),1,0)+IF(AND(L34&lt;&gt;"미상",L34&lt;&gt;""),1,0)+IF(AND(M34&lt;&gt;"미상",M34&lt;&gt;""),1,0)+IF(AND(N34&lt;&gt;"미상",N34&lt;&gt;""),1,0))&amp;"/11"</f>
         <v/>
       </c>
       <c r="AD34" s="6" t="inlineStr">

--- a/고양이_오메가3_제품_채점표.xlsx
+++ b/고양이_오메가3_제품_채점표.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="기준" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="점수표" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기준" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="점수표" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2769,16 +2769,18 @@
           <t>펫·스틱</t>
         </is>
       </c>
-      <c r="D14" s="7" t="n"/>
+      <c r="D14" s="7" t="n">
+        <v>560</v>
+      </c>
       <c r="E14" s="7" t="n"/>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>일부</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>rTG</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
@@ -2788,12 +2790,12 @@
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>있음</t>
         </is>
       </c>
       <c r="J14" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>우수</t>
         </is>
       </c>
       <c r="K14" s="7" t="inlineStr">
@@ -2882,7 +2884,7 @@
       </c>
       <c r="AD14" s="6" t="inlineStr">
         <is>
-          <t>수의사 설계 스틱·초고함량 표방·수치 미상 (이퀄)</t>
+          <t>EPA+DHA 560mg/스틱(라벨 명시·고함량)·rTG·정제어유(어종 미표기)·천연토코페롤(항산화)·멸균 레토르트 개별스틱 공기차단포장·원료 정제수/타피오카전분/치커리/정제어유/가쓰오엑기스 (equalpet.store/product/50 자동수집+비전확인 20260620)</t>
         </is>
       </c>
     </row>
@@ -3168,16 +3170,20 @@
           <t>펫·액상</t>
         </is>
       </c>
-      <c r="D17" s="7" t="n"/>
-      <c r="E17" s="7" t="n"/>
+      <c r="D17" s="7" t="n">
+        <v>147</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>15</v>
+      </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>명시</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>TG</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
@@ -3207,12 +3213,12 @@
       </c>
       <c r="M17" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>공개</t>
         </is>
       </c>
       <c r="N17" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>명시</t>
         </is>
       </c>
       <c r="O17" s="7">
@@ -3267,12 +3273,12 @@
       </c>
       <c r="AA17" s="7" t="inlineStr">
         <is>
-          <t>라벨만</t>
+          <t>공개·검증</t>
         </is>
       </c>
       <c r="AB17" s="7" t="inlineStr">
         <is>
-          <t>미정</t>
+          <t>일반유지</t>
         </is>
       </c>
       <c r="AC17" s="6">
@@ -3281,7 +3287,7 @@
       </c>
       <c r="AD17" s="6" t="inlineStr">
         <is>
-          <t>카이쿠라(KAIKOORA) 청어100%·아이슬란드산·EU특허 비산화구조·250/150ml 액상펌프·per회분 EPA+DHA mg 미상(이미지잠금) (kaikoora.com/펫프렌즈)</t>
+          <t>카이쿠라 청어100% 아이슬란드산 자연어유(TG)·성분표 per1g Total오메가3 199mg·DHA79+EPA70=147mg·DPA10mg·VitA/D ND·순도≈15%(147/1000)·사료검정 산가0.01(COA공개)·MSC인증·1펌프≈1ml·250ml (kaikoora.com/product/13 자동수집+비전확인 20260620)</t>
         </is>
       </c>
     </row>

--- a/고양이_오메가3_제품_채점표.xlsx
+++ b/고양이_오메가3_제품_채점표.xlsx
@@ -3037,51 +3037,55 @@
           <t>펫</t>
         </is>
       </c>
-      <c r="D16" s="7" t="n"/>
-      <c r="E16" s="7" t="n"/>
+      <c r="D16" s="7" t="n">
+        <v>128</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>80</v>
+      </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>일부</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>rTG</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>소형어</t>
         </is>
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>있음</t>
         </is>
       </c>
       <c r="J16" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>우수</t>
         </is>
       </c>
       <c r="K16" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>캡슐</t>
         </is>
       </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>있음</t>
         </is>
       </c>
       <c r="M16" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>공개</t>
         </is>
       </c>
       <c r="N16" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>명시</t>
         </is>
       </c>
       <c r="O16" s="7">
@@ -3136,12 +3140,12 @@
       </c>
       <c r="AA16" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>공개·검증</t>
         </is>
       </c>
       <c r="AB16" s="7" t="inlineStr">
         <is>
-          <t>미정</t>
+          <t>일반유지</t>
         </is>
       </c>
       <c r="AC16" s="6">
@@ -3150,7 +3154,7 @@
       </c>
       <c r="AD16" s="6" t="inlineStr">
         <is>
-          <t>미니 SKU·스펙 수집중</t>
+          <t>데일리케얼 슈퍼리얼 알티지(180캡슐 SKU 기준)·1캡슐 EPA+DHA 128mg·순도80%이상·Real rTG·정제어유 소형어·d-토코페롤(비타민E)·PTP개별포장 산패4중방어·KD파마(독일) 원료+완제품 IFOS5★·TOTOX/중금속 검사공개·연질캡슐 (fitpetmall goods/1000033651 자동수집+OCR 20260620)</t>
         </is>
       </c>
     </row>
@@ -3582,7 +3586,7 @@
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>TG</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
@@ -3602,7 +3606,7 @@
       </c>
       <c r="K20" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>펌프액상</t>
         </is>
       </c>
       <c r="L20" s="7" t="inlineStr">
@@ -3617,7 +3621,7 @@
       </c>
       <c r="N20" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>명시</t>
         </is>
       </c>
       <c r="O20" s="7">
@@ -3672,7 +3676,7 @@
       </c>
       <c r="AA20" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>라벨만</t>
         </is>
       </c>
       <c r="AB20" s="7" t="inlineStr">
@@ -3686,7 +3690,7 @@
       </c>
       <c r="AD20" s="6" t="inlineStr">
         <is>
-          <t>노르웨이 연어오일·스펙 수집중</t>
+          <t>Salmo Pet 노르웨이산 연어오일(NORGE 원산지 명시)·자연어유(TG)·연어 단일·5kg미만 1펌프~·DHA·EPA 함유 표기만·per펌프 EPA+DHA mg 미공개 (fitpetmall goods/1000024792 자동수집+비전 20260620)</t>
         </is>
       </c>
     </row>

--- a/고양이_오메가3_제품_채점표.xlsx
+++ b/고양이_오메가3_제품_채점표.xlsx
@@ -3311,16 +3311,18 @@
           <t>펫·액상</t>
         </is>
       </c>
-      <c r="D18" s="7" t="n"/>
+      <c r="D18" s="7" t="n">
+        <v>84</v>
+      </c>
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>일부</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>TG</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr">
@@ -3350,12 +3352,12 @@
       </c>
       <c r="M18" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>일부</t>
         </is>
       </c>
       <c r="N18" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>명시</t>
         </is>
       </c>
       <c r="O18" s="7">
@@ -3415,7 +3417,7 @@
       </c>
       <c r="AB18" s="7" t="inlineStr">
         <is>
-          <t>미정</t>
+          <t>일반유지</t>
         </is>
       </c>
       <c r="AC18" s="6">
@@ -3424,7 +3426,7 @@
       </c>
       <c r="AD18" s="6" t="inlineStr">
         <is>
-          <t>연어·액상·공기차단특허</t>
+          <t>바이오펫츠 펫메가3 150ml·1ml당 EPA+DHA 64~103mg(중간값 84)·연어오일99%(원육 노르웨이)·자연 비농축(TG)·공기차단 특허용기(특허 20-0470695)·비타민 1% 첨가·산가 2.5 공개(COA 일부)·per회분 mg 미상 (fitpetmall goods/1000037912 자동수집+OCR 20260620)</t>
         </is>
       </c>
     </row>

--- a/고양이_오메가3_제품_채점표.xlsx
+++ b/고양이_오메가3_제품_채점표.xlsx
@@ -2234,7 +2234,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>펫·캡슐</t>
+          <t>펫·액상</t>
         </is>
       </c>
       <c r="D10" s="7" t="n"/>
@@ -2251,12 +2251,12 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>일반어</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>있음</t>
         </is>
       </c>
       <c r="J10" s="7" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="K10" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>펌프액상</t>
         </is>
       </c>
       <c r="L10" s="7" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="AA10" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>라벨만</t>
         </is>
       </c>
       <c r="AB10" s="7" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="AD10" s="6" t="inlineStr">
         <is>
-          <t>스펙 수집중</t>
+          <t>아베텍 오메가3벳 125ml 액상·남태평양/남극해 바다생선(EPA·DHA 함유)·고순도 정제·천연항산화제(비타민E)·per회분 EPA+DHA mg 미공개 (easypet goods/1000000047·yourpet 254 확인 20260620)</t>
         </is>
       </c>
     </row>

--- a/고양이_오메가3_제품_채점표.xlsx
+++ b/고양이_오메가3_제품_채점표.xlsx
@@ -3446,16 +3446,20 @@
           <t>펫·액상</t>
         </is>
       </c>
-      <c r="D19" s="7" t="n"/>
-      <c r="E19" s="7" t="n"/>
+      <c r="D19" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>5</v>
+      </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>명시</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>TG</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
@@ -3465,12 +3469,12 @@
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>있음</t>
         </is>
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>취약</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K19" s="7" t="inlineStr">
@@ -3485,12 +3489,12 @@
       </c>
       <c r="M19" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>공개</t>
         </is>
       </c>
       <c r="N19" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>명시</t>
         </is>
       </c>
       <c r="O19" s="7">
@@ -3545,12 +3549,12 @@
       </c>
       <c r="AA19" s="7" t="inlineStr">
         <is>
-          <t>라벨만</t>
+          <t>공개·검증</t>
         </is>
       </c>
       <c r="AB19" s="7" t="inlineStr">
         <is>
-          <t>미정</t>
+          <t>일반유지</t>
         </is>
       </c>
       <c r="AC19" s="6">
@@ -3559,7 +3563,7 @@
       </c>
       <c r="AD19" s="6" t="inlineStr">
         <is>
-          <t>연어오일 1000ml 대용량 (핏펫)</t>
+          <t>브릴리언트 연어오일 CoA(페오펫 300ml 동일오일)·EPA≥20+DHA≥30=≥50mg/g·DPA≥10·Total오메가3≥140mg/g·Fat≥99%(순도≈5%)·노르웨이 연어 자연유(TG)·Astaxanthin&gt;6µg/g(천연항산화)·Peroxide≤12/Anisidine≤8/중금속&lt;0.1/PCB·다이옥신 분기검사(COA공개)·차단펌프(공기차단)·Friend of the Sea (shop.peopet.co.kr/goods/36686 비전확인 20260620)</t>
         </is>
       </c>
     </row>

--- a/고양이_오메가3_제품_채점표.xlsx
+++ b/고양이_오메가3_제품_채점표.xlsx
@@ -2367,44 +2367,48 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>펫</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="7" t="n"/>
+          <t>펫·캡슐</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>80</v>
+      </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>명시</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>rTG</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>소형어</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>있음</t>
         </is>
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>캡슐</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>있음</t>
         </is>
       </c>
       <c r="M11" s="7" t="inlineStr">
@@ -2414,7 +2418,7 @@
       </c>
       <c r="N11" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>명시</t>
         </is>
       </c>
       <c r="O11" s="7">
@@ -2469,12 +2473,12 @@
       </c>
       <c r="AA11" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>라벨만</t>
         </is>
       </c>
       <c r="AB11" s="7" t="inlineStr">
         <is>
-          <t>미정</t>
+          <t>일반유지</t>
         </is>
       </c>
       <c r="AC11" s="6">
@@ -2483,7 +2487,7 @@
       </c>
       <c r="AD11" s="6" t="inlineStr">
         <is>
-          <t>스펙 수집중</t>
+          <t>페스룸 TINY 오메가3 50mg(소형견·고양이 추천 SKU)·1캡슐 50mg 중 EPA+DHA 40mg·순도80%·3세대 rTG·멸치/청어 소형어·비타민E 0.13mg·통포장·KD Pharma(독일) 원료·IFOS5★+GOED 인증원료·150캡슐(0.5cm)·100mg형은 EPA48+DHA32=80mg/블리스터개별 (pethroom product_no=702 자동수집+비전 20260620)</t>
         </is>
       </c>
     </row>

--- a/고양이_오메가3_제품_채점표.xlsx
+++ b/고양이_오메가3_제품_채점표.xlsx
@@ -3850,7 +3850,7 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>펫</t>
+          <t>펫·액상</t>
         </is>
       </c>
       <c r="D22" s="7" t="n"/>
@@ -3862,12 +3862,12 @@
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>TG</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>일반어</t>
+          <t>미상</t>
         </is>
       </c>
       <c r="I22" s="7" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="K22" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>펌프액상</t>
         </is>
       </c>
       <c r="L22" s="7" t="inlineStr">
@@ -3897,7 +3897,7 @@
       </c>
       <c r="N22" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>명시</t>
         </is>
       </c>
       <c r="O22" s="7">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="AA22" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>라벨만</t>
         </is>
       </c>
       <c r="AB22" s="7" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="AD22" s="6" t="inlineStr">
         <is>
-          <t>물개오일+루테인·해양성·스펙 미상 (핏펫)</t>
+          <t>오메가3 플러스펫 캐나다 물개오일 140ml+루테인·해양 포유류 오일(해양성·EPA/DHA/DPA 공급</t>
         </is>
       </c>
     </row>

--- a/고양이_오메가3_제품_채점표.xlsx
+++ b/고양이_오메가3_제품_채점표.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C57"/>
+  <dimension ref="A1:C58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -618,138 +618,138 @@
     <row r="18">
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>식물성</t>
+          <t>해양포유류</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>조류</t>
+          <t>식물성</t>
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>조류</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>미상</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="3" t="inlineStr">
+    <row r="23">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>항산화제</t>
         </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>있음</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>있음</t>
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>없음</t>
         </is>
       </c>
       <c r="C25" s="4" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="3" t="inlineStr">
+    <row r="26">
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>미상</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>포장</t>
         </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>우수</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>우수</t>
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>취약</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>취약</t>
         </is>
       </c>
       <c r="C31" s="4" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="33">
-      <c r="B33" s="3" t="inlineStr">
+    <row r="32">
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>미상</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>제형</t>
         </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>캡슐</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>소프트젤</t>
+          <t>캡슐</t>
         </is>
       </c>
       <c r="C35" s="4" t="n">
@@ -759,17 +759,17 @@
     <row r="36">
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>츄</t>
+          <t>소프트젤</t>
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>스틱</t>
+          <t>츄</t>
         </is>
       </c>
       <c r="C37" s="4" t="n">
@@ -779,7 +779,7 @@
     <row r="38">
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>펌프액상</t>
+          <t>스틱</t>
         </is>
       </c>
       <c r="C38" s="4" t="n">
@@ -789,151 +789,161 @@
     <row r="39">
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>대용량액상</t>
+          <t>펌프액상</t>
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>대용량액상</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>미상</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="42">
-      <c r="B42" s="3" t="inlineStr">
+    <row r="43">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>인증</t>
         </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>있음</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>있음</t>
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>없음</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="47">
-      <c r="B47" s="3" t="inlineStr">
+    <row r="46">
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>미상</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>COA</t>
         </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>공개</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>일부</t>
+          <t>공개</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>일부</t>
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>없음</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="53">
-      <c r="B53" s="3" t="inlineStr">
+    <row r="52">
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>미상</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t>원료사</t>
         </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>명시</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>일부</t>
+          <t>명시</t>
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>일부</t>
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>없음</t>
         </is>
       </c>
       <c r="C57" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>미상</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1225,15 +1235,15 @@
         <v/>
       </c>
       <c r="T2" s="8">
-        <f>IFERROR(VLOOKUP(I2,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J2,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K2,기준!$B$34:$C$40,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I2,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J2,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K2,기준!$B$35:$C$41,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U2" s="8">
-        <f>IFERROR(VLOOKUP(G2,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H2,기준!$B$16:$C$20,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(G2,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H2,기준!$B$16:$C$21,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="V2" s="8">
-        <f>IFERROR(VLOOKUP(L2,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M2,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N2,기준!$B$54:$C$57,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L2,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M2,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N2,기준!$B$55:$C$58,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W2" s="8">
@@ -1360,15 +1370,15 @@
         <v/>
       </c>
       <c r="T3" s="8">
-        <f>IFERROR(VLOOKUP(I3,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J3,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K3,기준!$B$34:$C$40,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I3,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J3,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K3,기준!$B$35:$C$41,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U3" s="8">
-        <f>IFERROR(VLOOKUP(G3,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H3,기준!$B$16:$C$20,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(G3,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H3,기준!$B$16:$C$21,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="V3" s="8">
-        <f>IFERROR(VLOOKUP(L3,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M3,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N3,기준!$B$54:$C$57,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L3,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M3,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N3,기준!$B$55:$C$58,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W3" s="8">
@@ -1497,15 +1507,15 @@
         <v/>
       </c>
       <c r="T4" s="8">
-        <f>IFERROR(VLOOKUP(I4,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J4,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K4,기준!$B$34:$C$40,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I4,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J4,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K4,기준!$B$35:$C$41,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U4" s="8">
-        <f>IFERROR(VLOOKUP(G4,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H4,기준!$B$16:$C$20,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(G4,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H4,기준!$B$16:$C$21,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="V4" s="8">
-        <f>IFERROR(VLOOKUP(L4,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M4,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N4,기준!$B$54:$C$57,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L4,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M4,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N4,기준!$B$55:$C$58,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W4" s="8">
@@ -1634,15 +1644,15 @@
         <v/>
       </c>
       <c r="T5" s="8">
-        <f>IFERROR(VLOOKUP(I5,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J5,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K5,기준!$B$34:$C$40,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I5,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J5,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K5,기준!$B$35:$C$41,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U5" s="8">
-        <f>IFERROR(VLOOKUP(G5,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H5,기준!$B$16:$C$20,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(G5,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H5,기준!$B$16:$C$21,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="V5" s="8">
-        <f>IFERROR(VLOOKUP(L5,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M5,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N5,기준!$B$54:$C$57,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L5,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M5,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N5,기준!$B$55:$C$58,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W5" s="8">
@@ -1771,15 +1781,15 @@
         <v/>
       </c>
       <c r="T6" s="8">
-        <f>IFERROR(VLOOKUP(I6,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J6,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K6,기준!$B$34:$C$40,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I6,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J6,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K6,기준!$B$35:$C$41,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U6" s="8">
-        <f>IFERROR(VLOOKUP(G6,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H6,기준!$B$16:$C$20,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(G6,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H6,기준!$B$16:$C$21,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="V6" s="8">
-        <f>IFERROR(VLOOKUP(L6,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M6,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N6,기준!$B$54:$C$57,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L6,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M6,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N6,기준!$B$55:$C$58,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W6" s="8">
@@ -1908,15 +1918,15 @@
         <v/>
       </c>
       <c r="T7" s="8">
-        <f>IFERROR(VLOOKUP(I7,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J7,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K7,기준!$B$34:$C$40,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I7,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J7,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K7,기준!$B$35:$C$41,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U7" s="8">
-        <f>IFERROR(VLOOKUP(G7,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H7,기준!$B$16:$C$20,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(G7,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H7,기준!$B$16:$C$21,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="V7" s="8">
-        <f>IFERROR(VLOOKUP(L7,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M7,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N7,기준!$B$54:$C$57,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L7,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M7,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N7,기준!$B$55:$C$58,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W7" s="8">
@@ -2041,15 +2051,15 @@
         <v/>
       </c>
       <c r="T8" s="8">
-        <f>IFERROR(VLOOKUP(I8,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J8,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K8,기준!$B$34:$C$40,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I8,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J8,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K8,기준!$B$35:$C$41,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U8" s="8">
-        <f>IFERROR(VLOOKUP(G8,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H8,기준!$B$16:$C$20,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(G8,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H8,기준!$B$16:$C$21,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="V8" s="8">
-        <f>IFERROR(VLOOKUP(L8,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M8,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N8,기준!$B$54:$C$57,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L8,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M8,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N8,기준!$B$55:$C$58,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W8" s="8">
@@ -2174,15 +2184,15 @@
         <v/>
       </c>
       <c r="T9" s="8">
-        <f>IFERROR(VLOOKUP(I9,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J9,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K9,기준!$B$34:$C$40,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I9,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J9,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K9,기준!$B$35:$C$41,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U9" s="8">
-        <f>IFERROR(VLOOKUP(G9,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H9,기준!$B$16:$C$20,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(G9,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H9,기준!$B$16:$C$21,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="V9" s="8">
-        <f>IFERROR(VLOOKUP(L9,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M9,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N9,기준!$B$54:$C$57,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L9,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M9,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N9,기준!$B$55:$C$58,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W9" s="8">
@@ -2307,15 +2317,15 @@
         <v/>
       </c>
       <c r="T10" s="8">
-        <f>IFERROR(VLOOKUP(I10,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J10,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K10,기준!$B$34:$C$40,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I10,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J10,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K10,기준!$B$35:$C$41,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U10" s="8">
-        <f>IFERROR(VLOOKUP(G10,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H10,기준!$B$16:$C$20,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(G10,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H10,기준!$B$16:$C$21,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="V10" s="8">
-        <f>IFERROR(VLOOKUP(L10,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M10,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N10,기준!$B$54:$C$57,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L10,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M10,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N10,기준!$B$55:$C$58,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W10" s="8">
@@ -2444,15 +2454,15 @@
         <v/>
       </c>
       <c r="T11" s="8">
-        <f>IFERROR(VLOOKUP(I11,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J11,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K11,기준!$B$34:$C$40,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I11,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J11,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K11,기준!$B$35:$C$41,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U11" s="8">
-        <f>IFERROR(VLOOKUP(G11,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H11,기준!$B$16:$C$20,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(G11,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H11,기준!$B$16:$C$21,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="V11" s="8">
-        <f>IFERROR(VLOOKUP(L11,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M11,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N11,기준!$B$54:$C$57,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L11,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M11,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N11,기준!$B$55:$C$58,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W11" s="8">
@@ -2577,15 +2587,15 @@
         <v/>
       </c>
       <c r="T12" s="8">
-        <f>IFERROR(VLOOKUP(I12,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J12,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K12,기준!$B$34:$C$40,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I12,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J12,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K12,기준!$B$35:$C$41,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U12" s="8">
-        <f>IFERROR(VLOOKUP(G12,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H12,기준!$B$16:$C$20,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(G12,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H12,기준!$B$16:$C$21,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="V12" s="8">
-        <f>IFERROR(VLOOKUP(L12,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M12,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N12,기준!$B$54:$C$57,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L12,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M12,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N12,기준!$B$55:$C$58,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W12" s="8">
@@ -2710,15 +2720,15 @@
         <v/>
       </c>
       <c r="T13" s="8">
-        <f>IFERROR(VLOOKUP(I13,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J13,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K13,기준!$B$34:$C$40,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I13,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J13,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K13,기준!$B$35:$C$41,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U13" s="8">
-        <f>IFERROR(VLOOKUP(G13,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H13,기준!$B$16:$C$20,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(G13,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H13,기준!$B$16:$C$21,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="V13" s="8">
-        <f>IFERROR(VLOOKUP(L13,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M13,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N13,기준!$B$54:$C$57,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L13,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M13,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N13,기준!$B$55:$C$58,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W13" s="8">
@@ -2845,15 +2855,15 @@
         <v/>
       </c>
       <c r="T14" s="8">
-        <f>IFERROR(VLOOKUP(I14,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J14,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K14,기준!$B$34:$C$40,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I14,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J14,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K14,기준!$B$35:$C$41,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U14" s="8">
-        <f>IFERROR(VLOOKUP(G14,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H14,기준!$B$16:$C$20,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(G14,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H14,기준!$B$16:$C$21,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="V14" s="8">
-        <f>IFERROR(VLOOKUP(L14,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M14,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N14,기준!$B$54:$C$57,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L14,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M14,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N14,기준!$B$55:$C$58,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W14" s="8">
@@ -2978,15 +2988,15 @@
         <v/>
       </c>
       <c r="T15" s="8">
-        <f>IFERROR(VLOOKUP(I15,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J15,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K15,기준!$B$34:$C$40,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I15,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J15,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K15,기준!$B$35:$C$41,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U15" s="8">
-        <f>IFERROR(VLOOKUP(G15,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H15,기준!$B$16:$C$20,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(G15,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H15,기준!$B$16:$C$21,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="V15" s="8">
-        <f>IFERROR(VLOOKUP(L15,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M15,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N15,기준!$B$54:$C$57,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L15,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M15,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N15,기준!$B$55:$C$58,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W15" s="8">
@@ -3115,15 +3125,15 @@
         <v/>
       </c>
       <c r="T16" s="8">
-        <f>IFERROR(VLOOKUP(I16,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J16,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K16,기준!$B$34:$C$40,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I16,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J16,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K16,기준!$B$35:$C$41,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U16" s="8">
-        <f>IFERROR(VLOOKUP(G16,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H16,기준!$B$16:$C$20,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(G16,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H16,기준!$B$16:$C$21,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="V16" s="8">
-        <f>IFERROR(VLOOKUP(L16,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M16,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N16,기준!$B$54:$C$57,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L16,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M16,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N16,기준!$B$55:$C$58,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W16" s="8">
@@ -3252,15 +3262,15 @@
         <v/>
       </c>
       <c r="T17" s="8">
-        <f>IFERROR(VLOOKUP(I17,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J17,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K17,기준!$B$34:$C$40,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I17,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J17,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K17,기준!$B$35:$C$41,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U17" s="8">
-        <f>IFERROR(VLOOKUP(G17,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H17,기준!$B$16:$C$20,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(G17,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H17,기준!$B$16:$C$21,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="V17" s="8">
-        <f>IFERROR(VLOOKUP(L17,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M17,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N17,기준!$B$54:$C$57,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L17,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M17,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N17,기준!$B$55:$C$58,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W17" s="8">
@@ -3387,15 +3397,15 @@
         <v/>
       </c>
       <c r="T18" s="8">
-        <f>IFERROR(VLOOKUP(I18,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J18,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K18,기준!$B$34:$C$40,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I18,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J18,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K18,기준!$B$35:$C$41,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U18" s="8">
-        <f>IFERROR(VLOOKUP(G18,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H18,기준!$B$16:$C$20,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(G18,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H18,기준!$B$16:$C$21,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="V18" s="8">
-        <f>IFERROR(VLOOKUP(L18,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M18,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N18,기준!$B$54:$C$57,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L18,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M18,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N18,기준!$B$55:$C$58,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W18" s="8">
@@ -3524,15 +3534,15 @@
         <v/>
       </c>
       <c r="T19" s="8">
-        <f>IFERROR(VLOOKUP(I19,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J19,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K19,기준!$B$34:$C$40,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I19,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J19,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K19,기준!$B$35:$C$41,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U19" s="8">
-        <f>IFERROR(VLOOKUP(G19,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H19,기준!$B$16:$C$20,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(G19,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H19,기준!$B$16:$C$21,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="V19" s="8">
-        <f>IFERROR(VLOOKUP(L19,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M19,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N19,기준!$B$54:$C$57,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L19,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M19,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N19,기준!$B$55:$C$58,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W19" s="8">
@@ -3657,15 +3667,15 @@
         <v/>
       </c>
       <c r="T20" s="8">
-        <f>IFERROR(VLOOKUP(I20,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J20,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K20,기준!$B$34:$C$40,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I20,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J20,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K20,기준!$B$35:$C$41,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U20" s="8">
-        <f>IFERROR(VLOOKUP(G20,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H20,기준!$B$16:$C$20,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(G20,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H20,기준!$B$16:$C$21,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="V20" s="8">
-        <f>IFERROR(VLOOKUP(L20,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M20,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N20,기준!$B$54:$C$57,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L20,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M20,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N20,기준!$B$55:$C$58,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W20" s="8">
@@ -3790,15 +3800,15 @@
         <v/>
       </c>
       <c r="T21" s="8">
-        <f>IFERROR(VLOOKUP(I21,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J21,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K21,기준!$B$34:$C$40,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I21,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J21,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K21,기준!$B$35:$C$41,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U21" s="8">
-        <f>IFERROR(VLOOKUP(G21,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H21,기준!$B$16:$C$20,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(G21,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H21,기준!$B$16:$C$21,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="V21" s="8">
-        <f>IFERROR(VLOOKUP(L21,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M21,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N21,기준!$B$54:$C$57,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L21,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M21,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N21,기준!$B$55:$C$58,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W21" s="8">
@@ -3867,7 +3877,7 @@
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>해양포유류</t>
         </is>
       </c>
       <c r="I22" s="7" t="inlineStr">
@@ -3923,15 +3933,15 @@
         <v/>
       </c>
       <c r="T22" s="8">
-        <f>IFERROR(VLOOKUP(I22,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J22,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K22,기준!$B$34:$C$40,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I22,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J22,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K22,기준!$B$35:$C$41,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U22" s="8">
-        <f>IFERROR(VLOOKUP(G22,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H22,기준!$B$16:$C$20,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(G22,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H22,기준!$B$16:$C$21,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="V22" s="8">
-        <f>IFERROR(VLOOKUP(L22,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M22,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N22,기준!$B$54:$C$57,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L22,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M22,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N22,기준!$B$55:$C$58,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W22" s="8">
@@ -4058,15 +4068,15 @@
         <v/>
       </c>
       <c r="T23" s="8">
-        <f>IFERROR(VLOOKUP(I23,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J23,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K23,기준!$B$34:$C$40,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I23,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J23,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K23,기준!$B$35:$C$41,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U23" s="8">
-        <f>IFERROR(VLOOKUP(G23,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H23,기준!$B$16:$C$20,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(G23,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H23,기준!$B$16:$C$21,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="V23" s="8">
-        <f>IFERROR(VLOOKUP(L23,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M23,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N23,기준!$B$54:$C$57,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L23,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M23,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N23,기준!$B$55:$C$58,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W23" s="8">
@@ -4191,15 +4201,15 @@
         <v/>
       </c>
       <c r="T24" s="8">
-        <f>IFERROR(VLOOKUP(I24,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J24,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K24,기준!$B$34:$C$40,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I24,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J24,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K24,기준!$B$35:$C$41,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U24" s="8">
-        <f>IFERROR(VLOOKUP(G24,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H24,기준!$B$16:$C$20,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(G24,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H24,기준!$B$16:$C$21,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="V24" s="8">
-        <f>IFERROR(VLOOKUP(L24,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M24,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N24,기준!$B$54:$C$57,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L24,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M24,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N24,기준!$B$55:$C$58,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W24" s="8">
@@ -4324,15 +4334,15 @@
         <v/>
       </c>
       <c r="T25" s="8">
-        <f>IFERROR(VLOOKUP(I25,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J25,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K25,기준!$B$34:$C$40,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I25,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J25,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K25,기준!$B$35:$C$41,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U25" s="8">
-        <f>IFERROR(VLOOKUP(G25,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H25,기준!$B$16:$C$20,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(G25,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H25,기준!$B$16:$C$21,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="V25" s="8">
-        <f>IFERROR(VLOOKUP(L25,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M25,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N25,기준!$B$54:$C$57,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L25,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M25,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N25,기준!$B$55:$C$58,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W25" s="8">
@@ -4457,15 +4467,15 @@
         <v/>
       </c>
       <c r="T26" s="8">
-        <f>IFERROR(VLOOKUP(I26,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J26,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K26,기준!$B$34:$C$40,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I26,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J26,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K26,기준!$B$35:$C$41,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U26" s="8">
-        <f>IFERROR(VLOOKUP(G26,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H26,기준!$B$16:$C$20,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(G26,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H26,기준!$B$16:$C$21,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="V26" s="8">
-        <f>IFERROR(VLOOKUP(L26,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M26,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N26,기준!$B$54:$C$57,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L26,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M26,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N26,기준!$B$55:$C$58,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W26" s="8">
@@ -4594,15 +4604,15 @@
         <v/>
       </c>
       <c r="T27" s="8">
-        <f>IFERROR(VLOOKUP(I27,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J27,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K27,기준!$B$34:$C$40,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I27,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J27,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K27,기준!$B$35:$C$41,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U27" s="8">
-        <f>IFERROR(VLOOKUP(G27,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H27,기준!$B$16:$C$20,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(G27,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H27,기준!$B$16:$C$21,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="V27" s="8">
-        <f>IFERROR(VLOOKUP(L27,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M27,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N27,기준!$B$54:$C$57,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L27,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M27,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N27,기준!$B$55:$C$58,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W27" s="8">
@@ -4729,15 +4739,15 @@
         <v/>
       </c>
       <c r="T28" s="8">
-        <f>IFERROR(VLOOKUP(I28,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J28,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K28,기준!$B$34:$C$40,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I28,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J28,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K28,기준!$B$35:$C$41,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U28" s="8">
-        <f>IFERROR(VLOOKUP(G28,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H28,기준!$B$16:$C$20,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(G28,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H28,기준!$B$16:$C$21,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="V28" s="8">
-        <f>IFERROR(VLOOKUP(L28,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M28,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N28,기준!$B$54:$C$57,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L28,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M28,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N28,기준!$B$55:$C$58,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W28" s="8">
@@ -4862,15 +4872,15 @@
         <v/>
       </c>
       <c r="T29" s="8">
-        <f>IFERROR(VLOOKUP(I29,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J29,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K29,기준!$B$34:$C$40,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I29,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J29,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K29,기준!$B$35:$C$41,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U29" s="8">
-        <f>IFERROR(VLOOKUP(G29,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H29,기준!$B$16:$C$20,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(G29,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H29,기준!$B$16:$C$21,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="V29" s="8">
-        <f>IFERROR(VLOOKUP(L29,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M29,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N29,기준!$B$54:$C$57,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L29,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M29,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N29,기준!$B$55:$C$58,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W29" s="8">
@@ -4997,15 +5007,15 @@
         <v/>
       </c>
       <c r="T30" s="8">
-        <f>IFERROR(VLOOKUP(I30,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J30,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K30,기준!$B$34:$C$40,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I30,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J30,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K30,기준!$B$35:$C$41,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U30" s="8">
-        <f>IFERROR(VLOOKUP(G30,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H30,기준!$B$16:$C$20,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(G30,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H30,기준!$B$16:$C$21,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="V30" s="8">
-        <f>IFERROR(VLOOKUP(L30,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M30,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N30,기준!$B$54:$C$57,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L30,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M30,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N30,기준!$B$55:$C$58,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W30" s="8">
@@ -5132,15 +5142,15 @@
         <v/>
       </c>
       <c r="T31" s="8">
-        <f>IFERROR(VLOOKUP(I31,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J31,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K31,기준!$B$34:$C$40,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I31,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J31,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K31,기준!$B$35:$C$41,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U31" s="8">
-        <f>IFERROR(VLOOKUP(G31,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H31,기준!$B$16:$C$20,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(G31,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H31,기준!$B$16:$C$21,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="V31" s="8">
-        <f>IFERROR(VLOOKUP(L31,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M31,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N31,기준!$B$54:$C$57,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L31,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M31,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N31,기준!$B$55:$C$58,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W31" s="8">
@@ -5269,15 +5279,15 @@
         <v/>
       </c>
       <c r="T32" s="8">
-        <f>IFERROR(VLOOKUP(I32,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J32,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K32,기준!$B$34:$C$40,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I32,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J32,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K32,기준!$B$35:$C$41,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U32" s="8">
-        <f>IFERROR(VLOOKUP(G32,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H32,기준!$B$16:$C$20,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(G32,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H32,기준!$B$16:$C$21,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="V32" s="8">
-        <f>IFERROR(VLOOKUP(L32,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M32,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N32,기준!$B$54:$C$57,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L32,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M32,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N32,기준!$B$55:$C$58,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W32" s="8">
@@ -5406,15 +5416,15 @@
         <v/>
       </c>
       <c r="T33" s="8">
-        <f>IFERROR(VLOOKUP(I33,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J33,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K33,기준!$B$34:$C$40,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I33,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J33,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K33,기준!$B$35:$C$41,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U33" s="8">
-        <f>IFERROR(VLOOKUP(G33,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H33,기준!$B$16:$C$20,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(G33,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H33,기준!$B$16:$C$21,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="V33" s="8">
-        <f>IFERROR(VLOOKUP(L33,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M33,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N33,기준!$B$54:$C$57,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L33,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M33,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N33,기준!$B$55:$C$58,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W33" s="8">
@@ -5541,15 +5551,15 @@
         <v/>
       </c>
       <c r="T34" s="8">
-        <f>IFERROR(VLOOKUP(I34,기준!$B$23:$C$25,2,FALSE),0)+IFERROR(VLOOKUP(J34,기준!$B$28:$C$31,2,FALSE),0)+IFERROR(VLOOKUP(K34,기준!$B$34:$C$40,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I34,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J34,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K34,기준!$B$35:$C$41,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U34" s="8">
-        <f>IFERROR(VLOOKUP(G34,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H34,기준!$B$16:$C$20,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(G34,기준!$B$10:$C$13,2,FALSE),0)+IFERROR(VLOOKUP(H34,기준!$B$16:$C$21,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="V34" s="8">
-        <f>IFERROR(VLOOKUP(L34,기준!$B$43:$C$45,2,FALSE),0)+IFERROR(VLOOKUP(M34,기준!$B$48:$C$51,2,FALSE),0)+IFERROR(VLOOKUP(N34,기준!$B$54:$C$57,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L34,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M34,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N34,기준!$B$55:$C$58,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W34" s="8">

--- a/고양이_오메가3_제품_채점표.xlsx
+++ b/고양이_오메가3_제품_채점표.xlsx
@@ -2291,7 +2291,7 @@
       </c>
       <c r="N10" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>일부</t>
         </is>
       </c>
       <c r="O10" s="7">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AD10" s="6" t="inlineStr">
         <is>
-          <t>아베텍 오메가3벳 125ml 액상·남태평양/남극해 바다생선(EPA·DHA 함유)·고순도 정제·천연항산화제(비타민E)·per회분 EPA+DHA mg 미공개 (easypet goods/1000000047·yourpet 254 확인 20260620)</t>
+          <t>아베텍 오메가3벳 125ml 액상·남태평양/남극해 청정해역 바다생선(고함량 DHA·EPA·동물성)·고순도 정제(수직계열화)·천연항산화제·원산지 region만 명시(원료사 일부)·EPA+DHA mg·순도·형태(rTG/TG) 공식사이트도 미공개 (공식 a-vetech.com/94?idx=165·easypet 확인 20260620)</t>
         </is>
       </c>
     </row>

--- a/고양이_오메가3_제품_채점표.xlsx
+++ b/고양이_오메가3_제품_채점표.xlsx
@@ -3843,7 +3843,7 @@
       </c>
       <c r="AD21" s="6" t="inlineStr">
         <is>
-          <t>연어+폴락(대구과 어체유, 간유 아님)→비타민A/D 상한 부적용 (핏펫)</t>
+          <t>연어+폴락(대구과 어체유, 간유 아님)→비타민A/D 상한 부적용·국내 판매처 없음(2026-06 확인)·단종 추정으로 추가 수집 불가 (구 핏펫)</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="AD24" s="6" t="inlineStr">
         <is>
-          <t>식물성 rTG=미세조류 DHA(EPA 거의 없음)·상한 부적용·DHA 편중(브랜드 식물성라인 순도~80%) (소셜타임스)</t>
+          <t>식물성 rTG=미세조류 DHA(EPA 거의 없음)·상한 부적용·DHA 편중·브랜드 식물성라인 순도~80%·공식몰(nutricore.co.kr) 로그인 게이트라 펫 SKU 스펙 직접확인 불가·확인된 건 사람용 하이퍼셀(EPA+DHA 900mg/일·미세조류 rTG)뿐 (소셜타임스·공식 goodsInnb 2608678 게이트)</t>
         </is>
       </c>
     </row>

--- a/고양이_오메가3_제품_채점표.xlsx
+++ b/고양이_오메가3_제품_채점표.xlsx
@@ -4283,7 +4283,7 @@
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>있음</t>
         </is>
       </c>
       <c r="J25" s="7" t="inlineStr">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="N25" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>명시</t>
         </is>
       </c>
       <c r="O25" s="7">
@@ -4363,7 +4363,7 @@
       </c>
       <c r="AA25" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>라벨만</t>
         </is>
       </c>
       <c r="AB25" s="7" t="inlineStr">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="AD25" s="6" t="inlineStr">
         <is>
-          <t>병원/클리닉 채널·공개정보 적음·수집중</t>
+          <t>클리닉스 MEGA-3A 미세파우더(가루) 80g·제형토큰 없음(파우더)·생선오일분말(어종 미표기)·EPA/DHA/ALA 함유하나 per회분 mg·순도 미공개(한 스푼≈제품 700mg)·항산화 비타민E+천연알파토코페롤+로즈마리추출물·제조원 대성물산(원료사 명시)·24개월 산패안정성·성분등록 제55VVW0022 (petemart 2124 자동수집+비전 20260620)</t>
         </is>
       </c>
     </row>

--- a/고양이_오메가3_제품_채점표.xlsx
+++ b/고양이_오메가3_제품_채점표.xlsx
@@ -3887,7 +3887,7 @@
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>취약</t>
         </is>
       </c>
       <c r="K22" s="7" t="inlineStr">

--- a/고양이_오메가3_제품_채점표.xlsx
+++ b/고양이_오메가3_제품_채점표.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C58"/>
+  <dimension ref="A1:C59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -799,151 +799,161 @@
     <row r="40">
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>대용량액상</t>
+          <t>파우더</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>대용량액상</t>
         </is>
       </c>
       <c r="C41" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>미상</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="43">
-      <c r="B43" s="3" t="inlineStr">
+    <row r="44">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>인증</t>
         </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>있음</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>있음</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>없음</t>
         </is>
       </c>
       <c r="C46" s="4" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="48">
-      <c r="B48" s="3" t="inlineStr">
+    <row r="47">
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>미상</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>COA</t>
         </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>공개</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>일부</t>
+          <t>공개</t>
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>일부</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>없음</t>
         </is>
       </c>
       <c r="C52" s="4" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="54">
-      <c r="B54" s="3" t="inlineStr">
+    <row r="53">
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>미상</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>원료사</t>
         </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>명시</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>일부</t>
+          <t>명시</t>
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>일부</t>
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>없음</t>
         </is>
       </c>
       <c r="C58" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>미상</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1235,7 +1245,7 @@
         <v/>
       </c>
       <c r="T2" s="8">
-        <f>IFERROR(VLOOKUP(I2,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J2,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K2,기준!$B$35:$C$41,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I2,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J2,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K2,기준!$B$35:$C$42,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U2" s="8">
@@ -1243,7 +1253,7 @@
         <v/>
       </c>
       <c r="V2" s="8">
-        <f>IFERROR(VLOOKUP(L2,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M2,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N2,기준!$B$55:$C$58,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L2,기준!$B$45:$C$47,2,FALSE),0)+IFERROR(VLOOKUP(M2,기준!$B$50:$C$53,2,FALSE),0)+IFERROR(VLOOKUP(N2,기준!$B$56:$C$59,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W2" s="8">
@@ -1370,7 +1380,7 @@
         <v/>
       </c>
       <c r="T3" s="8">
-        <f>IFERROR(VLOOKUP(I3,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J3,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K3,기준!$B$35:$C$41,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I3,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J3,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K3,기준!$B$35:$C$42,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U3" s="8">
@@ -1378,7 +1388,7 @@
         <v/>
       </c>
       <c r="V3" s="8">
-        <f>IFERROR(VLOOKUP(L3,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M3,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N3,기준!$B$55:$C$58,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L3,기준!$B$45:$C$47,2,FALSE),0)+IFERROR(VLOOKUP(M3,기준!$B$50:$C$53,2,FALSE),0)+IFERROR(VLOOKUP(N3,기준!$B$56:$C$59,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W3" s="8">
@@ -1507,7 +1517,7 @@
         <v/>
       </c>
       <c r="T4" s="8">
-        <f>IFERROR(VLOOKUP(I4,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J4,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K4,기준!$B$35:$C$41,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I4,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J4,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K4,기준!$B$35:$C$42,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U4" s="8">
@@ -1515,7 +1525,7 @@
         <v/>
       </c>
       <c r="V4" s="8">
-        <f>IFERROR(VLOOKUP(L4,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M4,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N4,기준!$B$55:$C$58,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L4,기준!$B$45:$C$47,2,FALSE),0)+IFERROR(VLOOKUP(M4,기준!$B$50:$C$53,2,FALSE),0)+IFERROR(VLOOKUP(N4,기준!$B$56:$C$59,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W4" s="8">
@@ -1644,7 +1654,7 @@
         <v/>
       </c>
       <c r="T5" s="8">
-        <f>IFERROR(VLOOKUP(I5,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J5,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K5,기준!$B$35:$C$41,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I5,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J5,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K5,기준!$B$35:$C$42,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U5" s="8">
@@ -1652,7 +1662,7 @@
         <v/>
       </c>
       <c r="V5" s="8">
-        <f>IFERROR(VLOOKUP(L5,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M5,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N5,기준!$B$55:$C$58,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L5,기준!$B$45:$C$47,2,FALSE),0)+IFERROR(VLOOKUP(M5,기준!$B$50:$C$53,2,FALSE),0)+IFERROR(VLOOKUP(N5,기준!$B$56:$C$59,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W5" s="8">
@@ -1781,7 +1791,7 @@
         <v/>
       </c>
       <c r="T6" s="8">
-        <f>IFERROR(VLOOKUP(I6,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J6,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K6,기준!$B$35:$C$41,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I6,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J6,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K6,기준!$B$35:$C$42,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U6" s="8">
@@ -1789,7 +1799,7 @@
         <v/>
       </c>
       <c r="V6" s="8">
-        <f>IFERROR(VLOOKUP(L6,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M6,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N6,기준!$B$55:$C$58,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L6,기준!$B$45:$C$47,2,FALSE),0)+IFERROR(VLOOKUP(M6,기준!$B$50:$C$53,2,FALSE),0)+IFERROR(VLOOKUP(N6,기준!$B$56:$C$59,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W6" s="8">
@@ -1918,7 +1928,7 @@
         <v/>
       </c>
       <c r="T7" s="8">
-        <f>IFERROR(VLOOKUP(I7,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J7,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K7,기준!$B$35:$C$41,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I7,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J7,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K7,기준!$B$35:$C$42,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U7" s="8">
@@ -1926,7 +1936,7 @@
         <v/>
       </c>
       <c r="V7" s="8">
-        <f>IFERROR(VLOOKUP(L7,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M7,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N7,기준!$B$55:$C$58,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L7,기준!$B$45:$C$47,2,FALSE),0)+IFERROR(VLOOKUP(M7,기준!$B$50:$C$53,2,FALSE),0)+IFERROR(VLOOKUP(N7,기준!$B$56:$C$59,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W7" s="8">
@@ -2051,7 +2061,7 @@
         <v/>
       </c>
       <c r="T8" s="8">
-        <f>IFERROR(VLOOKUP(I8,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J8,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K8,기준!$B$35:$C$41,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I8,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J8,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K8,기준!$B$35:$C$42,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U8" s="8">
@@ -2059,7 +2069,7 @@
         <v/>
       </c>
       <c r="V8" s="8">
-        <f>IFERROR(VLOOKUP(L8,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M8,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N8,기준!$B$55:$C$58,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L8,기준!$B$45:$C$47,2,FALSE),0)+IFERROR(VLOOKUP(M8,기준!$B$50:$C$53,2,FALSE),0)+IFERROR(VLOOKUP(N8,기준!$B$56:$C$59,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W8" s="8">
@@ -2184,7 +2194,7 @@
         <v/>
       </c>
       <c r="T9" s="8">
-        <f>IFERROR(VLOOKUP(I9,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J9,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K9,기준!$B$35:$C$41,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I9,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J9,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K9,기준!$B$35:$C$42,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U9" s="8">
@@ -2192,7 +2202,7 @@
         <v/>
       </c>
       <c r="V9" s="8">
-        <f>IFERROR(VLOOKUP(L9,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M9,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N9,기준!$B$55:$C$58,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L9,기준!$B$45:$C$47,2,FALSE),0)+IFERROR(VLOOKUP(M9,기준!$B$50:$C$53,2,FALSE),0)+IFERROR(VLOOKUP(N9,기준!$B$56:$C$59,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W9" s="8">
@@ -2317,7 +2327,7 @@
         <v/>
       </c>
       <c r="T10" s="8">
-        <f>IFERROR(VLOOKUP(I10,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J10,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K10,기준!$B$35:$C$41,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I10,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J10,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K10,기준!$B$35:$C$42,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U10" s="8">
@@ -2325,7 +2335,7 @@
         <v/>
       </c>
       <c r="V10" s="8">
-        <f>IFERROR(VLOOKUP(L10,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M10,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N10,기준!$B$55:$C$58,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L10,기준!$B$45:$C$47,2,FALSE),0)+IFERROR(VLOOKUP(M10,기준!$B$50:$C$53,2,FALSE),0)+IFERROR(VLOOKUP(N10,기준!$B$56:$C$59,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W10" s="8">
@@ -2454,7 +2464,7 @@
         <v/>
       </c>
       <c r="T11" s="8">
-        <f>IFERROR(VLOOKUP(I11,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J11,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K11,기준!$B$35:$C$41,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I11,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J11,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K11,기준!$B$35:$C$42,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U11" s="8">
@@ -2462,7 +2472,7 @@
         <v/>
       </c>
       <c r="V11" s="8">
-        <f>IFERROR(VLOOKUP(L11,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M11,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N11,기준!$B$55:$C$58,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L11,기준!$B$45:$C$47,2,FALSE),0)+IFERROR(VLOOKUP(M11,기준!$B$50:$C$53,2,FALSE),0)+IFERROR(VLOOKUP(N11,기준!$B$56:$C$59,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W11" s="8">
@@ -2587,7 +2597,7 @@
         <v/>
       </c>
       <c r="T12" s="8">
-        <f>IFERROR(VLOOKUP(I12,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J12,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K12,기준!$B$35:$C$41,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I12,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J12,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K12,기준!$B$35:$C$42,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U12" s="8">
@@ -2595,7 +2605,7 @@
         <v/>
       </c>
       <c r="V12" s="8">
-        <f>IFERROR(VLOOKUP(L12,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M12,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N12,기준!$B$55:$C$58,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L12,기준!$B$45:$C$47,2,FALSE),0)+IFERROR(VLOOKUP(M12,기준!$B$50:$C$53,2,FALSE),0)+IFERROR(VLOOKUP(N12,기준!$B$56:$C$59,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W12" s="8">
@@ -2720,7 +2730,7 @@
         <v/>
       </c>
       <c r="T13" s="8">
-        <f>IFERROR(VLOOKUP(I13,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J13,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K13,기준!$B$35:$C$41,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I13,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J13,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K13,기준!$B$35:$C$42,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U13" s="8">
@@ -2728,7 +2738,7 @@
         <v/>
       </c>
       <c r="V13" s="8">
-        <f>IFERROR(VLOOKUP(L13,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M13,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N13,기준!$B$55:$C$58,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L13,기준!$B$45:$C$47,2,FALSE),0)+IFERROR(VLOOKUP(M13,기준!$B$50:$C$53,2,FALSE),0)+IFERROR(VLOOKUP(N13,기준!$B$56:$C$59,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W13" s="8">
@@ -2855,7 +2865,7 @@
         <v/>
       </c>
       <c r="T14" s="8">
-        <f>IFERROR(VLOOKUP(I14,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J14,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K14,기준!$B$35:$C$41,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I14,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J14,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K14,기준!$B$35:$C$42,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U14" s="8">
@@ -2863,7 +2873,7 @@
         <v/>
       </c>
       <c r="V14" s="8">
-        <f>IFERROR(VLOOKUP(L14,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M14,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N14,기준!$B$55:$C$58,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L14,기준!$B$45:$C$47,2,FALSE),0)+IFERROR(VLOOKUP(M14,기준!$B$50:$C$53,2,FALSE),0)+IFERROR(VLOOKUP(N14,기준!$B$56:$C$59,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W14" s="8">
@@ -2988,7 +2998,7 @@
         <v/>
       </c>
       <c r="T15" s="8">
-        <f>IFERROR(VLOOKUP(I15,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J15,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K15,기준!$B$35:$C$41,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I15,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J15,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K15,기준!$B$35:$C$42,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U15" s="8">
@@ -2996,7 +3006,7 @@
         <v/>
       </c>
       <c r="V15" s="8">
-        <f>IFERROR(VLOOKUP(L15,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M15,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N15,기준!$B$55:$C$58,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L15,기준!$B$45:$C$47,2,FALSE),0)+IFERROR(VLOOKUP(M15,기준!$B$50:$C$53,2,FALSE),0)+IFERROR(VLOOKUP(N15,기준!$B$56:$C$59,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W15" s="8">
@@ -3125,7 +3135,7 @@
         <v/>
       </c>
       <c r="T16" s="8">
-        <f>IFERROR(VLOOKUP(I16,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J16,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K16,기준!$B$35:$C$41,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I16,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J16,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K16,기준!$B$35:$C$42,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U16" s="8">
@@ -3133,7 +3143,7 @@
         <v/>
       </c>
       <c r="V16" s="8">
-        <f>IFERROR(VLOOKUP(L16,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M16,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N16,기준!$B$55:$C$58,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L16,기준!$B$45:$C$47,2,FALSE),0)+IFERROR(VLOOKUP(M16,기준!$B$50:$C$53,2,FALSE),0)+IFERROR(VLOOKUP(N16,기준!$B$56:$C$59,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W16" s="8">
@@ -3262,7 +3272,7 @@
         <v/>
       </c>
       <c r="T17" s="8">
-        <f>IFERROR(VLOOKUP(I17,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J17,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K17,기준!$B$35:$C$41,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I17,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J17,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K17,기준!$B$35:$C$42,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U17" s="8">
@@ -3270,7 +3280,7 @@
         <v/>
       </c>
       <c r="V17" s="8">
-        <f>IFERROR(VLOOKUP(L17,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M17,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N17,기준!$B$55:$C$58,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L17,기준!$B$45:$C$47,2,FALSE),0)+IFERROR(VLOOKUP(M17,기준!$B$50:$C$53,2,FALSE),0)+IFERROR(VLOOKUP(N17,기준!$B$56:$C$59,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W17" s="8">
@@ -3397,7 +3407,7 @@
         <v/>
       </c>
       <c r="T18" s="8">
-        <f>IFERROR(VLOOKUP(I18,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J18,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K18,기준!$B$35:$C$41,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I18,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J18,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K18,기준!$B$35:$C$42,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U18" s="8">
@@ -3405,7 +3415,7 @@
         <v/>
       </c>
       <c r="V18" s="8">
-        <f>IFERROR(VLOOKUP(L18,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M18,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N18,기준!$B$55:$C$58,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L18,기준!$B$45:$C$47,2,FALSE),0)+IFERROR(VLOOKUP(M18,기준!$B$50:$C$53,2,FALSE),0)+IFERROR(VLOOKUP(N18,기준!$B$56:$C$59,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W18" s="8">
@@ -3534,7 +3544,7 @@
         <v/>
       </c>
       <c r="T19" s="8">
-        <f>IFERROR(VLOOKUP(I19,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J19,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K19,기준!$B$35:$C$41,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I19,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J19,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K19,기준!$B$35:$C$42,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U19" s="8">
@@ -3542,7 +3552,7 @@
         <v/>
       </c>
       <c r="V19" s="8">
-        <f>IFERROR(VLOOKUP(L19,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M19,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N19,기준!$B$55:$C$58,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L19,기준!$B$45:$C$47,2,FALSE),0)+IFERROR(VLOOKUP(M19,기준!$B$50:$C$53,2,FALSE),0)+IFERROR(VLOOKUP(N19,기준!$B$56:$C$59,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W19" s="8">
@@ -3667,7 +3677,7 @@
         <v/>
       </c>
       <c r="T20" s="8">
-        <f>IFERROR(VLOOKUP(I20,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J20,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K20,기준!$B$35:$C$41,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I20,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J20,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K20,기준!$B$35:$C$42,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U20" s="8">
@@ -3675,7 +3685,7 @@
         <v/>
       </c>
       <c r="V20" s="8">
-        <f>IFERROR(VLOOKUP(L20,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M20,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N20,기준!$B$55:$C$58,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L20,기준!$B$45:$C$47,2,FALSE),0)+IFERROR(VLOOKUP(M20,기준!$B$50:$C$53,2,FALSE),0)+IFERROR(VLOOKUP(N20,기준!$B$56:$C$59,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W20" s="8">
@@ -3800,7 +3810,7 @@
         <v/>
       </c>
       <c r="T21" s="8">
-        <f>IFERROR(VLOOKUP(I21,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J21,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K21,기준!$B$35:$C$41,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I21,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J21,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K21,기준!$B$35:$C$42,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U21" s="8">
@@ -3808,7 +3818,7 @@
         <v/>
       </c>
       <c r="V21" s="8">
-        <f>IFERROR(VLOOKUP(L21,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M21,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N21,기준!$B$55:$C$58,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L21,기준!$B$45:$C$47,2,FALSE),0)+IFERROR(VLOOKUP(M21,기준!$B$50:$C$53,2,FALSE),0)+IFERROR(VLOOKUP(N21,기준!$B$56:$C$59,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W21" s="8">
@@ -3933,7 +3943,7 @@
         <v/>
       </c>
       <c r="T22" s="8">
-        <f>IFERROR(VLOOKUP(I22,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J22,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K22,기준!$B$35:$C$41,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I22,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J22,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K22,기준!$B$35:$C$42,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U22" s="8">
@@ -3941,7 +3951,7 @@
         <v/>
       </c>
       <c r="V22" s="8">
-        <f>IFERROR(VLOOKUP(L22,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M22,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N22,기준!$B$55:$C$58,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L22,기준!$B$45:$C$47,2,FALSE),0)+IFERROR(VLOOKUP(M22,기준!$B$50:$C$53,2,FALSE),0)+IFERROR(VLOOKUP(N22,기준!$B$56:$C$59,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W22" s="8">
@@ -4068,7 +4078,7 @@
         <v/>
       </c>
       <c r="T23" s="8">
-        <f>IFERROR(VLOOKUP(I23,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J23,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K23,기준!$B$35:$C$41,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I23,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J23,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K23,기준!$B$35:$C$42,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U23" s="8">
@@ -4076,7 +4086,7 @@
         <v/>
       </c>
       <c r="V23" s="8">
-        <f>IFERROR(VLOOKUP(L23,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M23,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N23,기준!$B$55:$C$58,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L23,기준!$B$45:$C$47,2,FALSE),0)+IFERROR(VLOOKUP(M23,기준!$B$50:$C$53,2,FALSE),0)+IFERROR(VLOOKUP(N23,기준!$B$56:$C$59,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W23" s="8">
@@ -4201,7 +4211,7 @@
         <v/>
       </c>
       <c r="T24" s="8">
-        <f>IFERROR(VLOOKUP(I24,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J24,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K24,기준!$B$35:$C$41,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I24,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J24,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K24,기준!$B$35:$C$42,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U24" s="8">
@@ -4209,7 +4219,7 @@
         <v/>
       </c>
       <c r="V24" s="8">
-        <f>IFERROR(VLOOKUP(L24,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M24,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N24,기준!$B$55:$C$58,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L24,기준!$B$45:$C$47,2,FALSE),0)+IFERROR(VLOOKUP(M24,기준!$B$50:$C$53,2,FALSE),0)+IFERROR(VLOOKUP(N24,기준!$B$56:$C$59,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W24" s="8">
@@ -4288,12 +4298,12 @@
       </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>취약</t>
         </is>
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>파우더</t>
         </is>
       </c>
       <c r="L25" s="7" t="inlineStr">
@@ -4334,7 +4344,7 @@
         <v/>
       </c>
       <c r="T25" s="8">
-        <f>IFERROR(VLOOKUP(I25,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J25,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K25,기준!$B$35:$C$41,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I25,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J25,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K25,기준!$B$35:$C$42,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U25" s="8">
@@ -4342,7 +4352,7 @@
         <v/>
       </c>
       <c r="V25" s="8">
-        <f>IFERROR(VLOOKUP(L25,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M25,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N25,기준!$B$55:$C$58,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L25,기준!$B$45:$C$47,2,FALSE),0)+IFERROR(VLOOKUP(M25,기준!$B$50:$C$53,2,FALSE),0)+IFERROR(VLOOKUP(N25,기준!$B$56:$C$59,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W25" s="8">
@@ -4377,7 +4387,7 @@
       </c>
       <c r="AD25" s="6" t="inlineStr">
         <is>
-          <t>클리닉스 MEGA-3A 미세파우더(가루) 80g·제형토큰 없음(파우더)·생선오일분말(어종 미표기)·EPA/DHA/ALA 함유하나 per회분 mg·순도 미공개(한 스푼≈제품 700mg)·항산화 비타민E+천연알파토코페롤+로즈마리추출물·제조원 대성물산(원료사 명시)·24개월 산패안정성·성분등록 제55VVW0022 (petemart 2124 자동수집+비전 20260620)</t>
+          <t>클리닉스 MEGA-3A 미세파우더(가루) 80g·제형 파우더(4점)·큰 뚜껑 통이라 밀폐·보관 취약·생선오일분말(어종 미표기)·EPA/DHA/ALA 함유하나 per회분 mg·순도 미공개(한 스푼≈제품 700mg)·항산화 비타민E+천연알파토코페롤+로즈마리추출물·제조원 대성물산(원료사 명시)·24개월 산패안정성 표방(실측 미공개)·성분등록 제55VVW0022 (petemart 2124 자동수집+비전 20260620)</t>
         </is>
       </c>
     </row>
@@ -4467,7 +4477,7 @@
         <v/>
       </c>
       <c r="T26" s="8">
-        <f>IFERROR(VLOOKUP(I26,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J26,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K26,기준!$B$35:$C$41,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I26,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J26,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K26,기준!$B$35:$C$42,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U26" s="8">
@@ -4475,7 +4485,7 @@
         <v/>
       </c>
       <c r="V26" s="8">
-        <f>IFERROR(VLOOKUP(L26,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M26,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N26,기준!$B$55:$C$58,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L26,기준!$B$45:$C$47,2,FALSE),0)+IFERROR(VLOOKUP(M26,기준!$B$50:$C$53,2,FALSE),0)+IFERROR(VLOOKUP(N26,기준!$B$56:$C$59,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W26" s="8">
@@ -4604,7 +4614,7 @@
         <v/>
       </c>
       <c r="T27" s="8">
-        <f>IFERROR(VLOOKUP(I27,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J27,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K27,기준!$B$35:$C$41,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I27,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J27,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K27,기준!$B$35:$C$42,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U27" s="8">
@@ -4612,7 +4622,7 @@
         <v/>
       </c>
       <c r="V27" s="8">
-        <f>IFERROR(VLOOKUP(L27,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M27,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N27,기준!$B$55:$C$58,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L27,기준!$B$45:$C$47,2,FALSE),0)+IFERROR(VLOOKUP(M27,기준!$B$50:$C$53,2,FALSE),0)+IFERROR(VLOOKUP(N27,기준!$B$56:$C$59,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W27" s="8">
@@ -4739,7 +4749,7 @@
         <v/>
       </c>
       <c r="T28" s="8">
-        <f>IFERROR(VLOOKUP(I28,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J28,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K28,기준!$B$35:$C$41,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I28,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J28,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K28,기준!$B$35:$C$42,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U28" s="8">
@@ -4747,7 +4757,7 @@
         <v/>
       </c>
       <c r="V28" s="8">
-        <f>IFERROR(VLOOKUP(L28,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M28,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N28,기준!$B$55:$C$58,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L28,기준!$B$45:$C$47,2,FALSE),0)+IFERROR(VLOOKUP(M28,기준!$B$50:$C$53,2,FALSE),0)+IFERROR(VLOOKUP(N28,기준!$B$56:$C$59,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W28" s="8">
@@ -4872,7 +4882,7 @@
         <v/>
       </c>
       <c r="T29" s="8">
-        <f>IFERROR(VLOOKUP(I29,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J29,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K29,기준!$B$35:$C$41,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I29,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J29,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K29,기준!$B$35:$C$42,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U29" s="8">
@@ -4880,7 +4890,7 @@
         <v/>
       </c>
       <c r="V29" s="8">
-        <f>IFERROR(VLOOKUP(L29,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M29,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N29,기준!$B$55:$C$58,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L29,기준!$B$45:$C$47,2,FALSE),0)+IFERROR(VLOOKUP(M29,기준!$B$50:$C$53,2,FALSE),0)+IFERROR(VLOOKUP(N29,기준!$B$56:$C$59,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W29" s="8">
@@ -5007,7 +5017,7 @@
         <v/>
       </c>
       <c r="T30" s="8">
-        <f>IFERROR(VLOOKUP(I30,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J30,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K30,기준!$B$35:$C$41,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I30,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J30,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K30,기준!$B$35:$C$42,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U30" s="8">
@@ -5015,7 +5025,7 @@
         <v/>
       </c>
       <c r="V30" s="8">
-        <f>IFERROR(VLOOKUP(L30,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M30,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N30,기준!$B$55:$C$58,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L30,기준!$B$45:$C$47,2,FALSE),0)+IFERROR(VLOOKUP(M30,기준!$B$50:$C$53,2,FALSE),0)+IFERROR(VLOOKUP(N30,기준!$B$56:$C$59,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W30" s="8">
@@ -5142,7 +5152,7 @@
         <v/>
       </c>
       <c r="T31" s="8">
-        <f>IFERROR(VLOOKUP(I31,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J31,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K31,기준!$B$35:$C$41,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I31,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J31,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K31,기준!$B$35:$C$42,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U31" s="8">
@@ -5150,7 +5160,7 @@
         <v/>
       </c>
       <c r="V31" s="8">
-        <f>IFERROR(VLOOKUP(L31,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M31,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N31,기준!$B$55:$C$58,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L31,기준!$B$45:$C$47,2,FALSE),0)+IFERROR(VLOOKUP(M31,기준!$B$50:$C$53,2,FALSE),0)+IFERROR(VLOOKUP(N31,기준!$B$56:$C$59,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W31" s="8">
@@ -5279,7 +5289,7 @@
         <v/>
       </c>
       <c r="T32" s="8">
-        <f>IFERROR(VLOOKUP(I32,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J32,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K32,기준!$B$35:$C$41,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I32,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J32,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K32,기준!$B$35:$C$42,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U32" s="8">
@@ -5287,7 +5297,7 @@
         <v/>
       </c>
       <c r="V32" s="8">
-        <f>IFERROR(VLOOKUP(L32,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M32,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N32,기준!$B$55:$C$58,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L32,기준!$B$45:$C$47,2,FALSE),0)+IFERROR(VLOOKUP(M32,기준!$B$50:$C$53,2,FALSE),0)+IFERROR(VLOOKUP(N32,기준!$B$56:$C$59,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W32" s="8">
@@ -5416,7 +5426,7 @@
         <v/>
       </c>
       <c r="T33" s="8">
-        <f>IFERROR(VLOOKUP(I33,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J33,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K33,기준!$B$35:$C$41,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I33,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J33,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K33,기준!$B$35:$C$42,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U33" s="8">
@@ -5424,7 +5434,7 @@
         <v/>
       </c>
       <c r="V33" s="8">
-        <f>IFERROR(VLOOKUP(L33,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M33,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N33,기준!$B$55:$C$58,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L33,기준!$B$45:$C$47,2,FALSE),0)+IFERROR(VLOOKUP(M33,기준!$B$50:$C$53,2,FALSE),0)+IFERROR(VLOOKUP(N33,기준!$B$56:$C$59,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W33" s="8">
@@ -5551,7 +5561,7 @@
         <v/>
       </c>
       <c r="T34" s="8">
-        <f>IFERROR(VLOOKUP(I34,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J34,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K34,기준!$B$35:$C$41,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(I34,기준!$B$24:$C$26,2,FALSE),0)+IFERROR(VLOOKUP(J34,기준!$B$29:$C$32,2,FALSE),0)+IFERROR(VLOOKUP(K34,기준!$B$35:$C$42,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="U34" s="8">
@@ -5559,7 +5569,7 @@
         <v/>
       </c>
       <c r="V34" s="8">
-        <f>IFERROR(VLOOKUP(L34,기준!$B$44:$C$46,2,FALSE),0)+IFERROR(VLOOKUP(M34,기준!$B$49:$C$52,2,FALSE),0)+IFERROR(VLOOKUP(N34,기준!$B$55:$C$58,2,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(L34,기준!$B$45:$C$47,2,FALSE),0)+IFERROR(VLOOKUP(M34,기준!$B$50:$C$53,2,FALSE),0)+IFERROR(VLOOKUP(N34,기준!$B$56:$C$59,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="W34" s="8">

--- a/고양이_오메가3_제품_채점표.xlsx
+++ b/고양이_오메가3_제품_채점표.xlsx
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>조공 rTG 퓨어 오메가3</t>
+          <t>조공 rTG 퓨어 오메가3(=#4 동일·개명 중복)</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -1309,9 +1309,7 @@
         </is>
       </c>
       <c r="D3" s="7" t="n"/>
-      <c r="E3" s="7" t="n">
-        <v>80</v>
-      </c>
+      <c r="E3" s="7" t="n"/>
       <c r="F3" s="7" t="inlineStr">
         <is>
           <t>미상</t>
@@ -1319,7 +1317,7 @@
       </c>
       <c r="G3" s="7" t="inlineStr">
         <is>
-          <t>rTG</t>
+          <t>미상</t>
         </is>
       </c>
       <c r="H3" s="7" t="inlineStr">
@@ -1339,22 +1337,22 @@
       </c>
       <c r="K3" s="7" t="inlineStr">
         <is>
-          <t>캡슐</t>
+          <t>미상</t>
         </is>
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
-          <t>있음</t>
+          <t>미상</t>
         </is>
       </c>
       <c r="M3" s="7" t="inlineStr">
         <is>
-          <t>일부</t>
+          <t>미상</t>
         </is>
       </c>
       <c r="N3" s="7" t="inlineStr">
         <is>
-          <t>명시</t>
+          <t>미상</t>
         </is>
       </c>
       <c r="O3" s="7">
@@ -1409,13 +1407,12 @@
       </c>
       <c r="AA3" s="7" t="inlineStr">
         <is>
-          <t>공개·검증</t>
-        </is>
-      </c>
-      <c r="AB3" s="7" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
+          <t>중복</t>
+        </is>
+      </c>
+      <c r="AB3" s="7">
+        <f>#4</f>
+        <v/>
       </c>
       <c r="AC3" s="6">
         <f>(IF(ISNUMBER(D3),1,0)+IF(ISNUMBER(E3),1,0)+IF(AND(F3&lt;&gt;"미상",F3&lt;&gt;""),1,0)+IF(AND(G3&lt;&gt;"미상",G3&lt;&gt;""),1,0)+IF(AND(H3&lt;&gt;"미상",H3&lt;&gt;""),1,0)+IF(AND(I3&lt;&gt;"미상",I3&lt;&gt;""),1,0)+IF(AND(J3&lt;&gt;"미상",J3&lt;&gt;""),1,0)+IF(AND(K3&lt;&gt;"미상",K3&lt;&gt;""),1,0)+IF(AND(L3&lt;&gt;"미상",L3&lt;&gt;""),1,0)+IF(AND(M3&lt;&gt;"미상",M3&lt;&gt;""),1,0)+IF(AND(N3&lt;&gt;"미상",N3&lt;&gt;""),1,0))&amp;"/11"</f>
@@ -1423,7 +1420,7 @@
       </c>
       <c r="AD3" s="6" t="inlineStr">
         <is>
-          <t>IFOS 5-star·Solutex·순도80%+ (모굿인)</t>
+          <t>사용자 확인: '조공 rTG 퓨어'는 '퓨어 오메가-3 미니'로 개명되어 #4(조공 데일리 퓨어 오메가-3 미니)와 동일 제품·중복 항목·채점 제외(점수데이터 비움)·실제 스펙은 #4 참조(EPA73.33+DHA36.67=110·순도75·Solutex rTG·IFOS) (choandkang 629)</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2101,7 @@
       </c>
       <c r="AD8" s="6" t="inlineStr">
         <is>
-          <t>씹는 츄·스펙 수집중</t>
+          <t>씹는 츄(제형 츄)·청어 원료·고양이 직접 급여 가능성(2차출처 미검증)·판매처 소수(쿠팡 등)이며 쿠팡 봇차단(403)으로 상세 자동수집 불가·EPA/DHA mg·순도 미공개 (coupang 197646144 차단)</t>
         </is>
       </c>
     </row>

--- a/고양이_오메가3_제품_채점표.xlsx
+++ b/고양이_오메가3_제품_채점표.xlsx
@@ -2002,17 +2002,17 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>소형어</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>있음</t>
         </is>
       </c>
       <c r="J8" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="K8" s="7" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="N8" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>명시</t>
         </is>
       </c>
       <c r="O8" s="7">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="AA8" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>라벨만</t>
         </is>
       </c>
       <c r="AB8" s="7" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="AD8" s="6" t="inlineStr">
         <is>
-          <t>씹는 츄(제형 츄)·청어 원료·고양이 직접 급여 가능성(2차출처 미검증)·판매처 소수(쿠팡 등)이며 쿠팡 봇차단(403)으로 상세 자동수집 불가·EPA/DHA mg·순도 미공개 (coupang 197646144 차단)</t>
+          <t>88PET 88OMEGAGUARD 씹어먹는 정제타입(츄) 60정 강아지·고양이 공용·노르웨이 Epax 정제어유(먹이사슬 최하단 청어=소형어)·DHA+EPA+토코페롤(항산화 있음)·흰 불투명병(포장 보통)·ELT사이언스 국내제조(원료사 명시)·VGMP/수의사추천/휴먼그레이드(IFOS·GOED 아님→인증 미상)·per정 EPA+DHA mg·순도·형태(rTG/TG) 미표기 (88PET 상세이미지 비전확인 20260620)</t>
         </is>
       </c>
     </row>

--- a/고양이_오메가3_제품_채점표.xlsx
+++ b/고양이_오메가3_제품_채점표.xlsx
@@ -2234,7 +2234,7 @@
       </c>
       <c r="AD9" s="6" t="inlineStr">
         <is>
-          <t>표시 500mg(오일 추정)·EPA+DHA 미상</t>
+          <t>표시 500mg(오일 추정)·EPA+DHA 미상·국내 판매처 없음(2026-06 확인)·단종 추정으로 추가 수집 불가</t>
         </is>
       </c>
     </row>
@@ -2521,54 +2521,58 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>펫</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="n"/>
-      <c r="E12" s="7" t="n"/>
+          <t>펫·캡슐</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>80</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>80</v>
+      </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>명시</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>rTG</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>소형어</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>있음</t>
         </is>
       </c>
       <c r="J12" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>우수</t>
         </is>
       </c>
       <c r="K12" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>캡슐</t>
         </is>
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>있음</t>
         </is>
       </c>
       <c r="M12" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>공개</t>
         </is>
       </c>
       <c r="N12" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>명시</t>
         </is>
       </c>
       <c r="O12" s="7">
@@ -2623,12 +2627,12 @@
       </c>
       <c r="AA12" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>공개·검증</t>
         </is>
       </c>
       <c r="AB12" s="7" t="inlineStr">
         <is>
-          <t>미정</t>
+          <t>일반유지</t>
         </is>
       </c>
       <c r="AC12" s="6">
@@ -2637,7 +2641,7 @@
       </c>
       <c r="AD12" s="6" t="inlineStr">
         <is>
-          <t>스펙 수집중</t>
+          <t>룰루키친 룰루파마 오메가3 100mg(3oval) SKU·1캡슐 내용물 100mg 중 EPA48+DHA32=80mg·순도80%·KD-PUR 480320 rTG(원료 EPA480/DHA320 mg/g)·소형 어종·d-토코페롤·PVDC 개별포장·IFOS5★+HACCP/ISO·Peroxide 1.63 실측(DeKrA COA공개)·코스맥스펫 국내제조(KD Pharma 원료)·250mg(6oval)형은 EPA120+DHA80=200mg (wooof 24245 자동수집+비전 20260620)</t>
         </is>
       </c>
     </row>
@@ -2654,54 +2658,58 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>펫</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="n"/>
-      <c r="E13" s="7" t="n"/>
+          <t>펫·캡슐</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>80</v>
+      </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>일부</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>rTG</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>소형어</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>있음</t>
         </is>
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>우수</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>캡슐</t>
         </is>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>있음</t>
         </is>
       </c>
       <c r="M13" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>공개</t>
         </is>
       </c>
       <c r="N13" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>명시</t>
         </is>
       </c>
       <c r="O13" s="7">
@@ -2756,12 +2764,12 @@
       </c>
       <c r="AA13" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>공개·검증</t>
         </is>
       </c>
       <c r="AB13" s="7" t="inlineStr">
         <is>
-          <t>미정</t>
+          <t>일반유지</t>
         </is>
       </c>
       <c r="AC13" s="6">
@@ -2770,7 +2778,7 @@
       </c>
       <c r="AD13" s="6" t="inlineStr">
         <is>
-          <t>스펙 수집중</t>
+          <t>씽크라이크펫 바이탈케어 알티지 오메가3 250mg 60캡슐·1캡슐 내용물 250mg 중 EPA+DHA 200mg·순도80%·KD-PUR 480320 rTG(KD Pharma 독일·#11과 동일 원료=소형어 멸치)·비타민E(항산화)·PVDC PTP 개별포장(우수)·IFOS5★·산가/과산화물가/아니시딘가/TOTOX/중금속 실측 공개(COA공개)·약1.3cm 소형캡슐·실제중량 15g (lifet P01106 자동수집+비전 20260620)</t>
         </is>
       </c>
     </row>
@@ -4404,41 +4412,45 @@
           <t>병원·클리닉</t>
         </is>
       </c>
-      <c r="D26" s="7" t="n"/>
-      <c r="E26" s="7" t="n"/>
+      <c r="D26" s="7" t="n">
+        <v>119</v>
+      </c>
+      <c r="E26" s="7" t="n">
+        <v>79</v>
+      </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>일부</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>rTG</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>소형어</t>
         </is>
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>있음</t>
         </is>
       </c>
       <c r="J26" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>우수</t>
         </is>
       </c>
       <c r="K26" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>소프트젤</t>
         </is>
       </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>있음</t>
         </is>
       </c>
       <c r="M26" s="7" t="inlineStr">
@@ -4448,7 +4460,7 @@
       </c>
       <c r="N26" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>명시</t>
         </is>
       </c>
       <c r="O26" s="7">
@@ -4503,12 +4515,12 @@
       </c>
       <c r="AA26" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>라벨만</t>
         </is>
       </c>
       <c r="AB26" s="7" t="inlineStr">
         <is>
-          <t>미정</t>
+          <t>일반유지</t>
         </is>
       </c>
       <c r="AC26" s="6">
@@ -4517,7 +4529,7 @@
       </c>
       <c r="AD26" s="6" t="inlineStr">
         <is>
-          <t>병원 납품·공개정보 적음·수집중</t>
+          <t>베네핏 오메가3플러스(수의사처방전용)·2캡슐(150mg×2)당 DHA+EPA 238mg→1캡슐 119mg·순도 238/300=79%(고순도)·독일 KD Pharma rTG·kd-pür 저온초임계(산패 최소화)·소형 어종(중금속 최소화)·IFOS 5 Star 원료·비타민E 1.4mg α-TE·블리스터 개별포장·연질캡슐·480정·실측 COA 수치는 미표기 (제조 ET022402 상세이미지 비전 20260620)</t>
         </is>
       </c>
     </row>

--- a/고양이_오메가3_제품_채점표.xlsx
+++ b/고양이_오메가3_제품_채점표.xlsx
@@ -4138,12 +4138,12 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>뉴트리코어 펫 식물성 rTG</t>
+          <t>뉴트리코어 하이퍼셀 식물성 알티지 오메가3(사람용)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>펫·식물성</t>
+          <t>사람용·식물성</t>
         </is>
       </c>
       <c r="D24" s="7" t="n"/>
@@ -4175,7 +4175,7 @@
       </c>
       <c r="K24" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>캡슐</t>
         </is>
       </c>
       <c r="L24" s="7" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="AD24" s="6" t="inlineStr">
         <is>
-          <t>식물성 rTG=미세조류 DHA(EPA 거의 없음)·상한 부적용·DHA 편중·브랜드 식물성라인 순도~80%·공식몰(nutricore.co.kr) 로그인 게이트라 펫 SKU 스펙 직접확인 불가·확인된 건 사람용 하이퍼셀(EPA+DHA 900mg/일·미세조류 rTG)뿐 (소셜타임스·공식 goodsInnb 2608678 게이트)</t>
+          <t>★사람용 제품(펫 전용 SKU 없음)·정확명 '뉴트리코어 하이퍼셀 식물성 알티지 오메가3' 또는 'NCS 초임계 식물성 알티지 오메가3'·미세조류 식물성 rTG(EPA 거의 없음·DHA 편중)·해양성 상한 부적용·EPA+DHA 900mg/일(사람 기준)·순도~80%·식물성캡슐·PTP 개별포장·공식몰 로그인 게이트 (다나와 pcode 9823842·공식 goodsInnb 2608678/2608648)</t>
         </is>
       </c>
     </row>

--- a/고양이_오메가3_제품_채점표.xlsx
+++ b/고양이_오메가3_제품_채점표.xlsx
@@ -4146,11 +4146,15 @@
           <t>사람용·식물성</t>
         </is>
       </c>
-      <c r="D24" s="7" t="n"/>
-      <c r="E24" s="7" t="n"/>
+      <c r="D24" s="7" t="n">
+        <v>900</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>67</v>
+      </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>일부</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
@@ -4170,7 +4174,7 @@
       </c>
       <c r="J24" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>우수</t>
         </is>
       </c>
       <c r="K24" s="7" t="inlineStr">
@@ -4180,7 +4184,7 @@
       </c>
       <c r="L24" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>있음</t>
         </is>
       </c>
       <c r="M24" s="7" t="inlineStr">
@@ -4259,7 +4263,7 @@
       </c>
       <c r="AD24" s="6" t="inlineStr">
         <is>
-          <t>★사람용 제품(펫 전용 SKU 없음)·정확명 '뉴트리코어 하이퍼셀 식물성 알티지 오메가3' 또는 'NCS 초임계 식물성 알티지 오메가3'·미세조류 식물성 rTG(EPA 거의 없음·DHA 편중)·해양성 상한 부적용·EPA+DHA 900mg/일(사람 기준)·순도~80%·식물성캡슐·PTP 개별포장·공식몰 로그인 게이트 (다나와 pcode 9823842·공식 goodsInnb 2608678/2608648)</t>
+          <t>사람용 건기식(1일1캡슐·펫전용 SKU 없음)·1캡슐 1340mg 중 EPA+DHA 900mg(완제품 순도 67%=900/1340·'80%'는 원료 미세조류 기준)·미세조류 rTG(DHA 편중·EPA 적음)·SEDS 하이퍼셀 인지질코팅(흡수↑)·50℃ 저온초임계(헥산 NO)·GOED 인증원료·식물성캡슐(홍조류)·개별 PTP 포장·900mg은 사람 1일량이라 4kg 고양이엔 분할급여 어려움(NCS 구버전=1126mg/순도80%) (공식 상세이미지 비전 20260620)</t>
         </is>
       </c>
     </row>

--- a/고양이_오메가3_제품_채점표.xlsx
+++ b/고양이_오메가3_제품_채점표.xlsx
@@ -3991,7 +3991,7 @@
       </c>
       <c r="AD22" s="6" t="inlineStr">
         <is>
-          <t>오메가3 플러스펫 캐나다 물개오일 140ml+루테인·해양 포유류 오일(해양성·EPA/DHA/DPA 공급</t>
+          <t>오메가3 플러스펫 캐나다 물개오일 140ml+루테인·해양 포유류 오일(해양성·EPA/DHA/DPA 공급·어종=해양포유류)·자연유 TG·투명용기(포장 취약)·캐나다산(원료사 명시)·실온보관·EPA+DHA mg/순도 미공개(SSG·펫프렌즈 확인) (ssg itemId 1000534830783 20260620)</t>
         </is>
       </c>
     </row>

--- a/고양이_오메가3_제품_채점표.xlsx
+++ b/고양이_오메가3_제품_채점표.xlsx
@@ -1889,7 +1889,7 @@
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>있음</t>
         </is>
       </c>
       <c r="M7" s="7" t="inlineStr">
@@ -1968,7 +1968,7 @@
       </c>
       <c r="AD7" s="6" t="inlineStr">
         <is>
-          <t>1소프트젤 EPA155+DHA100=255mg·멸치/정어리/고등어/청어·TG·토코페롤·배치별 시험공개 (onlynaturalpet/petco)</t>
+          <t>1소프트젤 EPA155+DHA100=255mg·멸치/정어리/고등어/청어·TG·토코페롤·배치별 시험공개·IFOS 완제품 인증(certifications.nutrasource.ca NRDN0097</t>
         </is>
       </c>
     </row>
@@ -4596,7 +4596,7 @@
       </c>
       <c r="M27" s="7" t="inlineStr">
         <is>
-          <t>일부</t>
+          <t>공개</t>
         </is>
       </c>
       <c r="N27" s="7" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="AD27" s="6" t="inlineStr">
         <is>
-          <t>EPA+DHA 937/캡슐·순도~75%·AlaskaOmega·IFOS·병포장 (필라이즈)</t>
+          <t>EPA+DHA 937/캡슐(라벨 EPA687+DHA250)·IFOS 5★ 완제품 lot UC180494 실측 EPA704+DHA271·TOTOX/과산화물/아니시딘/중금속(수은·납)/PCB/다이옥신 전부 합격(COA 공개)·AlaskaOmega·순도~75%·병포장 (IFOS certifications.nutrasource.ca)</t>
         </is>
       </c>
     </row>

--- a/고양이_오메가3_제품_채점표.xlsx
+++ b/고양이_오메가3_제품_채점표.xlsx
@@ -4711,12 +4711,12 @@
       </c>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>있음</t>
         </is>
       </c>
       <c r="J28" s="7" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>우수</t>
         </is>
       </c>
       <c r="K28" s="7" t="inlineStr">
@@ -4805,7 +4805,7 @@
       </c>
       <c r="AD28" s="6" t="inlineStr">
         <is>
-          <t>1캡슐 EPA+DHA 300mg·rTG·AlaskaOmega(알래스카 명태유=일반어)·비타민A 첨가(눈건강 기능성)·식약처 이중기능성 (ckdhcmall/필라이즈)</t>
+          <t>1캡슐 EPA+DHA 300mg(2캡슐 600mg)·rTG·AlaskaOmega(알래스카 명태유=일반어)·비타민E 11mg α-TE(항산화)·PTP 개별포장·비타민A 첨가(눈건강 기능성→상한40)·식약처 이중기능성·HACCP(IFOS 아님) (ckdhcmall/필라이즈/다나와)</t>
         </is>
       </c>
     </row>
